--- a/input/reg_employmentSelection.xlsx
+++ b/input/reg_employmentSelection.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPathsFork\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74BD663-D45B-4D16-9EAB-7EEC38374794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D0BA245-5975-4A87-8469-CA67F28FE086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="989" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="14566" windowHeight="17363" tabRatio="989" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="23">
   <si>
     <t>Dag</t>
   </si>
@@ -64,9 +64,6 @@
   </si>
   <si>
     <t>Dcpst_Partnered</t>
-  </si>
-  <si>
-    <t>Dlltsd</t>
   </si>
   <si>
     <t>Deh_c3_Medium_Dag</t>
@@ -103,6 +100,15 @@
   </si>
   <si>
     <t>COEFFICIENT</t>
+  </si>
+  <si>
+    <t>Y2020</t>
+  </si>
+  <si>
+    <t>Pt</t>
+  </si>
+  <si>
+    <t>RealWageGrowth</t>
   </si>
 </sst>
 </file>
@@ -491,14 +497,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="1"/>
+    <col min="2" max="2" width="10.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.1328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>5</v>
       </c>
@@ -510,9 +516,9 @@
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
     </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -520,7 +526,7 @@
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -528,7 +534,7 @@
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -536,7 +542,7 @@
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -544,7 +550,7 @@
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="6"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -552,7 +558,7 @@
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -560,7 +566,7 @@
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -568,7 +574,7 @@
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -589,18 +595,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02CE3350-4A93-42D4-A29F-C2F61C83EA8F}">
   <dimension ref="A1:S18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="25.5703125" style="2" customWidth="1"/>
-    <col min="2" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="25.59765625" style="2" customWidth="1"/>
+    <col min="2" max="16384" width="9.1328125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
         <v>19</v>
-      </c>
-      <c r="B1" t="s">
-        <v>20</v>
       </c>
       <c r="C1" t="s">
         <v>6</v>
@@ -618,19 +624,19 @@
         <v>4</v>
       </c>
       <c r="H1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" t="s">
         <v>9</v>
-      </c>
-      <c r="I1" t="s">
-        <v>10</v>
       </c>
       <c r="J1" t="s">
         <v>7</v>
       </c>
       <c r="K1" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" t="s">
         <v>12</v>
-      </c>
-      <c r="L1" t="s">
-        <v>8</v>
       </c>
       <c r="M1" t="s">
         <v>13</v>
@@ -648,1013 +654,1013 @@
         <v>17</v>
       </c>
       <c r="R1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="S1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2">
-        <v>0.40952509296311007</v>
+        <v>0.33947521800427954</v>
       </c>
       <c r="C2">
-        <v>2.3275775906513303E-3</v>
+        <v>4.1578601804538578E-3</v>
       </c>
       <c r="D2">
-        <v>-1.8714812420391854E-4</v>
+        <v>-3.0193286074183987E-4</v>
       </c>
       <c r="E2">
-        <v>1.7733760822851084E-6</v>
+        <v>2.7900136837488078E-6</v>
       </c>
       <c r="F2">
-        <v>-2.7733473590196237E-4</v>
+        <v>-4.0506264095513432E-4</v>
       </c>
       <c r="G2">
-        <v>-8.618298961913923E-4</v>
+        <v>-1.4512996463483716E-3</v>
       </c>
       <c r="H2">
-        <v>5.7340070196809313E-6</v>
+        <v>8.3722923393496956E-6</v>
       </c>
       <c r="I2">
-        <v>1.7482516347750133E-5</v>
+        <v>2.9654429672909643E-5</v>
       </c>
       <c r="J2">
-        <v>-1.5422064400803391E-4</v>
+        <v>-2.124165136014884E-4</v>
       </c>
       <c r="K2">
-        <v>-2.1660382480333438E-4</v>
+        <v>-6.9672191409764152E-4</v>
       </c>
       <c r="L2">
-        <v>-2.7982920129024362E-5</v>
+        <v>8.2230338360956309E-5</v>
       </c>
       <c r="M2">
-        <v>2.7881217298163295E-5</v>
+        <v>1.1537777637961582E-4</v>
       </c>
       <c r="N2">
-        <v>-2.6583405447699014E-6</v>
+        <v>1.4887031993687382E-4</v>
       </c>
       <c r="O2">
-        <v>2.2220239723418729E-6</v>
+        <v>3.9472029225297626E-4</v>
       </c>
       <c r="P2">
-        <v>1.3371268846366913E-4</v>
+        <v>2.0829329675364631E-5</v>
       </c>
       <c r="Q2">
-        <v>1.8172697328570783E-5</v>
+        <v>1.6505616544136144E-5</v>
       </c>
       <c r="R2">
-        <v>6.4583828968666838E-6</v>
+        <v>-1.8257688265506123E-5</v>
       </c>
       <c r="S2">
-        <v>2.5610463806704422E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+        <v>3.8863158939922331E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3">
-        <v>0.18742998641371927</v>
+        <v>0.21537408501480684</v>
       </c>
       <c r="C3">
-        <v>-1.8714812420391854E-4</v>
+        <v>-3.0193286074183987E-4</v>
       </c>
       <c r="D3">
-        <v>7.4972069518476939E-5</v>
+        <v>1.4597802320875762E-4</v>
       </c>
       <c r="E3">
-        <v>-7.7557539214614699E-7</v>
+        <v>-1.5431226701066272E-6</v>
       </c>
       <c r="F3">
-        <v>3.1012044319812945E-4</v>
+        <v>5.9987331833383521E-4</v>
       </c>
       <c r="G3">
-        <v>4.065801368757865E-4</v>
+        <v>7.5626170460459184E-4</v>
       </c>
       <c r="H3">
-        <v>-7.1150174870425059E-6</v>
+        <v>-1.4555724641660523E-5</v>
       </c>
       <c r="I3">
-        <v>-9.0719197713623329E-6</v>
+        <v>-1.7795484084529296E-5</v>
       </c>
       <c r="J3">
-        <v>-5.4457863317199559E-5</v>
+        <v>-6.8632436667661234E-5</v>
       </c>
       <c r="K3">
-        <v>-5.6163327258087624E-5</v>
+        <v>-1.8447619617759933E-4</v>
       </c>
       <c r="L3">
-        <v>-2.7085688584028331E-5</v>
+        <v>3.0708243458747904E-5</v>
       </c>
       <c r="M3">
-        <v>5.5867431346801727E-6</v>
+        <v>7.9953347160342911E-5</v>
       </c>
       <c r="N3">
-        <v>1.8242208687651923E-5</v>
+        <v>1.1417204932218116E-4</v>
       </c>
       <c r="O3">
-        <v>2.0030135838923209E-5</v>
+        <v>1.6189528805677831E-4</v>
       </c>
       <c r="P3">
-        <v>6.1489643241535523E-5</v>
+        <v>1.6872595630338986E-5</v>
       </c>
       <c r="Q3">
-        <v>1.2109694468228494E-5</v>
+        <v>1.5510551216171264E-5</v>
       </c>
       <c r="R3">
-        <v>1.0378124612031819E-5</v>
+        <v>8.7026706933264609E-6</v>
       </c>
       <c r="S3">
-        <v>-1.453612767902595E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+        <v>-2.8581571301533183E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>1</v>
       </c>
       <c r="B4">
-        <v>-2.4514741867794976E-3</v>
+        <v>-2.8917744464489249E-3</v>
       </c>
       <c r="C4">
-        <v>1.7733760822851084E-6</v>
+        <v>2.7900136837488078E-6</v>
       </c>
       <c r="D4">
-        <v>-7.7557539214614699E-7</v>
+        <v>-1.5431226701066272E-6</v>
       </c>
       <c r="E4">
-        <v>8.6599557754772367E-9</v>
+        <v>1.7703981049484196E-8</v>
       </c>
       <c r="F4">
-        <v>-1.4280215780212563E-6</v>
+        <v>-2.6699496081577421E-6</v>
       </c>
       <c r="G4">
-        <v>-2.4262437242658887E-6</v>
+        <v>-4.2550467905392369E-6</v>
       </c>
       <c r="H4">
-        <v>2.7654122145124706E-8</v>
+        <v>5.5562381026292045E-8</v>
       </c>
       <c r="I4">
-        <v>4.8105828367059159E-8</v>
+        <v>8.9049953555803996E-8</v>
       </c>
       <c r="J4">
-        <v>5.506980298671625E-7</v>
+        <v>6.2990552620261931E-7</v>
       </c>
       <c r="K4">
-        <v>7.667893214258164E-7</v>
+        <v>2.4292947141390848E-6</v>
       </c>
       <c r="L4">
-        <v>2.9932408531082515E-7</v>
+        <v>-4.6186928442329343E-7</v>
       </c>
       <c r="M4">
-        <v>-8.6369456114027877E-8</v>
+        <v>-1.0434650265746367E-6</v>
       </c>
       <c r="N4">
-        <v>-2.4279305128169216E-7</v>
+        <v>-1.2424134070337621E-6</v>
       </c>
       <c r="O4">
-        <v>-1.6075309552336896E-7</v>
+        <v>-1.6183808964829881E-6</v>
       </c>
       <c r="P4">
-        <v>-5.1545653324300121E-7</v>
+        <v>-1.2580808571203276E-7</v>
       </c>
       <c r="Q4">
-        <v>-1.0073124954324747E-7</v>
+        <v>-6.6606313499838964E-8</v>
       </c>
       <c r="R4">
-        <v>-5.0205343678327296E-8</v>
+        <v>-1.9557442724789961E-7</v>
       </c>
       <c r="S4">
-        <v>1.3935226290111964E-5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+        <v>2.818157147405309E-5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>2</v>
       </c>
       <c r="B5">
-        <v>-0.40815037257324416</v>
+        <v>-0.36295580308515796</v>
       </c>
       <c r="C5">
-        <v>-2.7733473590196237E-4</v>
+        <v>-4.0506264095513432E-4</v>
       </c>
       <c r="D5">
-        <v>3.1012044319812945E-4</v>
+        <v>5.9987331833383521E-4</v>
       </c>
       <c r="E5">
-        <v>-1.4280215780212563E-6</v>
+        <v>-2.6699496081577421E-6</v>
       </c>
       <c r="F5">
-        <v>1.0295147115375646E-2</v>
+        <v>1.9155244870478587E-2</v>
       </c>
       <c r="G5">
-        <v>8.3572367996208336E-3</v>
+        <v>1.5804055162631447E-2</v>
       </c>
       <c r="H5">
-        <v>-2.3528094739859505E-4</v>
+        <v>-4.5942099331200685E-4</v>
       </c>
       <c r="I5">
-        <v>-1.9206545616761637E-4</v>
+        <v>-3.8116678922359344E-4</v>
       </c>
       <c r="J5">
-        <v>-1.298713837701799E-5</v>
+        <v>-2.1122715779278831E-5</v>
       </c>
       <c r="K5">
-        <v>-2.4111324974799089E-4</v>
+        <v>-4.1626364003056641E-4</v>
       </c>
       <c r="L5">
-        <v>2.1696451997941358E-5</v>
+        <v>-1.6731932589809581E-4</v>
       </c>
       <c r="M5">
-        <v>1.6288276873278364E-5</v>
+        <v>-1.4671822199604622E-4</v>
       </c>
       <c r="N5">
-        <v>7.0770515485287649E-7</v>
+        <v>-1.3194073277830384E-4</v>
       </c>
       <c r="O5">
-        <v>-1.7583354672324764E-5</v>
+        <v>1.018260546815598E-4</v>
       </c>
       <c r="P5">
-        <v>1.5836421141088687E-4</v>
+        <v>2.261990491658815E-5</v>
       </c>
       <c r="Q5">
-        <v>9.7494876782615206E-6</v>
+        <v>2.7246971437353657E-5</v>
       </c>
       <c r="R5">
-        <v>1.507976235496088E-5</v>
+        <v>-1.5159431982458718E-4</v>
       </c>
       <c r="S5">
-        <v>-1.0162977222433771E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+        <v>-1.9149992060310678E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6">
-        <v>-1.2268192744023849</v>
+        <v>-1.2614661291375902</v>
       </c>
       <c r="C6">
-        <v>-8.618298961913923E-4</v>
+        <v>-1.4512996463483716E-3</v>
       </c>
       <c r="D6">
-        <v>4.065801368757865E-4</v>
+        <v>7.5626170460459184E-4</v>
       </c>
       <c r="E6">
-        <v>-2.4262437242658887E-6</v>
+        <v>-4.2550467905392369E-6</v>
       </c>
       <c r="F6">
-        <v>8.3572367996208336E-3</v>
+        <v>1.5804055162631447E-2</v>
       </c>
       <c r="G6">
-        <v>1.4410933759596681E-2</v>
+        <v>2.6333470879709116E-2</v>
       </c>
       <c r="H6">
-        <v>-1.9203163089533321E-4</v>
+        <v>-3.8119965875239013E-4</v>
       </c>
       <c r="I6">
-        <v>-3.1903179918418872E-4</v>
+        <v>-6.0726645138737992E-4</v>
       </c>
       <c r="J6">
-        <v>-8.4779959172638636E-5</v>
+        <v>-7.2425291302865278E-5</v>
       </c>
       <c r="K6">
-        <v>-4.1905454747779365E-4</v>
+        <v>-7.7387172355263282E-4</v>
       </c>
       <c r="L6">
-        <v>-6.120116936211194E-5</v>
+        <v>7.5775356124831161E-6</v>
       </c>
       <c r="M6">
-        <v>-5.1742213506744857E-5</v>
+        <v>-2.8891293896540424E-5</v>
       </c>
       <c r="N6">
-        <v>-1.2660479819085E-4</v>
+        <v>8.8640173035376899E-5</v>
       </c>
       <c r="O6">
-        <v>-1.3528493014229289E-4</v>
+        <v>5.9924675432466643E-4</v>
       </c>
       <c r="P6">
-        <v>1.7080230679732741E-4</v>
+        <v>4.8083250615777514E-5</v>
       </c>
       <c r="Q6">
-        <v>2.1691625354276317E-5</v>
+        <v>3.4117099875948561E-5</v>
       </c>
       <c r="R6">
-        <v>1.6255908307942816E-6</v>
+        <v>-1.2723143307259981E-4</v>
       </c>
       <c r="S6">
-        <v>-1.1568635308319237E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+        <v>-2.1826473824669911E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7">
+        <v>4.3171866110735995E-3</v>
+      </c>
+      <c r="C7">
+        <v>8.3722923393496956E-6</v>
+      </c>
+      <c r="D7">
+        <v>-1.4555724641660523E-5</v>
+      </c>
+      <c r="E7">
+        <v>5.5562381026292045E-8</v>
+      </c>
+      <c r="F7">
+        <v>-4.5942099331200685E-4</v>
+      </c>
+      <c r="G7">
+        <v>-3.8119965875239013E-4</v>
+      </c>
+      <c r="H7">
+        <v>1.2173150850574309E-5</v>
+      </c>
+      <c r="I7">
+        <v>1.0124028849058194E-5</v>
+      </c>
+      <c r="J7">
+        <v>1.9580800491922272E-7</v>
+      </c>
+      <c r="K7">
+        <v>1.0763127092899547E-5</v>
+      </c>
+      <c r="L7">
+        <v>6.6139504614660277E-6</v>
+      </c>
+      <c r="M7">
+        <v>6.7060242588601386E-6</v>
+      </c>
+      <c r="N7">
+        <v>9.6904154280227217E-6</v>
+      </c>
+      <c r="O7">
+        <v>7.0115586476318615E-6</v>
+      </c>
+      <c r="P7">
+        <v>-6.1958905351529415E-6</v>
+      </c>
+      <c r="Q7">
+        <v>-6.8687857282256937E-6</v>
+      </c>
+      <c r="R7">
+        <v>3.6507467770342076E-6</v>
+      </c>
+      <c r="S7">
+        <v>4.4527486209823102E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="B7">
-        <v>5.5315069710956902E-3</v>
-      </c>
-      <c r="C7">
-        <v>5.7340070196809313E-6</v>
-      </c>
-      <c r="D7">
-        <v>-7.1150174870425059E-6</v>
-      </c>
-      <c r="E7">
-        <v>2.7654122145124706E-8</v>
-      </c>
-      <c r="F7">
-        <v>-2.3528094739859505E-4</v>
-      </c>
-      <c r="G7">
-        <v>-1.9203163089533321E-4</v>
-      </c>
-      <c r="H7">
-        <v>5.9723461683918969E-6</v>
-      </c>
-      <c r="I7">
-        <v>4.8894121714024867E-6</v>
-      </c>
-      <c r="J7">
-        <v>2.7859396967854857E-7</v>
-      </c>
-      <c r="K7">
-        <v>5.1302032531072965E-6</v>
-      </c>
-      <c r="L7">
-        <v>-1.1249607796274443E-6</v>
-      </c>
-      <c r="M7">
-        <v>1.9134069174227243E-8</v>
-      </c>
-      <c r="N7">
-        <v>7.921699214579012E-7</v>
-      </c>
-      <c r="O7">
-        <v>3.3190772895134801E-6</v>
-      </c>
-      <c r="P7">
-        <v>7.1497102004821592E-7</v>
-      </c>
-      <c r="Q7">
-        <v>-3.5424636710575101E-6</v>
-      </c>
-      <c r="R7">
-        <v>-3.6711430998421278E-6</v>
-      </c>
-      <c r="S7">
-        <v>2.2501784238926158E-4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
       <c r="B8">
-        <v>1.880510970722446E-2</v>
+        <v>1.9562198097878725E-2</v>
       </c>
       <c r="C8">
-        <v>1.7482516347750133E-5</v>
+        <v>2.9654429672909643E-5</v>
       </c>
       <c r="D8">
-        <v>-9.0719197713623329E-6</v>
+        <v>-1.7795484084529296E-5</v>
       </c>
       <c r="E8">
-        <v>4.8105828367059159E-8</v>
+        <v>8.9049953555803996E-8</v>
       </c>
       <c r="F8">
-        <v>-1.9206545616761637E-4</v>
+        <v>-3.8116678922359344E-4</v>
       </c>
       <c r="G8">
-        <v>-3.1903179918418872E-4</v>
+        <v>-6.0726645138737992E-4</v>
       </c>
       <c r="H8">
-        <v>4.8894121714024867E-6</v>
+        <v>1.0124028849058194E-5</v>
       </c>
       <c r="I8">
-        <v>7.8418238307855522E-6</v>
+        <v>1.5459879947701973E-5</v>
       </c>
       <c r="J8">
-        <v>2.3436017059515395E-6</v>
+        <v>1.8361859811968447E-6</v>
       </c>
       <c r="K8">
-        <v>7.6766940772722314E-6</v>
+        <v>1.80393524828615E-5</v>
       </c>
       <c r="L8">
-        <v>1.0684150188437446E-7</v>
+        <v>1.3984421771957129E-6</v>
       </c>
       <c r="M8">
-        <v>2.2979509740297022E-6</v>
+        <v>5.7453329018472359E-6</v>
       </c>
       <c r="N8">
-        <v>6.1440317512110362E-6</v>
+        <v>1.0035382985086984E-5</v>
       </c>
       <c r="O8">
-        <v>1.0465741034986726E-5</v>
+        <v>2.1357349725871369E-6</v>
       </c>
       <c r="P8">
-        <v>5.4013390737438796E-6</v>
+        <v>-8.2279956031614683E-6</v>
       </c>
       <c r="Q8">
-        <v>-4.709201041612274E-6</v>
+        <v>-9.0712384899223721E-6</v>
       </c>
       <c r="R8">
-        <v>-4.6512969062745795E-6</v>
+        <v>3.132332616649057E-6</v>
       </c>
       <c r="S8">
-        <v>2.4986644073418608E-4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+        <v>4.9679490491840719E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>7</v>
       </c>
       <c r="B9">
-        <v>-0.13881505830669394</v>
+        <v>-0.1036741476323092</v>
       </c>
       <c r="C9">
-        <v>-1.5422064400803391E-4</v>
+        <v>-2.124165136014884E-4</v>
       </c>
       <c r="D9">
-        <v>-5.4457863317199559E-5</v>
+        <v>-6.8632436667661234E-5</v>
       </c>
       <c r="E9">
-        <v>5.506980298671625E-7</v>
+        <v>6.2990552620261931E-7</v>
       </c>
       <c r="F9">
-        <v>-1.298713837701799E-5</v>
+        <v>-2.1122715779278831E-5</v>
       </c>
       <c r="G9">
-        <v>-8.4779959172638636E-5</v>
+        <v>-7.2425291302865278E-5</v>
       </c>
       <c r="H9">
-        <v>2.7859396967854857E-7</v>
+        <v>1.9580800491922272E-7</v>
       </c>
       <c r="I9">
-        <v>2.3436017059515395E-6</v>
+        <v>1.8361859811968447E-6</v>
       </c>
       <c r="J9">
-        <v>7.7922669473044119E-4</v>
+        <v>1.4340986067414253E-3</v>
       </c>
       <c r="K9">
-        <v>-1.7914840079398265E-4</v>
+        <v>-5.0351212258405273E-4</v>
       </c>
       <c r="L9">
-        <v>5.8062087242541452E-5</v>
+        <v>-1.1568264221072891E-4</v>
       </c>
       <c r="M9">
-        <v>-3.2664973145506029E-5</v>
+        <v>-2.1723272922572455E-4</v>
       </c>
       <c r="N9">
-        <v>-6.85248830147937E-5</v>
+        <v>-2.8922311639553434E-4</v>
       </c>
       <c r="O9">
-        <v>-8.9107491679634452E-5</v>
+        <v>-2.6913474344141089E-4</v>
       </c>
       <c r="P9">
-        <v>-8.7313218848148095E-5</v>
+        <v>-2.0791106649345782E-5</v>
       </c>
       <c r="Q9">
-        <v>-2.1609458776534895E-5</v>
+        <v>-2.8064252310016522E-5</v>
       </c>
       <c r="R9">
-        <v>-3.1360525251278809E-5</v>
+        <v>-4.6637721693287143E-6</v>
       </c>
       <c r="S9">
-        <v>1.0837667911789025E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+        <v>1.4826908107089434E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10">
+        <v>-0.26873806692978114</v>
+      </c>
+      <c r="C10">
+        <v>-6.9672191409764152E-4</v>
+      </c>
+      <c r="D10">
+        <v>-1.8447619617759933E-4</v>
+      </c>
+      <c r="E10">
+        <v>2.4292947141390848E-6</v>
+      </c>
+      <c r="F10">
+        <v>-4.1626364003056641E-4</v>
+      </c>
+      <c r="G10">
+        <v>-7.7387172355263282E-4</v>
+      </c>
+      <c r="H10">
+        <v>1.0763127092899547E-5</v>
+      </c>
+      <c r="I10">
+        <v>1.80393524828615E-5</v>
+      </c>
+      <c r="J10">
+        <v>-5.0351212258405273E-4</v>
+      </c>
+      <c r="K10">
+        <v>2.0148842272593665E-3</v>
+      </c>
+      <c r="L10">
+        <v>-1.0870878561862831E-4</v>
+      </c>
+      <c r="M10">
+        <v>-2.9693641092092319E-4</v>
+      </c>
+      <c r="N10">
+        <v>-4.8397264972314008E-4</v>
+      </c>
+      <c r="O10">
+        <v>-4.1562994952643495E-4</v>
+      </c>
+      <c r="P10">
+        <v>-2.6073149019375987E-6</v>
+      </c>
+      <c r="Q10">
+        <v>-1.1037927979922312E-5</v>
+      </c>
+      <c r="R10">
+        <v>-5.003655087313272E-5</v>
+      </c>
+      <c r="S10">
+        <v>3.5041959466148389E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
         <v>12</v>
       </c>
-      <c r="B10">
-        <v>-0.2412241755320812</v>
-      </c>
-      <c r="C10">
-        <v>-2.1660382480333438E-4</v>
-      </c>
-      <c r="D10">
-        <v>-5.6163327258087624E-5</v>
-      </c>
-      <c r="E10">
-        <v>7.667893214258164E-7</v>
-      </c>
-      <c r="F10">
-        <v>-2.4111324974799089E-4</v>
-      </c>
-      <c r="G10">
-        <v>-4.1905454747779365E-4</v>
-      </c>
-      <c r="H10">
-        <v>5.1302032531072965E-6</v>
-      </c>
-      <c r="I10">
-        <v>7.6766940772722314E-6</v>
-      </c>
-      <c r="J10">
-        <v>-1.7914840079398265E-4</v>
-      </c>
-      <c r="K10">
-        <v>8.7507342865214533E-4</v>
-      </c>
-      <c r="L10">
-        <v>1.5232563621831331E-4</v>
-      </c>
-      <c r="M10">
-        <v>-2.1845717073919494E-5</v>
-      </c>
-      <c r="N10">
-        <v>-2.2249536738010438E-5</v>
-      </c>
-      <c r="O10">
-        <v>-6.9575524860072285E-5</v>
-      </c>
-      <c r="P10">
-        <v>-4.5323667970161469E-5</v>
-      </c>
-      <c r="Q10">
-        <v>4.0741907935681345E-7</v>
-      </c>
-      <c r="R10">
-        <v>2.7014587009686609E-6</v>
-      </c>
-      <c r="S10">
-        <v>8.3164814967714952E-4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
       <c r="B11">
-        <v>-0.63991923599567013</v>
+        <v>0.51526201552018336</v>
       </c>
       <c r="C11">
-        <v>-2.7982920129024362E-5</v>
+        <v>8.2230338360956309E-5</v>
       </c>
       <c r="D11">
-        <v>-2.7085688584028331E-5</v>
+        <v>3.0708243458747904E-5</v>
       </c>
       <c r="E11">
-        <v>2.9932408531082515E-7</v>
+        <v>-4.6186928442329343E-7</v>
       </c>
       <c r="F11">
-        <v>2.1696451997941358E-5</v>
+        <v>-1.6731932589809581E-4</v>
       </c>
       <c r="G11">
-        <v>-6.120116936211194E-5</v>
+        <v>7.5775356124831161E-6</v>
       </c>
       <c r="H11">
-        <v>-1.1249607796274443E-6</v>
+        <v>6.6139504614660277E-6</v>
       </c>
       <c r="I11">
-        <v>1.0684150188437446E-7</v>
+        <v>1.3984421771957129E-6</v>
       </c>
       <c r="J11">
-        <v>5.8062087242541452E-5</v>
+        <v>-1.1568264221072891E-4</v>
       </c>
       <c r="K11">
-        <v>1.5232563621831331E-4</v>
+        <v>-1.0870878561862831E-4</v>
       </c>
       <c r="L11">
-        <v>2.4471625815538217E-3</v>
+        <v>2.2240099473235908E-2</v>
       </c>
       <c r="M11">
-        <v>3.7421334849808616E-4</v>
+        <v>1.9440841999435087E-2</v>
       </c>
       <c r="N11">
-        <v>1.0267740188079767E-3</v>
+        <v>1.9429765706183218E-2</v>
       </c>
       <c r="O11">
-        <v>1.2518380731282759E-3</v>
+        <v>1.9416275664458693E-2</v>
       </c>
       <c r="P11">
-        <v>1.2361308964315839E-3</v>
+        <v>-4.7039535146227538E-5</v>
       </c>
       <c r="Q11">
-        <v>-6.2838557397981297E-5</v>
+        <v>-9.9998673860044005E-5</v>
       </c>
       <c r="R11">
-        <v>-5.2732662429913151E-5</v>
+        <v>8.9783212908460275E-5</v>
       </c>
       <c r="S11">
-        <v>-7.556680394635104E-4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+        <v>-1.9800603738740499E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12">
-        <v>0.35833596067174045</v>
+        <v>0.94193461576836424</v>
       </c>
       <c r="C12">
-        <v>2.7881217298163295E-5</v>
+        <v>1.1537777637961582E-4</v>
       </c>
       <c r="D12">
-        <v>5.5867431346801727E-6</v>
+        <v>7.9953347160342911E-5</v>
       </c>
       <c r="E12">
-        <v>-8.6369456114027877E-8</v>
+        <v>-1.0434650265746367E-6</v>
       </c>
       <c r="F12">
-        <v>1.6288276873278364E-5</v>
+        <v>-1.4671822199604622E-4</v>
       </c>
       <c r="G12">
-        <v>-5.1742213506744857E-5</v>
+        <v>-2.8891293896540424E-5</v>
       </c>
       <c r="H12">
-        <v>1.9134069174227243E-8</v>
+        <v>6.7060242588601386E-6</v>
       </c>
       <c r="I12">
-        <v>2.2979509740297022E-6</v>
+        <v>5.7453329018472359E-6</v>
       </c>
       <c r="J12">
-        <v>-3.2664973145506029E-5</v>
+        <v>-2.1723272922572455E-4</v>
       </c>
       <c r="K12">
-        <v>-2.1845717073919494E-5</v>
+        <v>-2.9693641092092319E-4</v>
       </c>
       <c r="L12">
-        <v>3.7421334849808616E-4</v>
+        <v>1.9440841999435087E-2</v>
       </c>
       <c r="M12">
-        <v>1.3287880740543313E-2</v>
+        <v>2.0459243142466874E-2</v>
       </c>
       <c r="N12">
-        <v>1.1536195812851568E-2</v>
+        <v>1.9597088476401112E-2</v>
       </c>
       <c r="O12">
-        <v>1.157815238649533E-2</v>
+        <v>1.9606061300908702E-2</v>
       </c>
       <c r="P12">
-        <v>1.1574965932334228E-2</v>
+        <v>-3.0781711528963748E-5</v>
       </c>
       <c r="Q12">
-        <v>-1.5310375462145845E-5</v>
+        <v>-1.2825417463708508E-4</v>
       </c>
       <c r="R12">
-        <v>-6.3753129445594974E-5</v>
+        <v>6.0431038624208776E-6</v>
       </c>
       <c r="S12">
-        <v>-1.1628232750512262E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+        <v>-2.0804139118815713E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>14</v>
       </c>
       <c r="B13">
-        <v>0.66103537168090976</v>
+        <v>1.0568213371373854</v>
       </c>
       <c r="C13">
-        <v>-2.6583405447699014E-6</v>
+        <v>1.4887031993687382E-4</v>
       </c>
       <c r="D13">
-        <v>1.8242208687651923E-5</v>
+        <v>1.1417204932218116E-4</v>
       </c>
       <c r="E13">
-        <v>-2.4279305128169216E-7</v>
+        <v>-1.2424134070337621E-6</v>
       </c>
       <c r="F13">
-        <v>7.0770515485287649E-7</v>
+        <v>-1.3194073277830384E-4</v>
       </c>
       <c r="G13">
-        <v>-1.2660479819085E-4</v>
+        <v>8.8640173035376899E-5</v>
       </c>
       <c r="H13">
-        <v>7.921699214579012E-7</v>
+        <v>9.6904154280227217E-6</v>
       </c>
       <c r="I13">
-        <v>6.1440317512110362E-6</v>
+        <v>1.0035382985086984E-5</v>
       </c>
       <c r="J13">
-        <v>-6.85248830147937E-5</v>
+        <v>-2.8922311639553434E-4</v>
       </c>
       <c r="K13">
-        <v>-2.2249536738010438E-5</v>
+        <v>-4.8397264972314008E-4</v>
       </c>
       <c r="L13">
-        <v>1.0267740188079767E-3</v>
+        <v>1.9429765706183218E-2</v>
       </c>
       <c r="M13">
-        <v>1.1536195812851568E-2</v>
+        <v>1.9597088476401112E-2</v>
       </c>
       <c r="N13">
-        <v>1.2388681306422244E-2</v>
+        <v>2.046866380775586E-2</v>
       </c>
       <c r="O13">
-        <v>1.19806573858416E-2</v>
+        <v>2.0166362279241904E-2</v>
       </c>
       <c r="P13">
-        <v>1.1992200326599901E-2</v>
+        <v>-1.5015507384381313E-5</v>
       </c>
       <c r="Q13">
-        <v>-2.4445917528833239E-5</v>
+        <v>-5.558868058671624E-5</v>
       </c>
       <c r="R13">
-        <v>-7.2779344581963958E-5</v>
+        <v>-1.3632238023688888E-5</v>
       </c>
       <c r="S13">
-        <v>-1.2239139749967936E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+        <v>-2.2218966211180368E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>15</v>
       </c>
       <c r="B14">
-        <v>0.73334028513632865</v>
+        <v>1.0153319711675051</v>
       </c>
       <c r="C14">
-        <v>2.2220239723418729E-6</v>
+        <v>3.9472029225297626E-4</v>
       </c>
       <c r="D14">
-        <v>2.0030135838923209E-5</v>
+        <v>1.6189528805677831E-4</v>
       </c>
       <c r="E14">
-        <v>-1.6075309552336896E-7</v>
+        <v>-1.6183808964829881E-6</v>
       </c>
       <c r="F14">
-        <v>-1.7583354672324764E-5</v>
+        <v>1.018260546815598E-4</v>
       </c>
       <c r="G14">
-        <v>-1.3528493014229289E-4</v>
+        <v>5.9924675432466643E-4</v>
       </c>
       <c r="H14">
-        <v>3.3190772895134801E-6</v>
+        <v>7.0115586476318615E-6</v>
       </c>
       <c r="I14">
-        <v>1.0465741034986726E-5</v>
+        <v>2.1357349725871369E-6</v>
       </c>
       <c r="J14">
-        <v>-8.9107491679634452E-5</v>
+        <v>-2.6913474344141089E-4</v>
       </c>
       <c r="K14">
-        <v>-6.9575524860072285E-5</v>
+        <v>-4.1562994952643495E-4</v>
       </c>
       <c r="L14">
-        <v>1.2518380731282759E-3</v>
+        <v>1.9416275664458693E-2</v>
       </c>
       <c r="M14">
-        <v>1.157815238649533E-2</v>
+        <v>1.9606061300908702E-2</v>
       </c>
       <c r="N14">
-        <v>1.19806573858416E-2</v>
+        <v>2.0166362279241904E-2</v>
       </c>
       <c r="O14">
-        <v>1.2592665662530582E-2</v>
+        <v>2.1793275211654171E-2</v>
       </c>
       <c r="P14">
-        <v>1.2426495348407993E-2</v>
+        <v>1.117564579505403E-5</v>
       </c>
       <c r="Q14">
-        <v>-3.4034425822210561E-5</v>
+        <v>2.8853081443033215E-5</v>
       </c>
       <c r="R14">
-        <v>-4.379591338442301E-5</v>
+        <v>-7.083927765002674E-5</v>
       </c>
       <c r="S14">
-        <v>-1.2832351522161164E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+        <v>-2.4038418509883794E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>16</v>
       </c>
       <c r="B15">
-        <v>0.74749040697873315</v>
+        <v>9.5565275286984913E-2</v>
       </c>
       <c r="C15">
-        <v>1.3371268846366913E-4</v>
+        <v>2.0829329675364631E-5</v>
       </c>
       <c r="D15">
-        <v>6.1489643241535523E-5</v>
+        <v>1.6872595630338986E-5</v>
       </c>
       <c r="E15">
-        <v>-5.1545653324300121E-7</v>
+        <v>-1.2580808571203276E-7</v>
       </c>
       <c r="F15">
-        <v>1.5836421141088687E-4</v>
+        <v>2.261990491658815E-5</v>
       </c>
       <c r="G15">
-        <v>1.7080230679732741E-4</v>
+        <v>4.8083250615777514E-5</v>
       </c>
       <c r="H15">
-        <v>7.1497102004821592E-7</v>
+        <v>-6.1958905351529415E-6</v>
       </c>
       <c r="I15">
-        <v>5.4013390737438796E-6</v>
+        <v>-8.2279956031614683E-6</v>
       </c>
       <c r="J15">
-        <v>-8.7313218848148095E-5</v>
+        <v>-2.0791106649345782E-5</v>
       </c>
       <c r="K15">
-        <v>-4.5323667970161469E-5</v>
+        <v>-2.6073149019375987E-6</v>
       </c>
       <c r="L15">
-        <v>1.2361308964315839E-3</v>
+        <v>-4.7039535146227538E-5</v>
       </c>
       <c r="M15">
-        <v>1.1574965932334228E-2</v>
+        <v>-3.0781711528963748E-5</v>
       </c>
       <c r="N15">
-        <v>1.1992200326599901E-2</v>
+        <v>-1.5015507384381313E-5</v>
       </c>
       <c r="O15">
-        <v>1.2426495348407993E-2</v>
+        <v>1.117564579505403E-5</v>
       </c>
       <c r="P15">
-        <v>1.3424714860227137E-2</v>
+        <v>2.3715190976560255E-3</v>
       </c>
       <c r="Q15">
-        <v>5.2568840600734977E-6</v>
+        <v>1.5756940003654491E-3</v>
       </c>
       <c r="R15">
-        <v>2.4998078284528416E-5</v>
+        <v>1.7192689053129402E-5</v>
       </c>
       <c r="S15">
-        <v>-1.4212013563392474E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+        <v>-1.8008641390792378E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>17</v>
       </c>
       <c r="B16">
-        <v>0.15940654703342902</v>
+        <v>9.9236734235755408E-2</v>
       </c>
       <c r="C16">
-        <v>1.8172697328570783E-5</v>
+        <v>1.6505616544136144E-5</v>
       </c>
       <c r="D16">
-        <v>1.2109694468228494E-5</v>
+        <v>1.5510551216171264E-5</v>
       </c>
       <c r="E16">
-        <v>-1.0073124954324747E-7</v>
+        <v>-6.6606313499838964E-8</v>
       </c>
       <c r="F16">
-        <v>9.7494876782615206E-6</v>
+        <v>2.7246971437353657E-5</v>
       </c>
       <c r="G16">
-        <v>2.1691625354276317E-5</v>
+        <v>3.4117099875948561E-5</v>
       </c>
       <c r="H16">
-        <v>-3.5424636710575101E-6</v>
+        <v>-6.8687857282256937E-6</v>
       </c>
       <c r="I16">
-        <v>-4.709201041612274E-6</v>
+        <v>-9.0712384899223721E-6</v>
       </c>
       <c r="J16">
-        <v>-2.1609458776534895E-5</v>
+        <v>-2.8064252310016522E-5</v>
       </c>
       <c r="K16">
-        <v>4.0741907935681345E-7</v>
+        <v>-1.1037927979922312E-5</v>
       </c>
       <c r="L16">
-        <v>-6.2838557397981297E-5</v>
+        <v>-9.9998673860044005E-5</v>
       </c>
       <c r="M16">
-        <v>-1.5310375462145845E-5</v>
+        <v>-1.2825417463708508E-4</v>
       </c>
       <c r="N16">
-        <v>-2.4445917528833239E-5</v>
+        <v>-5.558868058671624E-5</v>
       </c>
       <c r="O16">
-        <v>-3.4034425822210561E-5</v>
+        <v>2.8853081443033215E-5</v>
       </c>
       <c r="P16">
-        <v>5.2568840600734977E-6</v>
+        <v>1.5756940003654491E-3</v>
       </c>
       <c r="Q16">
-        <v>1.3192681180925591E-3</v>
+        <v>1.9951217122099727E-3</v>
       </c>
       <c r="R16">
-        <v>8.647233454426302E-4</v>
+        <v>3.9088272242092492E-5</v>
       </c>
       <c r="S16">
-        <v>-1.0211244767197791E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+        <v>-1.7813931082080829E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B17">
-        <v>8.8257923214638281E-2</v>
+        <v>1.4770954231726712E-2</v>
       </c>
       <c r="C17">
-        <v>6.4583828968666838E-6</v>
+        <v>-1.8257688265506123E-5</v>
       </c>
       <c r="D17">
-        <v>1.0378124612031819E-5</v>
+        <v>8.7026706933264609E-6</v>
       </c>
       <c r="E17">
-        <v>-5.0205343678327296E-8</v>
+        <v>-1.9557442724789961E-7</v>
       </c>
       <c r="F17">
-        <v>1.507976235496088E-5</v>
+        <v>-1.5159431982458718E-4</v>
       </c>
       <c r="G17">
-        <v>1.6255908307942816E-6</v>
+        <v>-1.2723143307259981E-4</v>
       </c>
       <c r="H17">
-        <v>-3.6711430998421278E-6</v>
+        <v>3.6507467770342076E-6</v>
       </c>
       <c r="I17">
-        <v>-4.6512969062745795E-6</v>
+        <v>3.132332616649057E-6</v>
       </c>
       <c r="J17">
-        <v>-3.1360525251278809E-5</v>
+        <v>-4.6637721693287143E-6</v>
       </c>
       <c r="K17">
-        <v>2.7014587009686609E-6</v>
+        <v>-5.003655087313272E-5</v>
       </c>
       <c r="L17">
-        <v>-5.2732662429913151E-5</v>
+        <v>8.9783212908460275E-5</v>
       </c>
       <c r="M17">
-        <v>-6.3753129445594974E-5</v>
+        <v>6.0431038624208776E-6</v>
       </c>
       <c r="N17">
-        <v>-7.2779344581963958E-5</v>
+        <v>-1.3632238023688888E-5</v>
       </c>
       <c r="O17">
-        <v>-4.379591338442301E-5</v>
+        <v>-7.083927765002674E-5</v>
       </c>
       <c r="P17">
-        <v>2.4998078284528416E-5</v>
+        <v>1.7192689053129402E-5</v>
       </c>
       <c r="Q17">
-        <v>8.647233454426302E-4</v>
+        <v>3.9088272242092492E-5</v>
       </c>
       <c r="R17">
-        <v>1.1237109721803648E-3</v>
+        <v>5.7291463757693133E-3</v>
       </c>
       <c r="S17">
-        <v>-1.0157073105362567E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+        <v>-2.1665954055174222E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>3</v>
       </c>
       <c r="B18">
-        <v>-4.6982600055626547</v>
+        <v>-5.4852866215125795</v>
       </c>
       <c r="C18">
-        <v>2.5610463806704422E-3</v>
+        <v>3.8863158939922331E-3</v>
       </c>
       <c r="D18">
-        <v>-1.453612767902595E-3</v>
+        <v>-2.8581571301533183E-3</v>
       </c>
       <c r="E18">
-        <v>1.3935226290111964E-5</v>
+        <v>2.818157147405309E-5</v>
       </c>
       <c r="F18">
-        <v>-1.0162977222433771E-2</v>
+        <v>-1.9149992060310678E-2</v>
       </c>
       <c r="G18">
-        <v>-1.1568635308319237E-2</v>
+        <v>-2.1826473824669911E-2</v>
       </c>
       <c r="H18">
-        <v>2.2501784238926158E-4</v>
+        <v>4.4527486209823102E-4</v>
       </c>
       <c r="I18">
-        <v>2.4986644073418608E-4</v>
+        <v>4.9679490491840719E-4</v>
       </c>
       <c r="J18">
-        <v>1.0837667911789025E-3</v>
+        <v>1.4826908107089434E-3</v>
       </c>
       <c r="K18">
-        <v>8.3164814967714952E-4</v>
+        <v>3.5041959466148389E-3</v>
       </c>
       <c r="L18">
-        <v>-7.556680394635104E-4</v>
+        <v>-1.9800603738740499E-2</v>
       </c>
       <c r="M18">
-        <v>-1.1628232750512262E-2</v>
+        <v>-2.0804139118815713E-2</v>
       </c>
       <c r="N18">
-        <v>-1.2239139749967936E-2</v>
+        <v>-2.2218966211180368E-2</v>
       </c>
       <c r="O18">
-        <v>-1.2832351522161164E-2</v>
+        <v>-2.4038418509883794E-2</v>
       </c>
       <c r="P18">
-        <v>-1.4212013563392474E-2</v>
+        <v>-1.8008641390792378E-3</v>
       </c>
       <c r="Q18">
-        <v>-1.0211244767197791E-3</v>
+        <v>-1.7813931082080829E-3</v>
       </c>
       <c r="R18">
-        <v>-1.0157073105362567E-3</v>
+        <v>-2.1665954055174222E-4</v>
       </c>
       <c r="S18">
-        <v>4.483126183110657E-2</v>
+        <v>8.3179540179307163E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1665,18 +1671,18 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EF7C3FD-31A1-4DD9-B07D-B9FF738D5357}">
   <dimension ref="A1:S18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" style="2" customWidth="1"/>
-    <col min="2" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="26.73046875" style="2" customWidth="1"/>
+    <col min="2" max="16384" width="9.1328125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
         <v>19</v>
-      </c>
-      <c r="B1" t="s">
-        <v>20</v>
       </c>
       <c r="C1" t="s">
         <v>6</v>
@@ -1694,1043 +1700,1043 @@
         <v>4</v>
       </c>
       <c r="H1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="M1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="P1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="Q1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="R1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="S1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2">
-        <v>0.78651694127358063</v>
+        <v>0.58920717407334799</v>
       </c>
       <c r="C2">
-        <v>1.9871502356149967E-3</v>
+        <v>3.4554667245972953E-3</v>
       </c>
       <c r="D2">
-        <v>-1.8984959488827706E-4</v>
+        <v>-3.4497586303510602E-4</v>
       </c>
       <c r="E2">
-        <v>1.8381349275415541E-6</v>
+        <v>3.3103443949837748E-6</v>
       </c>
       <c r="F2">
-        <v>-4.1732333593434186E-4</v>
+        <v>-8.6696256858092636E-4</v>
       </c>
       <c r="G2">
-        <v>-1.1829194370494727E-3</v>
+        <v>-2.4339541924386322E-3</v>
       </c>
       <c r="H2">
-        <v>7.7678803938668926E-6</v>
+        <v>1.580409984229596E-5</v>
       </c>
       <c r="I2">
-        <v>2.2879791410711083E-5</v>
+        <v>4.6970753942673727E-5</v>
       </c>
       <c r="J2">
-        <v>-5.6156941773235713E-5</v>
+        <v>-6.3640268953030834E-5</v>
       </c>
       <c r="K2">
-        <v>-4.0645061569740694E-5</v>
+        <v>-8.8908668162932246E-5</v>
       </c>
       <c r="L2">
-        <v>-3.235385062300051E-6</v>
+        <v>-5.5347424056183476E-5</v>
       </c>
       <c r="M2">
-        <v>-3.0592093046973847E-5</v>
+        <v>-8.790347570995392E-5</v>
       </c>
       <c r="N2">
-        <v>-3.4494389078431188E-5</v>
+        <v>-8.1459794787850422E-5</v>
       </c>
       <c r="O2">
-        <v>-3.7246523469036024E-5</v>
+        <v>1.7917037446905037E-4</v>
       </c>
       <c r="P2">
-        <v>1.0466685181951456E-4</v>
+        <v>-2.5954618541466679E-5</v>
       </c>
       <c r="Q2">
-        <v>-9.8925078877475168E-6</v>
+        <v>-8.7268047760245105E-5</v>
       </c>
       <c r="R2">
-        <v>-5.7450784840138572E-5</v>
+        <v>4.1284008183856723E-5</v>
       </c>
       <c r="S2">
-        <v>2.8732604107089572E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+        <v>5.4693867182005152E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3">
-        <v>0.11050111191664029</v>
+        <v>0.12713450499959258</v>
       </c>
       <c r="C3">
-        <v>-1.8984959488827706E-4</v>
+        <v>-3.4497586303510602E-4</v>
       </c>
       <c r="D3">
-        <v>7.6120057654467893E-5</v>
+        <v>1.5264248534080358E-4</v>
       </c>
       <c r="E3">
-        <v>-7.4790522849004062E-7</v>
+        <v>-1.543283441513817E-6</v>
       </c>
       <c r="F3">
-        <v>4.5268908064271645E-4</v>
+        <v>8.3678408455719992E-4</v>
       </c>
       <c r="G3">
-        <v>6.2836260499550491E-4</v>
+        <v>1.1644721797663855E-3</v>
       </c>
       <c r="H3">
-        <v>-1.0128206157431875E-5</v>
+        <v>-1.8933467604934594E-5</v>
       </c>
       <c r="I3">
-        <v>-1.4135376604364091E-5</v>
+        <v>-2.6407402494605685E-5</v>
       </c>
       <c r="J3">
-        <v>-6.1704692260177598E-5</v>
+        <v>-2.272363066802411E-5</v>
       </c>
       <c r="K3">
-        <v>-1.6601158361121101E-5</v>
+        <v>-2.0529558126984923E-4</v>
       </c>
       <c r="L3">
-        <v>-2.0504915454596157E-5</v>
+        <v>3.9233787976600157E-5</v>
       </c>
       <c r="M3">
-        <v>1.6684451655575832E-5</v>
+        <v>7.2140821891220823E-5</v>
       </c>
       <c r="N3">
-        <v>1.8341214156424913E-5</v>
+        <v>9.7820500987985236E-5</v>
       </c>
       <c r="O3">
-        <v>6.8934652799555176E-6</v>
+        <v>1.6745227351270403E-4</v>
       </c>
       <c r="P3">
-        <v>4.805207038577721E-5</v>
+        <v>4.1854861536380508E-5</v>
       </c>
       <c r="Q3">
-        <v>1.9070326766160424E-5</v>
+        <v>5.3839338159356383E-5</v>
       </c>
       <c r="R3">
-        <v>2.9664775078279023E-5</v>
+        <v>1.6539420053300593E-5</v>
       </c>
       <c r="S3">
-        <v>-1.582587139979215E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+        <v>-3.183080906889854E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>1</v>
       </c>
       <c r="B4">
-        <v>-1.6388600226071152E-3</v>
+        <v>-1.9212646490404134E-3</v>
       </c>
       <c r="C4">
-        <v>1.8381349275415541E-6</v>
+        <v>3.3103443949837748E-6</v>
       </c>
       <c r="D4">
-        <v>-7.4790522849004062E-7</v>
+        <v>-1.543283441513817E-6</v>
       </c>
       <c r="E4">
-        <v>8.2433999308988585E-9</v>
+        <v>1.7418377549785861E-8</v>
       </c>
       <c r="F4">
-        <v>-1.8284344213471886E-6</v>
+        <v>-3.537903295158924E-6</v>
       </c>
       <c r="G4">
-        <v>-3.617242632111223E-6</v>
+        <v>-6.8016901832557151E-6</v>
       </c>
       <c r="H4">
-        <v>3.5276661285991854E-8</v>
+        <v>6.6890131375377352E-8</v>
       </c>
       <c r="I4">
-        <v>7.677683740150323E-8</v>
+        <v>1.4304178108887042E-7</v>
       </c>
       <c r="J4">
-        <v>3.9132163105535278E-7</v>
+        <v>-4.8853756536914687E-7</v>
       </c>
       <c r="K4">
-        <v>3.0903382924757039E-7</v>
+        <v>2.7774383380096894E-6</v>
       </c>
       <c r="L4">
-        <v>2.1865171903521392E-7</v>
+        <v>-4.9917399270534627E-7</v>
       </c>
       <c r="M4">
-        <v>-2.0883358472509904E-7</v>
+        <v>-9.1101449031392744E-7</v>
       </c>
       <c r="N4">
-        <v>-2.6079051259154621E-7</v>
+        <v>-9.5945190228323437E-7</v>
       </c>
       <c r="O4">
-        <v>-4.4003254204761819E-9</v>
+        <v>-1.5659379052626398E-6</v>
       </c>
       <c r="P4">
-        <v>-3.5777106320020804E-7</v>
+        <v>-3.5509792192123915E-7</v>
       </c>
       <c r="Q4">
-        <v>-1.7568652577762842E-7</v>
+        <v>-4.5001561948948472E-7</v>
       </c>
       <c r="R4">
-        <v>-2.6597584017351772E-7</v>
+        <v>-2.8639602325529266E-7</v>
       </c>
       <c r="S4">
-        <v>1.3877078640669314E-5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+        <v>2.9177633485087495E-5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>2</v>
       </c>
       <c r="B5">
-        <v>-0.39676675352207996</v>
+        <v>-0.59401316453401576</v>
       </c>
       <c r="C5">
-        <v>-4.1732333593434186E-4</v>
+        <v>-8.6696256858092636E-4</v>
       </c>
       <c r="D5">
-        <v>4.5268908064271645E-4</v>
+        <v>8.3678408455719992E-4</v>
       </c>
       <c r="E5">
-        <v>-1.8284344213471886E-6</v>
+        <v>-3.537903295158924E-6</v>
       </c>
       <c r="F5">
-        <v>1.5563001888876469E-2</v>
+        <v>2.6780710613128568E-2</v>
       </c>
       <c r="G5">
-        <v>1.4109110497581016E-2</v>
+        <v>2.4453052878964807E-2</v>
       </c>
       <c r="H5">
-        <v>-3.3952593832661283E-4</v>
+        <v>-5.975628130608045E-4</v>
       </c>
       <c r="I5">
-        <v>-3.0760228183749526E-4</v>
+        <v>-5.4572058351625894E-4</v>
       </c>
       <c r="J5">
-        <v>-5.4272605048703046E-5</v>
+        <v>-2.5057171186941508E-4</v>
       </c>
       <c r="K5">
-        <v>-2.5715082754736293E-4</v>
+        <v>-3.8577490739989597E-4</v>
       </c>
       <c r="L5">
-        <v>2.716144929637809E-5</v>
+        <v>6.5410378533488529E-5</v>
       </c>
       <c r="M5">
-        <v>5.753408509872552E-5</v>
+        <v>-3.3008112238022864E-5</v>
       </c>
       <c r="N5">
-        <v>-4.0215247695098502E-6</v>
+        <v>-4.0528617447302233E-5</v>
       </c>
       <c r="O5">
-        <v>-1.0208832234492263E-4</v>
+        <v>1.3758549148622321E-4</v>
       </c>
       <c r="P5">
-        <v>-4.985805160543505E-5</v>
+        <v>2.4431651570773374E-4</v>
       </c>
       <c r="Q5">
-        <v>4.6658856854230079E-5</v>
+        <v>1.7456310998894891E-4</v>
       </c>
       <c r="R5">
-        <v>1.960600936334948E-5</v>
+        <v>-1.0864708922261266E-4</v>
       </c>
       <c r="S5">
-        <v>-1.6058940981721122E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+        <v>-2.8857939410375726E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6">
-        <v>-1.2793456943052504</v>
+        <v>-1.5116706097341968</v>
       </c>
       <c r="C6">
-        <v>-1.1829194370494727E-3</v>
+        <v>-2.4339541924386322E-3</v>
       </c>
       <c r="D6">
-        <v>6.2836260499550491E-4</v>
+        <v>1.1644721797663855E-3</v>
       </c>
       <c r="E6">
-        <v>-3.617242632111223E-6</v>
+        <v>-6.8016901832557151E-6</v>
       </c>
       <c r="F6">
-        <v>1.4109110497581016E-2</v>
+        <v>2.4453052878964807E-2</v>
       </c>
       <c r="G6">
-        <v>1.9933248529728817E-2</v>
+        <v>3.4369957859306244E-2</v>
       </c>
       <c r="H6">
-        <v>-3.0589999799002162E-4</v>
+        <v>-5.4184395822136269E-4</v>
       </c>
       <c r="I6">
-        <v>-4.3931189078675351E-4</v>
+        <v>-7.684534578220421E-4</v>
       </c>
       <c r="J6">
-        <v>-3.2893456010682086E-4</v>
+        <v>-7.9160184618635217E-4</v>
       </c>
       <c r="K6">
-        <v>-4.0496232757704451E-4</v>
+        <v>-6.7788584306874853E-4</v>
       </c>
       <c r="L6">
-        <v>-7.691120796404885E-5</v>
+        <v>2.6436453653944612E-4</v>
       </c>
       <c r="M6">
-        <v>5.2522265848652279E-5</v>
+        <v>9.7428880193300288E-5</v>
       </c>
       <c r="N6">
-        <v>-1.2997345483830528E-4</v>
+        <v>1.6439897089178413E-4</v>
       </c>
       <c r="O6">
-        <v>-1.8918886781289172E-4</v>
+        <v>7.0479835265462119E-4</v>
       </c>
       <c r="P6">
-        <v>5.6029012934952563E-5</v>
+        <v>1.0685245017961423E-4</v>
       </c>
       <c r="Q6">
-        <v>5.6004962950312494E-7</v>
+        <v>1.9126627767442246E-4</v>
       </c>
       <c r="R6">
-        <v>3.7667157218110509E-5</v>
+        <v>-3.581656785742148E-4</v>
       </c>
       <c r="S6">
-        <v>-1.9112075662264354E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+        <v>-3.4952833852940332E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B7">
-        <v>9.1788697462190771E-3</v>
+        <v>1.1902386801056632E-2</v>
       </c>
       <c r="C7">
-        <v>7.7678803938668926E-6</v>
+        <v>1.580409984229596E-5</v>
       </c>
       <c r="D7">
-        <v>-1.0128206157431875E-5</v>
+        <v>-1.8933467604934594E-5</v>
       </c>
       <c r="E7">
-        <v>3.5276661285991854E-8</v>
+        <v>6.6890131375377352E-8</v>
       </c>
       <c r="F7">
-        <v>-3.3952593832661283E-4</v>
+        <v>-5.975628130608045E-4</v>
       </c>
       <c r="G7">
-        <v>-3.0589999799002162E-4</v>
+        <v>-5.4184395822136269E-4</v>
       </c>
       <c r="H7">
-        <v>8.2706693934031823E-6</v>
+        <v>1.509200858938443E-5</v>
       </c>
       <c r="I7">
-        <v>7.4110477114606621E-6</v>
+        <v>1.3602903547126499E-5</v>
       </c>
       <c r="J7">
-        <v>1.7125576771912016E-6</v>
+        <v>5.5385254157713488E-6</v>
       </c>
       <c r="K7">
-        <v>5.2412985676670381E-6</v>
+        <v>1.028656846166545E-5</v>
       </c>
       <c r="L7">
-        <v>-2.4479911712053644E-6</v>
+        <v>2.7309252025789607E-7</v>
       </c>
       <c r="M7">
-        <v>-8.2457396797502706E-7</v>
+        <v>4.7166906834540472E-6</v>
       </c>
       <c r="N7">
-        <v>1.4509223874756386E-6</v>
+        <v>1.2408797643141716E-5</v>
       </c>
       <c r="O7">
-        <v>6.8126254031787635E-6</v>
+        <v>1.0787351170225769E-5</v>
       </c>
       <c r="P7">
-        <v>6.4704211268023999E-6</v>
+        <v>-1.4410739896764954E-5</v>
       </c>
       <c r="Q7">
-        <v>-5.7605405544250086E-6</v>
+        <v>-1.3514287682561773E-5</v>
       </c>
       <c r="R7">
-        <v>-5.1900659535332845E-6</v>
+        <v>3.0027204782498891E-6</v>
       </c>
       <c r="S7">
-        <v>3.4109955905497482E-4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+        <v>6.1812948909766247E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8">
-        <v>2.4448128924624182E-2</v>
+        <v>2.8858468352392159E-2</v>
       </c>
       <c r="C8">
-        <v>2.2879791410711083E-5</v>
+        <v>4.6970753942673727E-5</v>
       </c>
       <c r="D8">
-        <v>-1.4135376604364091E-5</v>
+        <v>-2.6407402494605685E-5</v>
       </c>
       <c r="E8">
-        <v>7.677683740150323E-8</v>
+        <v>1.4304178108887042E-7</v>
       </c>
       <c r="F8">
-        <v>-3.0760228183749526E-4</v>
+        <v>-5.4572058351625894E-4</v>
       </c>
       <c r="G8">
-        <v>-4.3931189078675351E-4</v>
+        <v>-7.684534578220421E-4</v>
       </c>
       <c r="H8">
-        <v>7.4110477114606621E-6</v>
+        <v>1.3602903547126499E-5</v>
       </c>
       <c r="I8">
-        <v>1.0870203084830044E-5</v>
+        <v>1.9384085296086538E-5</v>
       </c>
       <c r="J8">
-        <v>8.6281214834885751E-6</v>
+        <v>1.8482494956095857E-5</v>
       </c>
       <c r="K8">
-        <v>6.040665020627644E-6</v>
+        <v>1.1788719533721538E-5</v>
       </c>
       <c r="L8">
-        <v>3.4326749522655939E-8</v>
+        <v>-4.0112590497622992E-6</v>
       </c>
       <c r="M8">
-        <v>-1.2762624988045188E-7</v>
+        <v>4.621645565726102E-6</v>
       </c>
       <c r="N8">
-        <v>7.0929073225948971E-6</v>
+        <v>1.2493873332751146E-5</v>
       </c>
       <c r="O8">
-        <v>1.3577200636811658E-5</v>
+        <v>4.0091523130991399E-6</v>
       </c>
       <c r="P8">
-        <v>9.6197978446312539E-6</v>
+        <v>-1.3552648385926027E-5</v>
       </c>
       <c r="Q8">
-        <v>-5.3198972962569178E-6</v>
+        <v>-1.5921918718951811E-5</v>
       </c>
       <c r="R8">
-        <v>-6.6889474738087896E-6</v>
+        <v>6.9254514953309459E-6</v>
       </c>
       <c r="S8">
-        <v>4.076453765696343E-4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+        <v>7.5483573927942634E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B9">
-        <v>0.15452932839870515</v>
+        <v>0.14080678972193889</v>
       </c>
       <c r="C9">
-        <v>-5.6156941773235713E-5</v>
+        <v>-6.3640268953030834E-5</v>
       </c>
       <c r="D9">
-        <v>-6.1704692260177598E-5</v>
+        <v>-2.272363066802411E-5</v>
       </c>
       <c r="E9">
-        <v>3.9132163105535278E-7</v>
+        <v>-4.8853756536914687E-7</v>
       </c>
       <c r="F9">
-        <v>-5.4272605048703046E-5</v>
+        <v>-2.5057171186941508E-4</v>
       </c>
       <c r="G9">
-        <v>-3.2893456010682086E-4</v>
+        <v>-7.9160184618635217E-4</v>
       </c>
       <c r="H9">
-        <v>1.7125576771912016E-6</v>
+        <v>5.5385254157713488E-6</v>
       </c>
       <c r="I9">
-        <v>8.6281214834885751E-6</v>
+        <v>1.8482494956095857E-5</v>
       </c>
       <c r="J9">
-        <v>1.2334814831781559E-3</v>
+        <v>2.8657711945956977E-3</v>
       </c>
       <c r="K9">
-        <v>-4.0613065021202158E-4</v>
+        <v>-1.759192990183722E-3</v>
       </c>
       <c r="L9">
-        <v>7.9986068685385399E-5</v>
+        <v>-4.5445682625412708E-5</v>
       </c>
       <c r="M9">
-        <v>-2.4240115504341902E-5</v>
+        <v>-1.4100272939955699E-4</v>
       </c>
       <c r="N9">
-        <v>-3.3403319690278853E-5</v>
+        <v>-2.0082163148422554E-4</v>
       </c>
       <c r="O9">
-        <v>-5.2628238469907814E-5</v>
+        <v>-1.8184685124191929E-4</v>
       </c>
       <c r="P9">
-        <v>-7.8373299717757845E-5</v>
+        <v>-2.061952706123057E-6</v>
       </c>
       <c r="Q9">
-        <v>6.3176215659144886E-6</v>
+        <v>-5.1854676594704771E-5</v>
       </c>
       <c r="R9">
-        <v>-3.2568270055214753E-5</v>
+        <v>7.1923405901732265E-5</v>
       </c>
       <c r="S9">
-        <v>1.4072066216154161E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+        <v>1.0809788466888258E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10">
-        <v>1.729121951725948E-3</v>
+        <v>6.6909517123602727E-2</v>
       </c>
       <c r="C10">
-        <v>-4.0645061569740694E-5</v>
+        <v>-8.8908668162932246E-5</v>
       </c>
       <c r="D10">
-        <v>-1.6601158361121101E-5</v>
+        <v>-2.0529558126984923E-4</v>
       </c>
       <c r="E10">
-        <v>3.0903382924757039E-7</v>
+        <v>2.7774383380096894E-6</v>
       </c>
       <c r="F10">
-        <v>-2.5715082754736293E-4</v>
+        <v>-3.8577490739989597E-4</v>
       </c>
       <c r="G10">
-        <v>-4.0496232757704451E-4</v>
+        <v>-6.7788584306874853E-4</v>
       </c>
       <c r="H10">
-        <v>5.2412985676670381E-6</v>
+        <v>1.028656846166545E-5</v>
       </c>
       <c r="I10">
-        <v>6.040665020627644E-6</v>
+        <v>1.1788719533721538E-5</v>
       </c>
       <c r="J10">
-        <v>-4.0613065021202158E-4</v>
+        <v>-1.759192990183722E-3</v>
       </c>
       <c r="K10">
-        <v>9.1702508194259379E-4</v>
+        <v>3.4635018352733716E-3</v>
       </c>
       <c r="L10">
-        <v>3.7626288546167796E-5</v>
+        <v>-2.6149141745599683E-5</v>
       </c>
       <c r="M10">
-        <v>2.4086125331495724E-5</v>
+        <v>-9.9929573926994916E-5</v>
       </c>
       <c r="N10">
-        <v>-4.2917578323717836E-6</v>
+        <v>-2.0096800746628805E-4</v>
       </c>
       <c r="O10">
-        <v>-3.6131229186836667E-5</v>
+        <v>-1.9571446909699664E-4</v>
       </c>
       <c r="P10">
-        <v>-7.1172205508027183E-6</v>
+        <v>-1.5286505074062247E-5</v>
       </c>
       <c r="Q10">
-        <v>-8.2883657565052433E-6</v>
+        <v>-1.0225393353802788E-4</v>
       </c>
       <c r="R10">
-        <v>-4.3017240761036946E-5</v>
+        <v>4.2052567295545172E-6</v>
       </c>
       <c r="S10">
-        <v>1.1989401991599705E-4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+        <v>3.6023939084818576E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B11">
-        <v>-0.91020048934948339</v>
+        <v>0.2952514973473071</v>
       </c>
       <c r="C11">
-        <v>-3.235385062300051E-6</v>
+        <v>-5.5347424056183476E-5</v>
       </c>
       <c r="D11">
-        <v>-2.0504915454596157E-5</v>
+        <v>3.9233787976600157E-5</v>
       </c>
       <c r="E11">
-        <v>2.1865171903521392E-7</v>
+        <v>-4.9917399270534627E-7</v>
       </c>
       <c r="F11">
-        <v>2.716144929637809E-5</v>
+        <v>6.5410378533488529E-5</v>
       </c>
       <c r="G11">
-        <v>-7.691120796404885E-5</v>
+        <v>2.6436453653944612E-4</v>
       </c>
       <c r="H11">
-        <v>-2.4479911712053644E-6</v>
+        <v>2.7309252025789607E-7</v>
       </c>
       <c r="I11">
-        <v>3.4326749522655939E-8</v>
+        <v>-4.0112590497622992E-6</v>
       </c>
       <c r="J11">
-        <v>7.9986068685385399E-5</v>
+        <v>-4.5445682625412708E-5</v>
       </c>
       <c r="K11">
-        <v>3.7626288546167796E-5</v>
+        <v>-2.6149141745599683E-5</v>
       </c>
       <c r="L11">
-        <v>2.835876209480752E-3</v>
+        <v>2.0959685223279043E-2</v>
       </c>
       <c r="M11">
-        <v>8.4984053727399047E-5</v>
+        <v>1.7359018136741435E-2</v>
       </c>
       <c r="N11">
-        <v>9.0893219990358391E-4</v>
+        <v>1.7312634987172934E-2</v>
       </c>
       <c r="O11">
-        <v>1.2185332801927385E-3</v>
+        <v>1.7293689290262426E-2</v>
       </c>
       <c r="P11">
-        <v>1.2095779869325156E-3</v>
+        <v>7.1018514009501307E-5</v>
       </c>
       <c r="Q11">
-        <v>-5.6897367177495081E-5</v>
+        <v>-5.3936328870933937E-5</v>
       </c>
       <c r="R11">
-        <v>-7.9582875953180621E-5</v>
+        <v>2.2930781021454307E-4</v>
       </c>
       <c r="S11">
-        <v>-7.7823907841851508E-4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+        <v>-1.7987202798699815E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B12">
-        <v>0.3923890316888044</v>
+        <v>0.98778472233998482</v>
       </c>
       <c r="C12">
-        <v>-3.0592093046973847E-5</v>
+        <v>-8.790347570995392E-5</v>
       </c>
       <c r="D12">
-        <v>1.6684451655575832E-5</v>
+        <v>7.2140821891220823E-5</v>
       </c>
       <c r="E12">
-        <v>-2.0883358472509904E-7</v>
+        <v>-9.1101449031392744E-7</v>
       </c>
       <c r="F12">
-        <v>5.753408509872552E-5</v>
+        <v>-3.3008112238022864E-5</v>
       </c>
       <c r="G12">
-        <v>5.2522265848652279E-5</v>
+        <v>9.7428880193300288E-5</v>
       </c>
       <c r="H12">
-        <v>-8.2457396797502706E-7</v>
+        <v>4.7166906834540472E-6</v>
       </c>
       <c r="I12">
-        <v>-1.2762624988045188E-7</v>
+        <v>4.621645565726102E-6</v>
       </c>
       <c r="J12">
-        <v>-2.4240115504341902E-5</v>
+        <v>-1.4100272939955699E-4</v>
       </c>
       <c r="K12">
-        <v>2.4086125331495724E-5</v>
+        <v>-9.9929573926994916E-5</v>
       </c>
       <c r="L12">
-        <v>8.4984053727399047E-5</v>
+        <v>1.7359018136741435E-2</v>
       </c>
       <c r="M12">
-        <v>1.6054896822642516E-2</v>
+        <v>1.8582738645423147E-2</v>
       </c>
       <c r="N12">
-        <v>1.3848166675760602E-2</v>
+        <v>1.7405247200850283E-2</v>
       </c>
       <c r="O12">
-        <v>1.3827182251372552E-2</v>
+        <v>1.7419459165215846E-2</v>
       </c>
       <c r="P12">
-        <v>1.3815916427760748E-2</v>
+        <v>8.9645711805002269E-5</v>
       </c>
       <c r="Q12">
-        <v>-1.824099509547877E-5</v>
+        <v>1.7678683831553804E-6</v>
       </c>
       <c r="R12">
-        <v>-8.1705215180906843E-5</v>
+        <v>3.1579345404245866E-4</v>
       </c>
       <c r="S12">
-        <v>-1.4071958731727296E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+        <v>-1.8679743762675484E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B13">
-        <v>0.74379923165852668</v>
+        <v>1.2942333522779608</v>
       </c>
       <c r="C13">
-        <v>-3.4494389078431188E-5</v>
+        <v>-8.1459794787850422E-5</v>
       </c>
       <c r="D13">
-        <v>1.8341214156424913E-5</v>
+        <v>9.7820500987985236E-5</v>
       </c>
       <c r="E13">
-        <v>-2.6079051259154621E-7</v>
+        <v>-9.5945190228323437E-7</v>
       </c>
       <c r="F13">
-        <v>-4.0215247695098502E-6</v>
+        <v>-4.0528617447302233E-5</v>
       </c>
       <c r="G13">
-        <v>-1.2997345483830528E-4</v>
+        <v>1.6439897089178413E-4</v>
       </c>
       <c r="H13">
-        <v>1.4509223874756386E-6</v>
+        <v>1.2408797643141716E-5</v>
       </c>
       <c r="I13">
-        <v>7.0929073225948971E-6</v>
+        <v>1.2493873332751146E-5</v>
       </c>
       <c r="J13">
-        <v>-3.3403319690278853E-5</v>
+        <v>-2.0082163148422554E-4</v>
       </c>
       <c r="K13">
-        <v>-4.2917578323717836E-6</v>
+        <v>-2.0096800746628805E-4</v>
       </c>
       <c r="L13">
-        <v>9.0893219990358391E-4</v>
+        <v>1.7312634987172934E-2</v>
       </c>
       <c r="M13">
-        <v>1.3848166675760602E-2</v>
+        <v>1.7405247200850283E-2</v>
       </c>
       <c r="N13">
-        <v>1.4862563954224514E-2</v>
+        <v>1.8473283636919323E-2</v>
       </c>
       <c r="O13">
-        <v>1.4231387600922166E-2</v>
+        <v>1.8106745013871078E-2</v>
       </c>
       <c r="P13">
-        <v>1.4235847108544983E-2</v>
+        <v>1.1130571888789509E-4</v>
       </c>
       <c r="Q13">
-        <v>-3.6439431865515064E-5</v>
+        <v>3.0607835015725713E-5</v>
       </c>
       <c r="R13">
-        <v>-8.4444305399556426E-5</v>
+        <v>3.0783883234234701E-4</v>
       </c>
       <c r="S13">
-        <v>-1.4475746378943092E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+        <v>-2.0172344905685487E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B14">
-        <v>0.92726474772914158</v>
+        <v>1.247901489129686</v>
       </c>
       <c r="C14">
-        <v>-3.7246523469036024E-5</v>
+        <v>1.7917037446905037E-4</v>
       </c>
       <c r="D14">
-        <v>6.8934652799555176E-6</v>
+        <v>1.6745227351270403E-4</v>
       </c>
       <c r="E14">
-        <v>-4.4003254204761819E-9</v>
+        <v>-1.5659379052626398E-6</v>
       </c>
       <c r="F14">
-        <v>-1.0208832234492263E-4</v>
+        <v>1.3758549148622321E-4</v>
       </c>
       <c r="G14">
-        <v>-1.8918886781289172E-4</v>
+        <v>7.0479835265462119E-4</v>
       </c>
       <c r="H14">
-        <v>6.8126254031787635E-6</v>
+        <v>1.0787351170225769E-5</v>
       </c>
       <c r="I14">
-        <v>1.3577200636811658E-5</v>
+        <v>4.0091523130991399E-6</v>
       </c>
       <c r="J14">
-        <v>-5.2628238469907814E-5</v>
+        <v>-1.8184685124191929E-4</v>
       </c>
       <c r="K14">
-        <v>-3.6131229186836667E-5</v>
+        <v>-1.9571446909699664E-4</v>
       </c>
       <c r="L14">
-        <v>1.2185332801927385E-3</v>
+        <v>1.7293689290262426E-2</v>
       </c>
       <c r="M14">
-        <v>1.3827182251372552E-2</v>
+        <v>1.7419459165215846E-2</v>
       </c>
       <c r="N14">
-        <v>1.4231387600922166E-2</v>
+        <v>1.8106745013871078E-2</v>
       </c>
       <c r="O14">
-        <v>1.4918737116888358E-2</v>
+        <v>1.9834678608839383E-2</v>
       </c>
       <c r="P14">
-        <v>1.4718704775254342E-2</v>
+        <v>1.7169970864766852E-4</v>
       </c>
       <c r="Q14">
-        <v>-3.6926472400665845E-5</v>
+        <v>1.1904920627386526E-4</v>
       </c>
       <c r="R14">
-        <v>-7.6472789093684664E-5</v>
+        <v>2.0501903717101954E-4</v>
       </c>
       <c r="S14">
-        <v>-1.4895936789019508E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+        <v>-2.250079914339604E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B15">
-        <v>0.95511527010149877</v>
+        <v>0.12528571820150292</v>
       </c>
       <c r="C15">
-        <v>1.0466685181951456E-4</v>
+        <v>-2.5954618541466679E-5</v>
       </c>
       <c r="D15">
-        <v>4.805207038577721E-5</v>
+        <v>4.1854861536380508E-5</v>
       </c>
       <c r="E15">
-        <v>-3.5777106320020804E-7</v>
+        <v>-3.5509792192123915E-7</v>
       </c>
       <c r="F15">
-        <v>-4.985805160543505E-5</v>
+        <v>2.4431651570773374E-4</v>
       </c>
       <c r="G15">
-        <v>5.6029012934952563E-5</v>
+        <v>1.0685245017961423E-4</v>
       </c>
       <c r="H15">
-        <v>6.4704211268023999E-6</v>
+        <v>-1.4410739896764954E-5</v>
       </c>
       <c r="I15">
-        <v>9.6197978446312539E-6</v>
+        <v>-1.3552648385926027E-5</v>
       </c>
       <c r="J15">
-        <v>-7.8373299717757845E-5</v>
+        <v>-2.061952706123057E-6</v>
       </c>
       <c r="K15">
-        <v>-7.1172205508027183E-6</v>
+        <v>-1.5286505074062247E-5</v>
       </c>
       <c r="L15">
-        <v>1.2095779869325156E-3</v>
+        <v>7.1018514009501307E-5</v>
       </c>
       <c r="M15">
-        <v>1.3815916427760748E-2</v>
+        <v>8.9645711805002269E-5</v>
       </c>
       <c r="N15">
-        <v>1.4235847108544983E-2</v>
+        <v>1.1130571888789509E-4</v>
       </c>
       <c r="O15">
-        <v>1.4718704775254342E-2</v>
+        <v>1.7169970864766852E-4</v>
       </c>
       <c r="P15">
-        <v>1.5681346145828806E-2</v>
+        <v>2.8375769844225583E-3</v>
       </c>
       <c r="Q15">
-        <v>2.588698961063533E-5</v>
+        <v>1.8089734307241449E-3</v>
       </c>
       <c r="R15">
-        <v>3.7059723152401552E-6</v>
+        <v>1.4536970427957467E-4</v>
       </c>
       <c r="S15">
-        <v>-1.6259796219309511E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+        <v>-2.5962417107201537E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B16">
-        <v>0.17904048738740611</v>
+        <v>0.10179921953020396</v>
       </c>
       <c r="C16">
-        <v>-9.8925078877475168E-6</v>
+        <v>-8.7268047760245105E-5</v>
       </c>
       <c r="D16">
-        <v>1.9070326766160424E-5</v>
+        <v>5.3839338159356383E-5</v>
       </c>
       <c r="E16">
-        <v>-1.7568652577762842E-7</v>
+        <v>-4.5001561948948472E-7</v>
       </c>
       <c r="F16">
-        <v>4.6658856854230079E-5</v>
+        <v>1.7456310998894891E-4</v>
       </c>
       <c r="G16">
-        <v>5.6004962950312494E-7</v>
+        <v>1.9126627767442246E-4</v>
       </c>
       <c r="H16">
-        <v>-5.7605405544250086E-6</v>
+        <v>-1.3514287682561773E-5</v>
       </c>
       <c r="I16">
-        <v>-5.3198972962569178E-6</v>
+        <v>-1.5921918718951811E-5</v>
       </c>
       <c r="J16">
-        <v>6.3176215659144886E-6</v>
+        <v>-5.1854676594704771E-5</v>
       </c>
       <c r="K16">
-        <v>-8.2883657565052433E-6</v>
+        <v>-1.0225393353802788E-4</v>
       </c>
       <c r="L16">
-        <v>-5.6897367177495081E-5</v>
+        <v>-5.3936328870933937E-5</v>
       </c>
       <c r="M16">
-        <v>-1.824099509547877E-5</v>
+        <v>1.7678683831553804E-6</v>
       </c>
       <c r="N16">
-        <v>-3.6439431865515064E-5</v>
+        <v>3.0607835015725713E-5</v>
       </c>
       <c r="O16">
-        <v>-3.6926472400665845E-5</v>
+        <v>1.1904920627386526E-4</v>
       </c>
       <c r="P16">
-        <v>2.588698961063533E-5</v>
+        <v>1.8089734307241449E-3</v>
       </c>
       <c r="Q16">
-        <v>1.5103759365932992E-3</v>
+        <v>2.3104672553552327E-3</v>
       </c>
       <c r="R16">
-        <v>9.6885125113098229E-4</v>
+        <v>9.5921768177394259E-5</v>
       </c>
       <c r="S16">
-        <v>-1.2038783072624692E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+        <v>-2.7160272852711684E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B17">
-        <v>0.12521105821158601</v>
+        <v>0.28540510530988306</v>
       </c>
       <c r="C17">
-        <v>-5.7450784840138572E-5</v>
+        <v>4.1284008183856723E-5</v>
       </c>
       <c r="D17">
-        <v>2.9664775078279023E-5</v>
+        <v>1.6539420053300593E-5</v>
       </c>
       <c r="E17">
-        <v>-2.6597584017351772E-7</v>
+        <v>-2.8639602325529266E-7</v>
       </c>
       <c r="F17">
-        <v>1.960600936334948E-5</v>
+        <v>-1.0864708922261266E-4</v>
       </c>
       <c r="G17">
-        <v>3.7667157218110509E-5</v>
+        <v>-3.581656785742148E-4</v>
       </c>
       <c r="H17">
-        <v>-5.1900659535332845E-6</v>
+        <v>3.0027204782498891E-6</v>
       </c>
       <c r="I17">
-        <v>-6.6889474738087896E-6</v>
+        <v>6.9254514953309459E-6</v>
       </c>
       <c r="J17">
-        <v>-3.2568270055214753E-5</v>
+        <v>7.1923405901732265E-5</v>
       </c>
       <c r="K17">
-        <v>-4.3017240761036946E-5</v>
+        <v>4.2052567295545172E-6</v>
       </c>
       <c r="L17">
-        <v>-7.9582875953180621E-5</v>
+        <v>2.2930781021454307E-4</v>
       </c>
       <c r="M17">
-        <v>-8.1705215180906843E-5</v>
+        <v>3.1579345404245866E-4</v>
       </c>
       <c r="N17">
-        <v>-8.4444305399556426E-5</v>
+        <v>3.0783883234234701E-4</v>
       </c>
       <c r="O17">
-        <v>-7.6472789093684664E-5</v>
+        <v>2.0501903717101954E-4</v>
       </c>
       <c r="P17">
-        <v>3.7059723152401552E-6</v>
+        <v>1.4536970427957467E-4</v>
       </c>
       <c r="Q17">
-        <v>9.6885125113098229E-4</v>
+        <v>9.5921768177394259E-5</v>
       </c>
       <c r="R17">
-        <v>1.2688021107042785E-3</v>
+        <v>6.9045805632721342E-3</v>
       </c>
       <c r="S17">
-        <v>-1.3550857758053176E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+        <v>-8.4555059844418205E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>3</v>
       </c>
       <c r="B18">
-        <v>-3.6283861926610577</v>
+        <v>-4.0533585592513788</v>
       </c>
       <c r="C18">
-        <v>2.8732604107089572E-3</v>
+        <v>5.4693867182005152E-3</v>
       </c>
       <c r="D18">
-        <v>-1.582587139979215E-3</v>
+        <v>-3.183080906889854E-3</v>
       </c>
       <c r="E18">
-        <v>1.3877078640669314E-5</v>
+        <v>2.9177633485087495E-5</v>
       </c>
       <c r="F18">
-        <v>-1.6058940981721122E-2</v>
+        <v>-2.8857939410375726E-2</v>
       </c>
       <c r="G18">
-        <v>-1.9112075662264354E-2</v>
+        <v>-3.4952833852940332E-2</v>
       </c>
       <c r="H18">
-        <v>3.4109955905497482E-4</v>
+        <v>6.1812948909766247E-4</v>
       </c>
       <c r="I18">
-        <v>4.076453765696343E-4</v>
+        <v>7.5483573927942634E-4</v>
       </c>
       <c r="J18">
-        <v>1.4072066216154161E-3</v>
+        <v>1.0809788466888258E-3</v>
       </c>
       <c r="K18">
-        <v>1.1989401991599705E-4</v>
+        <v>3.6023939084818576E-3</v>
       </c>
       <c r="L18">
-        <v>-7.7823907841851508E-4</v>
+        <v>-1.7987202798699815E-2</v>
       </c>
       <c r="M18">
-        <v>-1.4071958731727296E-2</v>
+        <v>-1.8679743762675484E-2</v>
       </c>
       <c r="N18">
-        <v>-1.4475746378943092E-2</v>
+        <v>-2.0172344905685487E-2</v>
       </c>
       <c r="O18">
-        <v>-1.4895936789019508E-2</v>
+        <v>-2.250079914339604E-2</v>
       </c>
       <c r="P18">
-        <v>-1.6259796219309511E-2</v>
+        <v>-2.5962417107201537E-3</v>
       </c>
       <c r="Q18">
-        <v>-1.2038783072624692E-3</v>
+        <v>-2.7160272852711684E-3</v>
       </c>
       <c r="R18">
-        <v>-1.3550857758053176E-3</v>
+        <v>-8.4555059844418205E-4</v>
       </c>
       <c r="S18">
-        <v>5.347828305862673E-2</v>
+        <v>9.4631103631195479E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2741,18 +2747,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1B0716A-7AD7-48C5-B132-6B376B317883}">
   <dimension ref="A1:R17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="23.5703125" style="2" customWidth="1"/>
-    <col min="2" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="23.59765625" style="2" customWidth="1"/>
+    <col min="2" max="16384" width="9.1328125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
         <v>19</v>
-      </c>
-      <c r="B1" t="s">
-        <v>20</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -2767,19 +2773,19 @@
         <v>4</v>
       </c>
       <c r="G1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" t="s">
         <v>9</v>
-      </c>
-      <c r="H1" t="s">
-        <v>10</v>
       </c>
       <c r="I1" t="s">
         <v>7</v>
       </c>
       <c r="J1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" t="s">
         <v>12</v>
-      </c>
-      <c r="K1" t="s">
-        <v>8</v>
       </c>
       <c r="L1" t="s">
         <v>13</v>
@@ -2797,906 +2803,906 @@
         <v>17</v>
       </c>
       <c r="Q1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="R1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.22631868292032631</v>
+        <v>0.28900975060454243</v>
       </c>
       <c r="C2">
-        <v>7.7651203458025159E-5</v>
+        <v>1.379032898396003E-4</v>
       </c>
       <c r="D2">
-        <v>-8.5028072760585472E-7</v>
+        <v>-1.518963952292478E-6</v>
       </c>
       <c r="E2">
-        <v>2.1022461201483802E-4</v>
+        <v>3.5673018833991255E-4</v>
       </c>
       <c r="F2">
-        <v>1.4366374992263341E-4</v>
+        <v>2.1445049493163765E-4</v>
       </c>
       <c r="G2">
-        <v>-4.6679531098624355E-6</v>
+        <v>-8.0458397808778717E-6</v>
       </c>
       <c r="H2">
-        <v>-3.0960202856542621E-6</v>
+        <v>-4.8390006318121267E-6</v>
       </c>
       <c r="I2">
-        <v>-3.9749009609073806E-5</v>
+        <v>-5.7250520881495972E-5</v>
       </c>
       <c r="J2">
-        <v>-6.9661501792601377E-5</v>
+        <v>-1.7084624969435492E-4</v>
       </c>
       <c r="K2">
-        <v>8.8421015091308343E-6</v>
+        <v>2.2701276696877404E-5</v>
       </c>
       <c r="L2">
-        <v>1.6085577879934761E-5</v>
+        <v>3.1891168058820587E-5</v>
       </c>
       <c r="M2">
-        <v>1.7849435101213859E-5</v>
+        <v>3.2258358275356284E-5</v>
       </c>
       <c r="N2">
-        <v>1.4588057721068759E-5</v>
+        <v>1.008549169433762E-4</v>
       </c>
       <c r="O2">
-        <v>6.1336160001339702E-5</v>
+        <v>-5.3835717163258916E-7</v>
       </c>
       <c r="P2">
-        <v>-2.8534138400756467E-7</v>
+        <v>4.8240918232226161E-8</v>
       </c>
       <c r="Q2">
-        <v>3.0948622998538909E-7</v>
+        <v>1.9952950059447219E-5</v>
       </c>
       <c r="R2">
-        <v>-1.6321105455625858E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-2.8675003921770294E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3">
-        <v>-2.4763342987114334E-3</v>
+        <v>-3.2103034923865836E-3</v>
       </c>
       <c r="C3">
-        <v>-8.5028072760585472E-7</v>
+        <v>-1.518963952292478E-6</v>
       </c>
       <c r="D3">
-        <v>9.7885401041772255E-9</v>
+        <v>1.7499941857494213E-8</v>
       </c>
       <c r="E3">
-        <v>-6.9306660222151474E-7</v>
+        <v>-1.3480476675497691E-6</v>
       </c>
       <c r="F3">
-        <v>8.2586220481516472E-8</v>
+        <v>3.4417805630563367E-7</v>
       </c>
       <c r="G3">
-        <v>1.3853616001486691E-8</v>
+        <v>2.9444599897870155E-8</v>
       </c>
       <c r="H3">
-        <v>-4.2719860390317967E-9</v>
+        <v>-8.2230775977626735E-9</v>
       </c>
       <c r="I3">
-        <v>3.8148335594775103E-7</v>
+        <v>5.5080195962226936E-7</v>
       </c>
       <c r="J3">
-        <v>8.7230052576653517E-7</v>
+        <v>2.0996125655545774E-6</v>
       </c>
       <c r="K3">
-        <v>-9.096976204439846E-8</v>
+        <v>-2.4979547907951261E-7</v>
       </c>
       <c r="L3">
-        <v>-1.8625480181782308E-7</v>
+        <v>-3.8805576545794083E-7</v>
       </c>
       <c r="M3">
-        <v>-2.2302876931093128E-7</v>
+        <v>-2.8648237626648773E-7</v>
       </c>
       <c r="N3">
-        <v>-1.0550940739351458E-7</v>
+        <v>-8.2827936561178794E-7</v>
       </c>
       <c r="O3">
-        <v>-5.2159384788359643E-7</v>
+        <v>2.5326740573565246E-8</v>
       </c>
       <c r="P3">
-        <v>1.2049835516143592E-8</v>
+        <v>2.3136485195784772E-8</v>
       </c>
       <c r="Q3">
-        <v>8.0343208336362217E-9</v>
+        <v>-2.9603840140851104E-7</v>
       </c>
       <c r="R3">
-        <v>1.6852222283021417E-5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+        <v>2.9905497144040133E-5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0.18003085539679323</v>
+        <v>0.35139566653963095</v>
       </c>
       <c r="C4">
-        <v>2.1022461201483802E-4</v>
+        <v>3.5673018833991255E-4</v>
       </c>
       <c r="D4">
-        <v>-6.9306660222151474E-7</v>
+        <v>-1.3480476675497691E-6</v>
       </c>
       <c r="E4">
-        <v>1.030286639434866E-2</v>
+        <v>1.6640675086369155E-2</v>
       </c>
       <c r="F4">
-        <v>7.1244679991555003E-3</v>
+        <v>1.1384880810401198E-2</v>
       </c>
       <c r="G4">
-        <v>-2.2077024088487039E-4</v>
+        <v>-3.5440235332734489E-4</v>
       </c>
       <c r="H4">
-        <v>-1.5381411874706622E-4</v>
+        <v>-2.447151191275866E-4</v>
       </c>
       <c r="I4">
-        <v>3.0881185392259559E-6</v>
+        <v>2.6311581133387288E-5</v>
       </c>
       <c r="J4">
-        <v>-2.2472607936359335E-4</v>
+        <v>-3.9665440901014609E-4</v>
       </c>
       <c r="K4">
-        <v>1.7786202918941281E-4</v>
+        <v>7.5058804882857655E-5</v>
       </c>
       <c r="L4">
-        <v>1.0490283697320866E-4</v>
+        <v>-2.2713075836398519E-6</v>
       </c>
       <c r="M4">
-        <v>2.0297018501569918E-5</v>
+        <v>-9.642087398527158E-5</v>
       </c>
       <c r="N4">
-        <v>-8.9409278258155596E-6</v>
+        <v>2.587958821756893E-4</v>
       </c>
       <c r="O4">
-        <v>1.0344590083602835E-4</v>
+        <v>-6.4027560846233417E-5</v>
       </c>
       <c r="P4">
-        <v>-6.6119321545317168E-5</v>
+        <v>-3.329134193651097E-5</v>
       </c>
       <c r="Q4">
-        <v>-5.370471368795151E-5</v>
+        <v>1.9753856748480901E-6</v>
       </c>
       <c r="R4">
-        <v>-8.045509535291661E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-1.3328555072557868E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>-0.1577970475777668</v>
+        <v>0.18620726084209027</v>
       </c>
       <c r="C5">
-        <v>1.4366374992263341E-4</v>
+        <v>2.1445049493163765E-4</v>
       </c>
       <c r="D5">
-        <v>8.2586220481516472E-8</v>
+        <v>3.4417805630563367E-7</v>
       </c>
       <c r="E5">
-        <v>7.1244679991555003E-3</v>
+        <v>1.1384880810401198E-2</v>
       </c>
       <c r="F5">
-        <v>2.4439379227069111E-2</v>
+        <v>3.9568232900242944E-2</v>
       </c>
       <c r="G5">
-        <v>-1.5402720298398386E-4</v>
+        <v>-2.4459275810544573E-4</v>
       </c>
       <c r="H5">
-        <v>-4.9570788619699596E-4</v>
+        <v>-7.9354674634994431E-4</v>
       </c>
       <c r="I5">
-        <v>-6.2766318430628438E-5</v>
+        <v>-1.5872878971572423E-4</v>
       </c>
       <c r="J5">
-        <v>-4.6968649925907308E-4</v>
+        <v>-6.3564081991252202E-4</v>
       </c>
       <c r="K5">
-        <v>2.5696642069232708E-4</v>
+        <v>1.3993567054166808E-4</v>
       </c>
       <c r="L5">
-        <v>1.7401790463893608E-4</v>
+        <v>-1.0613749985563482E-4</v>
       </c>
       <c r="M5">
-        <v>1.1066381415341265E-5</v>
+        <v>-2.0231407135168572E-4</v>
       </c>
       <c r="N5">
-        <v>-3.3798194459368561E-5</v>
+        <v>5.8717293861776333E-4</v>
       </c>
       <c r="O5">
-        <v>2.8524091831153443E-4</v>
+        <v>-1.3994199184280006E-5</v>
       </c>
       <c r="P5">
-        <v>-3.9752103300731896E-5</v>
+        <v>-5.1575584992851503E-5</v>
       </c>
       <c r="Q5">
-        <v>-5.3142857639408277E-5</v>
+        <v>-1.8060610251339405E-4</v>
       </c>
       <c r="R5">
-        <v>-6.6369066943382116E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-1.0378133747098775E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>-9.8653864753224327E-3</v>
+      </c>
+      <c r="C6">
+        <v>-8.0458397808778717E-6</v>
+      </c>
+      <c r="D6">
+        <v>2.9444599897870155E-8</v>
+      </c>
+      <c r="E6">
+        <v>-3.5440235332734489E-4</v>
+      </c>
+      <c r="F6">
+        <v>-2.4459275810544573E-4</v>
+      </c>
+      <c r="G6">
+        <v>8.1058521441029473E-6</v>
+      </c>
+      <c r="H6">
+        <v>5.6710495912289797E-6</v>
+      </c>
+      <c r="I6">
+        <v>-1.0376486808220645E-6</v>
+      </c>
+      <c r="J6">
+        <v>9.266301556893933E-6</v>
+      </c>
+      <c r="K6">
+        <v>-2.8573999712117802E-6</v>
+      </c>
+      <c r="L6">
+        <v>2.2739406307308951E-7</v>
+      </c>
+      <c r="M6">
+        <v>4.4013018801793971E-6</v>
+      </c>
+      <c r="N6">
+        <v>-9.953152187544052E-7</v>
+      </c>
+      <c r="O6">
+        <v>-1.6915635592258843E-6</v>
+      </c>
+      <c r="P6">
+        <v>-2.0790634640891635E-6</v>
+      </c>
+      <c r="Q6">
+        <v>-1.1410093011359125E-6</v>
+      </c>
+      <c r="R6">
+        <v>2.851540945620351E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
         <v>9</v>
       </c>
-      <c r="B6">
-        <v>-6.4223329521294475E-3</v>
-      </c>
-      <c r="C6">
-        <v>-4.6679531098624355E-6</v>
-      </c>
-      <c r="D6">
-        <v>1.3853616001486691E-8</v>
-      </c>
-      <c r="E6">
-        <v>-2.2077024088487039E-4</v>
-      </c>
-      <c r="F6">
-        <v>-1.5402720298398386E-4</v>
-      </c>
-      <c r="G6">
-        <v>5.0791007441823064E-6</v>
-      </c>
-      <c r="H6">
-        <v>3.5821848940891238E-6</v>
-      </c>
-      <c r="I6">
-        <v>-3.8189656655171251E-7</v>
-      </c>
-      <c r="J6">
-        <v>4.7269470424102415E-6</v>
-      </c>
-      <c r="K6">
-        <v>-5.4456398448492658E-6</v>
-      </c>
-      <c r="L6">
-        <v>-3.0805352458525067E-6</v>
-      </c>
-      <c r="M6">
-        <v>-6.1224240254822949E-7</v>
-      </c>
-      <c r="N6">
-        <v>1.2551888331589829E-6</v>
-      </c>
-      <c r="O6">
-        <v>1.0245404409449756E-7</v>
-      </c>
-      <c r="P6">
-        <v>-4.6324626572046809E-7</v>
-      </c>
-      <c r="Q6">
-        <v>-4.3147221995909979E-7</v>
-      </c>
-      <c r="R6">
-        <v>1.7154989787195255E-4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
       <c r="B7">
-        <v>-3.559688337234601E-3</v>
+        <v>-1.1533185740924577E-2</v>
       </c>
       <c r="C7">
-        <v>-3.0960202856542621E-6</v>
+        <v>-4.8390006318121267E-6</v>
       </c>
       <c r="D7">
-        <v>-4.2719860390317967E-9</v>
+        <v>-8.2230775977626735E-9</v>
       </c>
       <c r="E7">
-        <v>-1.5381411874706622E-4</v>
+        <v>-2.447151191275866E-4</v>
       </c>
       <c r="F7">
-        <v>-4.9570788619699596E-4</v>
+        <v>-7.9354674634994431E-4</v>
       </c>
       <c r="G7">
-        <v>3.5821848940891238E-6</v>
+        <v>5.6710495912289797E-6</v>
       </c>
       <c r="H7">
-        <v>1.0673720660909428E-5</v>
+        <v>1.6859894118154084E-5</v>
       </c>
       <c r="I7">
-        <v>1.1682119697230496E-6</v>
+        <v>3.0563307547537706E-6</v>
       </c>
       <c r="J7">
-        <v>8.493379193651847E-6</v>
+        <v>1.3145718025320401E-5</v>
       </c>
       <c r="K7">
-        <v>-6.267307036053484E-6</v>
+        <v>-5.4071288059370036E-6</v>
       </c>
       <c r="L7">
-        <v>-3.5293385356878381E-6</v>
+        <v>4.006024852589403E-6</v>
       </c>
       <c r="M7">
-        <v>2.7496146584132347E-6</v>
+        <v>1.0457083066752165E-5</v>
       </c>
       <c r="N7">
-        <v>6.5782845889064876E-6</v>
+        <v>-2.6243805360400235E-6</v>
       </c>
       <c r="O7">
-        <v>1.6259673652372229E-6</v>
+        <v>-4.1308180956013379E-6</v>
       </c>
       <c r="P7">
-        <v>-1.7356981343608313E-6</v>
+        <v>-3.2356973076175813E-6</v>
       </c>
       <c r="Q7">
-        <v>-1.1443763466430396E-6</v>
+        <v>2.5044642490246679E-6</v>
       </c>
       <c r="R7">
-        <v>1.3443700185652437E-4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+        <v>2.1571734513415713E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.10871227841234643</v>
+        <v>-3.4605321642208899E-2</v>
       </c>
       <c r="C8">
-        <v>-3.9749009609073806E-5</v>
+        <v>-5.7250520881495972E-5</v>
       </c>
       <c r="D8">
-        <v>3.8148335594775103E-7</v>
+        <v>5.5080195962226936E-7</v>
       </c>
       <c r="E8">
-        <v>3.0881185392259559E-6</v>
+        <v>2.6311581133387288E-5</v>
       </c>
       <c r="F8">
-        <v>-6.2766318430628438E-5</v>
+        <v>-1.5872878971572423E-4</v>
       </c>
       <c r="G8">
-        <v>-3.8189656655171251E-7</v>
+        <v>-1.0376486808220645E-6</v>
       </c>
       <c r="H8">
-        <v>1.1682119697230496E-6</v>
+        <v>3.0563307547537706E-6</v>
       </c>
       <c r="I8">
-        <v>5.8380440250922706E-4</v>
+        <v>9.6539983833275232E-4</v>
       </c>
       <c r="J8">
-        <v>-1.2715708090908632E-4</v>
+        <v>-2.2871303999174371E-4</v>
       </c>
       <c r="K8">
-        <v>-1.64721935568037E-5</v>
+        <v>-4.1552005467528893E-5</v>
       </c>
       <c r="L8">
-        <v>-9.8095864964041772E-6</v>
+        <v>-2.761746715199614E-5</v>
       </c>
       <c r="M8">
-        <v>-2.2065179306763894E-5</v>
+        <v>-8.3293645589158701E-5</v>
       </c>
       <c r="N8">
-        <v>-3.8375890269001474E-5</v>
+        <v>-4.141845809350653E-5</v>
       </c>
       <c r="O8">
-        <v>-4.1051181293713098E-5</v>
+        <v>-3.3097037931515037E-5</v>
       </c>
       <c r="P8">
-        <v>-2.2832518841860447E-5</v>
+        <v>-5.0920741027229427E-5</v>
       </c>
       <c r="Q8">
-        <v>-2.878315030818674E-5</v>
+        <v>-1.0662833501723235E-5</v>
       </c>
       <c r="R8">
-        <v>7.3233530796113638E-4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+        <v>9.685122269941195E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <v>-0.33290073028628747</v>
+      </c>
+      <c r="C9">
+        <v>-1.7084624969435492E-4</v>
+      </c>
+      <c r="D9">
+        <v>2.0996125655545774E-6</v>
+      </c>
+      <c r="E9">
+        <v>-3.9665440901014609E-4</v>
+      </c>
+      <c r="F9">
+        <v>-6.3564081991252202E-4</v>
+      </c>
+      <c r="G9">
+        <v>9.266301556893933E-6</v>
+      </c>
+      <c r="H9">
+        <v>1.3145718025320401E-5</v>
+      </c>
+      <c r="I9">
+        <v>-2.2871303999174371E-4</v>
+      </c>
+      <c r="J9">
+        <v>1.3751397409597365E-3</v>
+      </c>
+      <c r="K9">
+        <v>-9.5197263790350881E-6</v>
+      </c>
+      <c r="L9">
+        <v>-6.3226280143379408E-5</v>
+      </c>
+      <c r="M9">
+        <v>-8.9947041915851376E-5</v>
+      </c>
+      <c r="N9">
+        <v>-3.6136859163913931E-5</v>
+      </c>
+      <c r="O9">
+        <v>-5.5856232561778803E-6</v>
+      </c>
+      <c r="P9">
+        <v>-2.4954454843412912E-5</v>
+      </c>
+      <c r="Q9">
+        <v>-6.582919212544226E-5</v>
+      </c>
+      <c r="R9">
+        <v>2.924566870873222E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
         <v>12</v>
       </c>
-      <c r="B9">
-        <v>-0.16738654861163121</v>
-      </c>
-      <c r="C9">
-        <v>-6.9661501792601377E-5</v>
-      </c>
-      <c r="D9">
-        <v>8.7230052576653517E-7</v>
-      </c>
-      <c r="E9">
-        <v>-2.2472607936359335E-4</v>
-      </c>
-      <c r="F9">
-        <v>-4.6968649925907308E-4</v>
-      </c>
-      <c r="G9">
-        <v>4.7269470424102415E-6</v>
-      </c>
-      <c r="H9">
-        <v>8.493379193651847E-6</v>
-      </c>
-      <c r="I9">
-        <v>-1.2715708090908632E-4</v>
-      </c>
-      <c r="J9">
-        <v>7.4174847669903482E-4</v>
-      </c>
-      <c r="K9">
-        <v>4.5543802630172633E-5</v>
-      </c>
-      <c r="L9">
-        <v>8.2547143839681791E-7</v>
-      </c>
-      <c r="M9">
-        <v>-6.4932781996575317E-7</v>
-      </c>
-      <c r="N9">
-        <v>-2.2824502199345108E-6</v>
-      </c>
-      <c r="O9">
-        <v>1.6117246590135093E-6</v>
-      </c>
-      <c r="P9">
-        <v>-4.9433391925456608E-6</v>
-      </c>
-      <c r="Q9">
-        <v>-8.7925736489692518E-6</v>
-      </c>
-      <c r="R9">
-        <v>1.1036651800808476E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
       <c r="B10">
-        <v>-1.5273608918626485</v>
+        <v>0.33967344596385929</v>
       </c>
       <c r="C10">
-        <v>8.8421015091308343E-6</v>
+        <v>2.2701276696877404E-5</v>
       </c>
       <c r="D10">
-        <v>-9.096976204439846E-8</v>
+        <v>-2.4979547907951261E-7</v>
       </c>
       <c r="E10">
-        <v>1.7786202918941281E-4</v>
+        <v>7.5058804882857655E-5</v>
       </c>
       <c r="F10">
-        <v>2.5696642069232708E-4</v>
+        <v>1.3993567054166808E-4</v>
       </c>
       <c r="G10">
-        <v>-5.4456398448492658E-6</v>
+        <v>-2.8573999712117802E-6</v>
       </c>
       <c r="H10">
-        <v>-6.267307036053484E-6</v>
+        <v>-5.4071288059370036E-6</v>
       </c>
       <c r="I10">
-        <v>-1.64721935568037E-5</v>
+        <v>-4.1552005467528893E-5</v>
       </c>
       <c r="J10">
-        <v>4.5543802630172633E-5</v>
+        <v>-9.5197263790350881E-6</v>
       </c>
       <c r="K10">
-        <v>1.0512414611450274E-2</v>
+        <v>2.8770461292526049E-2</v>
       </c>
       <c r="L10">
-        <v>1.4583527906433641E-3</v>
+        <v>2.5257221590582642E-2</v>
       </c>
       <c r="M10">
-        <v>2.2182739079216044E-3</v>
+        <v>2.5229307305498307E-2</v>
       </c>
       <c r="N10">
-        <v>2.3805427437065094E-3</v>
+        <v>2.5213914858029915E-2</v>
       </c>
       <c r="O10">
-        <v>2.3632753860340439E-3</v>
+        <v>5.9292889716510089E-5</v>
       </c>
       <c r="P10">
-        <v>-9.3700640268392423E-5</v>
+        <v>-1.9664860620704496E-5</v>
       </c>
       <c r="Q10">
-        <v>-7.3663126828088141E-5</v>
+        <v>5.4819112902517906E-5</v>
       </c>
       <c r="R10">
-        <v>-2.5078519463427357E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-2.5648610532396362E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>13</v>
       </c>
       <c r="B11">
-        <v>0.35373436516013401</v>
+        <v>0.69749597146999465</v>
       </c>
       <c r="C11">
-        <v>1.6085577879934761E-5</v>
+        <v>3.1891168058820587E-5</v>
       </c>
       <c r="D11">
-        <v>-1.8625480181782308E-7</v>
+        <v>-3.8805576545794083E-7</v>
       </c>
       <c r="E11">
-        <v>1.0490283697320866E-4</v>
+        <v>-2.2713075836398519E-6</v>
       </c>
       <c r="F11">
-        <v>1.7401790463893608E-4</v>
+        <v>-1.0613749985563482E-4</v>
       </c>
       <c r="G11">
-        <v>-3.0805352458525067E-6</v>
+        <v>2.2739406307308951E-7</v>
       </c>
       <c r="H11">
-        <v>-3.5293385356878381E-6</v>
+        <v>4.006024852589403E-6</v>
       </c>
       <c r="I11">
-        <v>-9.8095864964041772E-6</v>
+        <v>-2.761746715199614E-5</v>
       </c>
       <c r="J11">
-        <v>8.2547143839681791E-7</v>
+        <v>-6.3226280143379408E-5</v>
       </c>
       <c r="K11">
-        <v>1.4583527906433641E-3</v>
+        <v>2.5257221590582642E-2</v>
       </c>
       <c r="L11">
-        <v>2.0902909621068964E-2</v>
+        <v>2.601877279183833E-2</v>
       </c>
       <c r="M11">
-        <v>1.8323220789430411E-2</v>
+        <v>2.527469614945102E-2</v>
       </c>
       <c r="N11">
-        <v>1.8329086685413588E-2</v>
+        <v>2.5278430172063004E-2</v>
       </c>
       <c r="O11">
-        <v>1.831992717775224E-2</v>
+        <v>-6.4921917778294346E-6</v>
       </c>
       <c r="P11">
-        <v>6.9527131174456931E-6</v>
+        <v>-4.7756059766504281E-5</v>
       </c>
       <c r="Q11">
-        <v>2.7708902116628509E-6</v>
+        <v>1.2319656962183874E-6</v>
       </c>
       <c r="R11">
-        <v>-1.8638491928052763E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-2.5823936510038913E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>14</v>
       </c>
       <c r="B12">
-        <v>0.54428575722636208</v>
+        <v>0.79083775932354416</v>
       </c>
       <c r="C12">
-        <v>1.7849435101213859E-5</v>
+        <v>3.2258358275356284E-5</v>
       </c>
       <c r="D12">
-        <v>-2.2302876931093128E-7</v>
+        <v>-2.8648237626648773E-7</v>
       </c>
       <c r="E12">
-        <v>2.0297018501569918E-5</v>
+        <v>-9.642087398527158E-5</v>
       </c>
       <c r="F12">
-        <v>1.1066381415341265E-5</v>
+        <v>-2.0231407135168572E-4</v>
       </c>
       <c r="G12">
-        <v>-6.1224240254822949E-7</v>
+        <v>4.4013018801793971E-6</v>
       </c>
       <c r="H12">
-        <v>2.7496146584132347E-6</v>
+        <v>1.0457083066752165E-5</v>
       </c>
       <c r="I12">
-        <v>-2.2065179306763894E-5</v>
+        <v>-8.3293645589158701E-5</v>
       </c>
       <c r="J12">
-        <v>-6.4932781996575317E-7</v>
+        <v>-8.9947041915851376E-5</v>
       </c>
       <c r="K12">
-        <v>2.2182739079216044E-3</v>
+        <v>2.5229307305498307E-2</v>
       </c>
       <c r="L12">
-        <v>1.8323220789430411E-2</v>
+        <v>2.527469614945102E-2</v>
       </c>
       <c r="M12">
-        <v>1.8999126774858405E-2</v>
+        <v>2.5771880217037583E-2</v>
       </c>
       <c r="N12">
-        <v>1.8544400975780851E-2</v>
+        <v>2.5518937922341819E-2</v>
       </c>
       <c r="O12">
-        <v>1.8548287400995237E-2</v>
+        <v>8.6964207753596366E-7</v>
       </c>
       <c r="P12">
-        <v>-2.9638669806016549E-5</v>
+        <v>-1.8119669995256087E-5</v>
       </c>
       <c r="Q12">
-        <v>-2.0251895819155827E-5</v>
+        <v>-3.9959951092701654E-5</v>
       </c>
       <c r="R12">
-        <v>-1.8856007107679651E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-2.6227629444114744E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>15</v>
       </c>
       <c r="B13">
-        <v>0.5447466277319567</v>
+        <v>0.80057638191003</v>
       </c>
       <c r="C13">
-        <v>1.4588057721068759E-5</v>
+        <v>1.008549169433762E-4</v>
       </c>
       <c r="D13">
-        <v>-1.0550940739351458E-7</v>
+        <v>-8.2827936561178794E-7</v>
       </c>
       <c r="E13">
-        <v>-8.9409278258155596E-6</v>
+        <v>2.587958821756893E-4</v>
       </c>
       <c r="F13">
-        <v>-3.3798194459368561E-5</v>
+        <v>5.8717293861776333E-4</v>
       </c>
       <c r="G13">
-        <v>1.2551888331589829E-6</v>
+        <v>-9.953152187544052E-7</v>
       </c>
       <c r="H13">
-        <v>6.5782845889064876E-6</v>
+        <v>-2.6243805360400235E-6</v>
       </c>
       <c r="I13">
-        <v>-3.8375890269001474E-5</v>
+        <v>-4.141845809350653E-5</v>
       </c>
       <c r="J13">
-        <v>-2.2824502199345108E-6</v>
+        <v>-3.6136859163913931E-5</v>
       </c>
       <c r="K13">
-        <v>2.3805427437065094E-3</v>
+        <v>2.5213914858029915E-2</v>
       </c>
       <c r="L13">
-        <v>1.8329086685413588E-2</v>
+        <v>2.5278430172063004E-2</v>
       </c>
       <c r="M13">
-        <v>1.8544400975780851E-2</v>
+        <v>2.5518937922341819E-2</v>
       </c>
       <c r="N13">
-        <v>1.889080519004422E-2</v>
+        <v>2.72110671655784E-2</v>
       </c>
       <c r="O13">
-        <v>1.8751793449415074E-2</v>
+        <v>-3.9313850017392432E-6</v>
       </c>
       <c r="P13">
-        <v>-2.6892745924405914E-5</v>
+        <v>-8.1989646171176872E-7</v>
       </c>
       <c r="Q13">
-        <v>3.6050445477317722E-6</v>
+        <v>-4.3579487833981595E-5</v>
       </c>
       <c r="R13">
-        <v>-1.9131985569891465E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-2.8397307697527019E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>16</v>
       </c>
       <c r="B14">
-        <v>0.73002233937492689</v>
+        <v>1.6590253689334967E-2</v>
       </c>
       <c r="C14">
-        <v>6.1336160001339702E-5</v>
+        <v>-5.3835717163258916E-7</v>
       </c>
       <c r="D14">
-        <v>-5.2159384788359643E-7</v>
+        <v>2.5326740573565246E-8</v>
       </c>
       <c r="E14">
-        <v>1.0344590083602835E-4</v>
+        <v>-6.4027560846233417E-5</v>
       </c>
       <c r="F14">
-        <v>2.8524091831153443E-4</v>
+        <v>-1.3994199184280006E-5</v>
       </c>
       <c r="G14">
-        <v>1.0245404409449756E-7</v>
+        <v>-1.6915635592258843E-6</v>
       </c>
       <c r="H14">
-        <v>1.6259673652372229E-6</v>
+        <v>-4.1308180956013379E-6</v>
       </c>
       <c r="I14">
-        <v>-4.1051181293713098E-5</v>
+        <v>-3.3097037931515037E-5</v>
       </c>
       <c r="J14">
-        <v>1.6117246590135093E-6</v>
+        <v>-5.5856232561778803E-6</v>
       </c>
       <c r="K14">
-        <v>2.3632753860340439E-3</v>
+        <v>5.9292889716510089E-5</v>
       </c>
       <c r="L14">
-        <v>1.831992717775224E-2</v>
+        <v>-6.4921917778294346E-6</v>
       </c>
       <c r="M14">
-        <v>1.8548287400995237E-2</v>
+        <v>8.6964207753596366E-7</v>
       </c>
       <c r="N14">
-        <v>1.8751793449415074E-2</v>
+        <v>-3.9313850017392432E-6</v>
       </c>
       <c r="O14">
-        <v>1.9879500581741306E-2</v>
+        <v>1.7507242900570178E-3</v>
       </c>
       <c r="P14">
-        <v>-2.458566599709502E-5</v>
+        <v>1.0954969636951157E-3</v>
       </c>
       <c r="Q14">
-        <v>2.8790942844971124E-5</v>
+        <v>2.740911322599926E-5</v>
       </c>
       <c r="R14">
-        <v>-2.0464114106240532E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-9.8480498202710453E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>17</v>
       </c>
       <c r="B15">
-        <v>-6.4736071635387903E-4</v>
+        <v>3.2174648308921285E-2</v>
       </c>
       <c r="C15">
-        <v>-2.8534138400756467E-7</v>
+        <v>4.8240918232226161E-8</v>
       </c>
       <c r="D15">
-        <v>1.2049835516143592E-8</v>
+        <v>2.3136485195784772E-8</v>
       </c>
       <c r="E15">
-        <v>-6.6119321545317168E-5</v>
+        <v>-3.329134193651097E-5</v>
       </c>
       <c r="F15">
-        <v>-3.9752103300731896E-5</v>
+        <v>-5.1575584992851503E-5</v>
       </c>
       <c r="G15">
-        <v>-4.6324626572046809E-7</v>
+        <v>-2.0790634640891635E-6</v>
       </c>
       <c r="H15">
-        <v>-1.7356981343608313E-6</v>
+        <v>-3.2356973076175813E-6</v>
       </c>
       <c r="I15">
-        <v>-2.2832518841860447E-5</v>
+        <v>-5.0920741027229427E-5</v>
       </c>
       <c r="J15">
-        <v>-4.9433391925456608E-6</v>
+        <v>-2.4954454843412912E-5</v>
       </c>
       <c r="K15">
-        <v>-9.3700640268392423E-5</v>
+        <v>-1.9664860620704496E-5</v>
       </c>
       <c r="L15">
-        <v>6.9527131174456931E-6</v>
+        <v>-4.7756059766504281E-5</v>
       </c>
       <c r="M15">
-        <v>-2.9638669806016549E-5</v>
+        <v>-1.8119669995256087E-5</v>
       </c>
       <c r="N15">
-        <v>-2.6892745924405914E-5</v>
+        <v>-8.1989646171176872E-7</v>
       </c>
       <c r="O15">
-        <v>-2.458566599709502E-5</v>
+        <v>1.0954969636951157E-3</v>
       </c>
       <c r="P15">
-        <v>1.0818934160242953E-3</v>
+        <v>1.4765238067515625E-3</v>
       </c>
       <c r="Q15">
-        <v>6.6945803799702734E-4</v>
+        <v>5.4219243725026323E-5</v>
       </c>
       <c r="R15">
-        <v>-5.6823211635214396E-4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-9.7636894331574802E-4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B16">
-        <v>2.9189559390160425E-2</v>
+        <v>0.16391245572823404</v>
       </c>
       <c r="C16">
-        <v>3.0948622998538909E-7</v>
+        <v>1.9952950059447219E-5</v>
       </c>
       <c r="D16">
-        <v>8.0343208336362217E-9</v>
+        <v>-2.9603840140851104E-7</v>
       </c>
       <c r="E16">
-        <v>-5.370471368795151E-5</v>
+        <v>1.9753856748480901E-6</v>
       </c>
       <c r="F16">
-        <v>-5.3142857639408277E-5</v>
+        <v>-1.8060610251339405E-4</v>
       </c>
       <c r="G16">
-        <v>-4.3147221995909979E-7</v>
+        <v>-1.1410093011359125E-6</v>
       </c>
       <c r="H16">
-        <v>-1.1443763466430396E-6</v>
+        <v>2.5044642490246679E-6</v>
       </c>
       <c r="I16">
-        <v>-2.878315030818674E-5</v>
+        <v>-1.0662833501723235E-5</v>
       </c>
       <c r="J16">
-        <v>-8.7925736489692518E-6</v>
+        <v>-6.582919212544226E-5</v>
       </c>
       <c r="K16">
-        <v>-7.3663126828088141E-5</v>
+        <v>5.4819112902517906E-5</v>
       </c>
       <c r="L16">
-        <v>2.7708902116628509E-6</v>
+        <v>1.2319656962183874E-6</v>
       </c>
       <c r="M16">
-        <v>-2.0251895819155827E-5</v>
+        <v>-3.9959951092701654E-5</v>
       </c>
       <c r="N16">
-        <v>3.6050445477317722E-6</v>
+        <v>-4.3579487833981595E-5</v>
       </c>
       <c r="O16">
-        <v>2.8790942844971124E-5</v>
+        <v>2.740911322599926E-5</v>
       </c>
       <c r="P16">
-        <v>6.6945803799702734E-4</v>
+        <v>5.4219243725026323E-5</v>
       </c>
       <c r="Q16">
-        <v>9.0919696925045629E-4</v>
+        <v>3.7272277078617411E-3</v>
       </c>
       <c r="R16">
-        <v>-6.1870813755848504E-4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-4.1172076562624114E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>3</v>
       </c>
       <c r="B17">
-        <v>-4.2123778410144608</v>
+        <v>-5.4581725894825732</v>
       </c>
       <c r="C17">
-        <v>-1.6321105455625858E-3</v>
+        <v>-2.8675003921770294E-3</v>
       </c>
       <c r="D17">
-        <v>1.6852222283021417E-5</v>
+        <v>2.9905497144040133E-5</v>
       </c>
       <c r="E17">
-        <v>-8.045509535291661E-3</v>
+        <v>-1.3328555072557868E-2</v>
       </c>
       <c r="F17">
-        <v>-6.6369066943382116E-3</v>
+        <v>-1.0378133747098775E-2</v>
       </c>
       <c r="G17">
-        <v>1.7154989787195255E-4</v>
+        <v>2.851540945620351E-4</v>
       </c>
       <c r="H17">
-        <v>1.3443700185652437E-4</v>
+        <v>2.1571734513415713E-4</v>
       </c>
       <c r="I17">
-        <v>7.3233530796113638E-4</v>
+        <v>9.685122269941195E-4</v>
       </c>
       <c r="J17">
-        <v>1.1036651800808476E-3</v>
+        <v>2.924566870873222E-3</v>
       </c>
       <c r="K17">
-        <v>-2.5078519463427357E-3</v>
+        <v>-2.5648610532396362E-2</v>
       </c>
       <c r="L17">
-        <v>-1.8638491928052763E-2</v>
+        <v>-2.5823936510038913E-2</v>
       </c>
       <c r="M17">
-        <v>-1.8856007107679651E-2</v>
+        <v>-2.6227629444114744E-2</v>
       </c>
       <c r="N17">
-        <v>-1.9131985569891465E-2</v>
+        <v>-2.8397307697527019E-2</v>
       </c>
       <c r="O17">
-        <v>-2.0464114106240532E-2</v>
+        <v>-9.8480498202710453E-4</v>
       </c>
       <c r="P17">
-        <v>-5.6823211635214396E-4</v>
+        <v>-9.7636894331574802E-4</v>
       </c>
       <c r="Q17">
-        <v>-6.1870813755848504E-4</v>
+        <v>-4.1172076562624114E-4</v>
       </c>
       <c r="R17">
-        <v>5.618318527899404E-2</v>
+        <v>9.036301826941974E-2</v>
       </c>
     </row>
   </sheetData>
@@ -3707,19 +3713,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{287274D1-3866-4EF0-9DE7-D6181E6D59EB}">
   <dimension ref="A1:R17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="23.85546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" style="2" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="23.86328125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="19.73046875" style="2" customWidth="1"/>
+    <col min="3" max="16384" width="9.1328125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" t="s">
         <v>19</v>
-      </c>
-      <c r="B1" t="s">
-        <v>20</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -3734,19 +3740,19 @@
         <v>4</v>
       </c>
       <c r="G1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" t="s">
         <v>9</v>
-      </c>
-      <c r="H1" t="s">
-        <v>10</v>
       </c>
       <c r="I1" t="s">
         <v>7</v>
       </c>
       <c r="J1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" t="s">
         <v>12</v>
-      </c>
-      <c r="K1" t="s">
-        <v>8</v>
       </c>
       <c r="L1" t="s">
         <v>13</v>
@@ -3764,906 +3770,906 @@
         <v>17</v>
       </c>
       <c r="Q1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="R1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2">
-        <v>8.6202303753547593E-2</v>
+        <v>0.12720865421710068</v>
       </c>
       <c r="C2">
-        <v>6.3870270423670947E-5</v>
+        <v>1.1153080973005351E-4</v>
       </c>
       <c r="D2">
-        <v>-6.5243112127805002E-7</v>
+        <v>-1.1537985413591532E-6</v>
       </c>
       <c r="E2">
-        <v>3.2412903165935703E-4</v>
+        <v>5.292211160775836E-4</v>
       </c>
       <c r="F2">
-        <v>4.0870134245807175E-4</v>
+        <v>6.7852319123646785E-4</v>
       </c>
       <c r="G2">
-        <v>-7.2272867915517042E-6</v>
+        <v>-1.1678006236885946E-5</v>
       </c>
       <c r="H2">
-        <v>-9.1297108130513041E-6</v>
+        <v>-1.5118362483050954E-5</v>
       </c>
       <c r="I2">
-        <v>-3.2547377843146458E-5</v>
+        <v>-2.970189975275786E-5</v>
       </c>
       <c r="J2">
-        <v>-4.0387001455349558E-5</v>
+        <v>-1.2295771149021216E-4</v>
       </c>
       <c r="K2">
-        <v>8.4974148420205071E-6</v>
+        <v>-7.3089656121707669E-6</v>
       </c>
       <c r="L2">
-        <v>-9.2393128626455916E-6</v>
+        <v>-1.5276580710465873E-5</v>
       </c>
       <c r="M2">
-        <v>-1.7722852483142526E-5</v>
+        <v>-2.8435297296814602E-5</v>
       </c>
       <c r="N2">
-        <v>-3.0902379440253818E-5</v>
+        <v>3.1384791243555996E-5</v>
       </c>
       <c r="O2">
-        <v>1.2152529841430904E-5</v>
+        <v>-2.1841890148576881E-6</v>
       </c>
       <c r="P2">
-        <v>2.1481347739229437E-6</v>
+        <v>6.1640780045583254E-6</v>
       </c>
       <c r="Q2">
-        <v>8.1734365381689261E-6</v>
+        <v>2.1208562743559133E-5</v>
       </c>
       <c r="R2">
-        <v>-1.4087183286513388E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-2.4483841478452105E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3">
-        <v>-1.02932842063135E-3</v>
+        <v>-1.4575962054669514E-3</v>
       </c>
       <c r="C3">
-        <v>-6.5243112127805002E-7</v>
+        <v>-1.1537985413591532E-6</v>
       </c>
       <c r="D3">
-        <v>7.300603876469714E-9</v>
+        <v>1.2978744720721817E-8</v>
       </c>
       <c r="E3">
-        <v>-1.182291070193728E-6</v>
+        <v>-1.9776539476851904E-6</v>
       </c>
       <c r="F3">
-        <v>-2.099235847517097E-6</v>
+        <v>-3.5556560408391601E-6</v>
       </c>
       <c r="G3">
-        <v>2.4743657837924166E-8</v>
+        <v>4.1650769832714824E-8</v>
       </c>
       <c r="H3">
-        <v>4.5345124203471098E-8</v>
+        <v>7.8208789660386946E-8</v>
       </c>
       <c r="I3">
-        <v>1.9175430484149621E-7</v>
+        <v>1.4181228881716173E-8</v>
       </c>
       <c r="J3">
-        <v>5.4978754675856993E-7</v>
+        <v>1.6042937316210618E-6</v>
       </c>
       <c r="K3">
-        <v>-7.9035281097244285E-8</v>
+        <v>1.0996977292159709E-7</v>
       </c>
       <c r="L3">
-        <v>8.2218452617291619E-8</v>
+        <v>1.8705271156600982E-7</v>
       </c>
       <c r="M3">
-        <v>1.6573333884871471E-7</v>
+        <v>4.3749198867188072E-7</v>
       </c>
       <c r="N3">
-        <v>3.9297546229457309E-7</v>
+        <v>-2.6305327230516223E-8</v>
       </c>
       <c r="O3">
-        <v>1.2703387055540379E-8</v>
+        <v>9.7517832901967176E-9</v>
       </c>
       <c r="P3">
-        <v>-3.191408989754877E-8</v>
+        <v>-6.9698550982882291E-8</v>
       </c>
       <c r="Q3">
-        <v>-8.6788219579794393E-8</v>
+        <v>-2.7107965348503815E-7</v>
       </c>
       <c r="R3">
-        <v>1.3075498575651646E-5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+        <v>2.3107281941569843E-5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4">
-        <v>2.3562767401524166E-2</v>
+        <v>-4.5632204264978569E-2</v>
       </c>
       <c r="C4">
-        <v>3.2412903165935703E-4</v>
+        <v>5.292211160775836E-4</v>
       </c>
       <c r="D4">
-        <v>-1.182291070193728E-6</v>
+        <v>-1.9776539476851904E-6</v>
       </c>
       <c r="E4">
-        <v>1.2664934883282583E-2</v>
+        <v>2.0573709430668219E-2</v>
       </c>
       <c r="F4">
-        <v>1.0619694189834985E-2</v>
+        <v>1.72471452870393E-2</v>
       </c>
       <c r="G4">
-        <v>-2.7172063387433451E-4</v>
+        <v>-4.3535325547473021E-4</v>
       </c>
       <c r="H4">
-        <v>-2.2803256913286229E-4</v>
+        <v>-3.6575486105139759E-4</v>
       </c>
       <c r="I4">
-        <v>4.7406993558328601E-5</v>
+        <v>8.5434505501953158E-5</v>
       </c>
       <c r="J4">
-        <v>-2.0137252551615526E-4</v>
+        <v>-2.3372214604045052E-4</v>
       </c>
       <c r="K4">
-        <v>1.393614379076238E-4</v>
+        <v>1.7789411862583707E-4</v>
       </c>
       <c r="L4">
-        <v>-4.3887495888677609E-5</v>
+        <v>5.0594820844262513E-5</v>
       </c>
       <c r="M4">
-        <v>-1.4809025360811631E-4</v>
+        <v>-9.6358046068047327E-5</v>
       </c>
       <c r="N4">
-        <v>-1.9570848811492191E-4</v>
+        <v>2.2467893025046332E-4</v>
       </c>
       <c r="O4">
-        <v>-8.5895010958281053E-5</v>
+        <v>-2.5400756610220905E-4</v>
       </c>
       <c r="P4">
-        <v>-1.5334698222548346E-4</v>
+        <v>-2.3522823903594222E-4</v>
       </c>
       <c r="Q4">
-        <v>-1.1527795402893314E-4</v>
+        <v>1.0806845340908015E-4</v>
       </c>
       <c r="R4">
-        <v>-1.20575732975589E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-2.0103855978975023E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>-0.64578349617790709</v>
+        <v>-0.86104932666260858</v>
       </c>
       <c r="C5">
-        <v>4.0870134245807175E-4</v>
+        <v>6.7852319123646785E-4</v>
       </c>
       <c r="D5">
-        <v>-2.099235847517097E-6</v>
+        <v>-3.5556560408391601E-6</v>
       </c>
       <c r="E5">
-        <v>1.0619694189834985E-2</v>
+        <v>1.72471452870393E-2</v>
       </c>
       <c r="F5">
-        <v>2.1444712081840327E-2</v>
+        <v>3.4279483265859577E-2</v>
       </c>
       <c r="G5">
-        <v>-2.2819279015536006E-4</v>
+        <v>-3.6519973010068138E-4</v>
       </c>
       <c r="H5">
-        <v>-4.651091975973216E-4</v>
+        <v>-7.380756492080102E-4</v>
       </c>
       <c r="I5">
-        <v>-7.5030464865235097E-5</v>
+        <v>-1.7666366003977858E-4</v>
       </c>
       <c r="J5">
-        <v>-3.7229533327480578E-4</v>
+        <v>-4.8845128090811219E-4</v>
       </c>
       <c r="K5">
-        <v>8.3516060487565211E-5</v>
+        <v>5.9895693162018409E-4</v>
       </c>
       <c r="L5">
-        <v>1.3630436341688541E-4</v>
+        <v>3.3647306042407146E-4</v>
       </c>
       <c r="M5">
-        <v>-3.6833780042395264E-5</v>
+        <v>2.2963155423698887E-4</v>
       </c>
       <c r="N5">
-        <v>-1.0346245973351723E-4</v>
+        <v>8.8489719203771293E-4</v>
       </c>
       <c r="O5">
-        <v>1.4049486863351637E-4</v>
+        <v>-1.7975201920246875E-4</v>
       </c>
       <c r="P5">
-        <v>-1.4106631261330693E-4</v>
+        <v>-1.881971516892555E-4</v>
       </c>
       <c r="Q5">
-        <v>-1.0020977904269616E-4</v>
+        <v>4.0837503960346384E-6</v>
       </c>
       <c r="R5">
-        <v>-1.3881236120587585E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-2.3586525274693296E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>1.8242696352029971E-3</v>
+      </c>
+      <c r="C6">
+        <v>-1.1678006236885946E-5</v>
+      </c>
+      <c r="D6">
+        <v>4.1650769832714824E-8</v>
+      </c>
+      <c r="E6">
+        <v>-4.3535325547473021E-4</v>
+      </c>
+      <c r="F6">
+        <v>-3.6519973010068138E-4</v>
+      </c>
+      <c r="G6">
+        <v>9.9007495055338699E-6</v>
+      </c>
+      <c r="H6">
+        <v>8.3120329901776684E-6</v>
+      </c>
+      <c r="I6">
+        <v>-1.6036537416044963E-6</v>
+      </c>
+      <c r="J6">
+        <v>6.1482698914884629E-6</v>
+      </c>
+      <c r="K6">
+        <v>-6.0830283499899065E-6</v>
+      </c>
+      <c r="L6">
+        <v>-2.3179006153353451E-6</v>
+      </c>
+      <c r="M6">
+        <v>3.3557652164308536E-6</v>
+      </c>
+      <c r="N6">
+        <v>-1.2699107549425225E-6</v>
+      </c>
+      <c r="O6">
+        <v>9.8366461349245973E-7</v>
+      </c>
+      <c r="P6">
+        <v>9.7757585494703074E-7</v>
+      </c>
+      <c r="Q6">
+        <v>-3.4493323826957822E-6</v>
+      </c>
+      <c r="R6">
+        <v>4.2455279019085722E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
         <v>9</v>
       </c>
-      <c r="B6">
-        <v>-8.4332282230374666E-4</v>
-      </c>
-      <c r="C6">
-        <v>-7.2272867915517042E-6</v>
-      </c>
-      <c r="D6">
-        <v>2.4743657837924166E-8</v>
-      </c>
-      <c r="E6">
-        <v>-2.7172063387433451E-4</v>
-      </c>
-      <c r="F6">
-        <v>-2.2819279015536006E-4</v>
-      </c>
-      <c r="G6">
-        <v>6.2505031219547191E-6</v>
-      </c>
-      <c r="H6">
-        <v>5.2464981717751536E-6</v>
-      </c>
-      <c r="I6">
-        <v>-5.2024574800919671E-7</v>
-      </c>
-      <c r="J6">
-        <v>4.407393536779885E-6</v>
-      </c>
-      <c r="K6">
-        <v>-4.0642198592018532E-6</v>
-      </c>
-      <c r="L6">
-        <v>9.65608970357175E-7</v>
-      </c>
-      <c r="M6">
-        <v>3.8908610140461715E-6</v>
-      </c>
-      <c r="N6">
-        <v>6.1194540076434377E-6</v>
-      </c>
-      <c r="O6">
-        <v>4.8301945640284418E-6</v>
-      </c>
-      <c r="P6">
-        <v>8.4788966855237874E-7</v>
-      </c>
-      <c r="Q6">
-        <v>2.5525066676766119E-7</v>
-      </c>
-      <c r="R6">
-        <v>2.5688971663025649E-4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
       <c r="B7">
-        <v>9.6350645601530095E-3</v>
+        <v>1.3509655535622203E-2</v>
       </c>
       <c r="C7">
-        <v>-9.1297108130513041E-6</v>
+        <v>-1.5118362483050954E-5</v>
       </c>
       <c r="D7">
-        <v>4.5345124203471098E-8</v>
+        <v>7.8208789660386946E-8</v>
       </c>
       <c r="E7">
-        <v>-2.2803256913286229E-4</v>
+        <v>-3.6575486105139759E-4</v>
       </c>
       <c r="F7">
-        <v>-4.651091975973216E-4</v>
+        <v>-7.380756492080102E-4</v>
       </c>
       <c r="G7">
-        <v>5.2464981717751536E-6</v>
+        <v>8.3120329901776684E-6</v>
       </c>
       <c r="H7">
-        <v>1.0859721962282748E-5</v>
+        <v>1.7120337126428389E-5</v>
       </c>
       <c r="I7">
-        <v>3.0340641067149135E-6</v>
+        <v>5.0541736961544456E-6</v>
       </c>
       <c r="J7">
-        <v>6.3720325236428756E-6</v>
+        <v>9.480654663401974E-6</v>
       </c>
       <c r="K7">
-        <v>-3.8755393446306126E-6</v>
+        <v>-1.7519852593323354E-5</v>
       </c>
       <c r="L7">
-        <v>-3.5831864102675077E-6</v>
+        <v>-8.2385285952475001E-6</v>
       </c>
       <c r="M7">
-        <v>1.8971812953018493E-6</v>
+        <v>-2.4480805110979251E-6</v>
       </c>
       <c r="N7">
-        <v>5.435267808649922E-6</v>
+        <v>-1.3217495158695858E-5</v>
       </c>
       <c r="O7">
-        <v>1.6968265440685997E-6</v>
+        <v>-9.1097592598350188E-7</v>
       </c>
       <c r="P7">
-        <v>1.9688965621162179E-7</v>
+        <v>-1.2122219056883042E-6</v>
       </c>
       <c r="Q7">
-        <v>-8.7138031752735286E-7</v>
+        <v>-1.7328183545869865E-6</v>
       </c>
       <c r="R7">
-        <v>2.9723814330323892E-4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+        <v>5.0348902261089447E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.55965625582030332</v>
+        <v>0.16218469858014337</v>
       </c>
       <c r="C8">
-        <v>-3.2547377843146458E-5</v>
+        <v>-2.970189975275786E-5</v>
       </c>
       <c r="D8">
-        <v>1.9175430484149621E-7</v>
+        <v>1.4181228881716173E-8</v>
       </c>
       <c r="E8">
-        <v>4.7406993558328601E-5</v>
+        <v>8.5434505501953158E-5</v>
       </c>
       <c r="F8">
-        <v>-7.5030464865235097E-5</v>
+        <v>-1.7666366003977858E-4</v>
       </c>
       <c r="G8">
-        <v>-5.2024574800919671E-7</v>
+        <v>-1.6036537416044963E-6</v>
       </c>
       <c r="H8">
-        <v>3.0340641067149135E-6</v>
+        <v>5.0541736961544456E-6</v>
       </c>
       <c r="I8">
-        <v>7.7155605501930558E-4</v>
+        <v>1.4711591707290822E-3</v>
       </c>
       <c r="J8">
-        <v>-3.4636828994617536E-4</v>
+        <v>-7.869595262910375E-4</v>
       </c>
       <c r="K8">
-        <v>-3.4092172529602589E-5</v>
+        <v>1.30451211121232E-4</v>
       </c>
       <c r="L8">
-        <v>8.5916091035933087E-5</v>
+        <v>1.1247580307965785E-4</v>
       </c>
       <c r="M8">
-        <v>6.5573049203160132E-5</v>
+        <v>9.3653435233481463E-5</v>
       </c>
       <c r="N8">
-        <v>6.9846197270008524E-5</v>
+        <v>1.4294985330686223E-4</v>
       </c>
       <c r="O8">
-        <v>8.0520769629509694E-5</v>
+        <v>3.1945383379322319E-6</v>
       </c>
       <c r="P8">
-        <v>-3.5724152791381781E-6</v>
+        <v>-3.6538811385585051E-5</v>
       </c>
       <c r="Q8">
-        <v>-3.4616149440854319E-5</v>
+        <v>7.0038946951474492E-5</v>
       </c>
       <c r="R8">
-        <v>6.1905793652870767E-4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+        <v>4.4056376662862732E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <v>3.7719230802749193E-2</v>
+      </c>
+      <c r="C9">
+        <v>-1.2295771149021216E-4</v>
+      </c>
+      <c r="D9">
+        <v>1.6042937316210618E-6</v>
+      </c>
+      <c r="E9">
+        <v>-2.3372214604045052E-4</v>
+      </c>
+      <c r="F9">
+        <v>-4.8845128090811219E-4</v>
+      </c>
+      <c r="G9">
+        <v>6.1482698914884629E-6</v>
+      </c>
+      <c r="H9">
+        <v>9.480654663401974E-6</v>
+      </c>
+      <c r="I9">
+        <v>-7.869595262910375E-4</v>
+      </c>
+      <c r="J9">
+        <v>1.5514120766675955E-3</v>
+      </c>
+      <c r="K9">
+        <v>5.0538771229066974E-5</v>
+      </c>
+      <c r="L9">
+        <v>1.9228052371415621E-5</v>
+      </c>
+      <c r="M9">
+        <v>5.9805891836788895E-7</v>
+      </c>
+      <c r="N9">
+        <v>3.4565714879205059E-5</v>
+      </c>
+      <c r="O9">
+        <v>-1.8552032417175831E-5</v>
+      </c>
+      <c r="P9">
+        <v>-3.0434076236871742E-5</v>
+      </c>
+      <c r="Q9">
+        <v>-5.1903182124989929E-5</v>
+      </c>
+      <c r="R9">
+        <v>2.1234088483335655E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
         <v>12</v>
       </c>
-      <c r="B9">
-        <v>-0.21793231469482144</v>
-      </c>
-      <c r="C9">
-        <v>-4.0387001455349558E-5</v>
-      </c>
-      <c r="D9">
-        <v>5.4978754675856993E-7</v>
-      </c>
-      <c r="E9">
-        <v>-2.0137252551615526E-4</v>
-      </c>
-      <c r="F9">
-        <v>-3.7229533327480578E-4</v>
-      </c>
-      <c r="G9">
-        <v>4.407393536779885E-6</v>
-      </c>
-      <c r="H9">
-        <v>6.3720325236428756E-6</v>
-      </c>
-      <c r="I9">
-        <v>-3.4636828994617536E-4</v>
-      </c>
-      <c r="J9">
-        <v>7.2292027796990485E-4</v>
-      </c>
-      <c r="K9">
-        <v>2.9035521251542975E-5</v>
-      </c>
-      <c r="L9">
-        <v>-3.6894990315287771E-5</v>
-      </c>
-      <c r="M9">
-        <v>-3.8929411697125982E-5</v>
-      </c>
-      <c r="N9">
-        <v>-5.0989985708779718E-5</v>
-      </c>
-      <c r="O9">
-        <v>-4.8274318898793418E-5</v>
-      </c>
-      <c r="P9">
-        <v>-1.1195026956656622E-5</v>
-      </c>
-      <c r="Q9">
-        <v>-2.0112442527853019E-5</v>
-      </c>
-      <c r="R9">
-        <v>6.6343801497852702E-4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>8</v>
-      </c>
       <c r="B10">
-        <v>-1.8034893584637397</v>
+        <v>0.28461421399898768</v>
       </c>
       <c r="C10">
-        <v>8.4974148420205071E-6</v>
+        <v>-7.3089656121707669E-6</v>
       </c>
       <c r="D10">
-        <v>-7.9035281097244285E-8</v>
+        <v>1.0996977292159709E-7</v>
       </c>
       <c r="E10">
-        <v>1.393614379076238E-4</v>
+        <v>1.7789411862583707E-4</v>
       </c>
       <c r="F10">
-        <v>8.3516060487565211E-5</v>
+        <v>5.9895693162018409E-4</v>
       </c>
       <c r="G10">
-        <v>-4.0642198592018532E-6</v>
+        <v>-6.0830283499899065E-6</v>
       </c>
       <c r="H10">
-        <v>-3.8755393446306126E-6</v>
+        <v>-1.7519852593323354E-5</v>
       </c>
       <c r="I10">
-        <v>-3.4092172529602589E-5</v>
+        <v>1.30451211121232E-4</v>
       </c>
       <c r="J10">
-        <v>2.9035521251542975E-5</v>
+        <v>5.0538771229066974E-5</v>
       </c>
       <c r="K10">
-        <v>1.2535085389610016E-2</v>
+        <v>3.0017343986842648E-2</v>
       </c>
       <c r="L10">
-        <v>6.4113088199739467E-4</v>
+        <v>2.6227231594993784E-2</v>
       </c>
       <c r="M10">
-        <v>1.773018955508571E-3</v>
+        <v>2.618660514630201E-2</v>
       </c>
       <c r="N10">
-        <v>1.9371097687477144E-3</v>
+        <v>2.6167030994803019E-2</v>
       </c>
       <c r="O10">
-        <v>1.915080660766651E-3</v>
+        <v>-8.5590652280930033E-5</v>
       </c>
       <c r="P10">
-        <v>-2.2622541980037467E-5</v>
+        <v>-1.9808607909128207E-4</v>
       </c>
       <c r="Q10">
-        <v>-2.7175779574259259E-5</v>
+        <v>6.1429457743990604E-7</v>
       </c>
       <c r="R10">
-        <v>-2.1014895049823994E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-2.5988676741413676E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>13</v>
       </c>
       <c r="B11">
-        <v>0.20897451199705794</v>
+        <v>0.68625659460068877</v>
       </c>
       <c r="C11">
-        <v>-9.2393128626455916E-6</v>
+        <v>-1.5276580710465873E-5</v>
       </c>
       <c r="D11">
-        <v>8.2218452617291619E-8</v>
+        <v>1.8705271156600982E-7</v>
       </c>
       <c r="E11">
-        <v>-4.3887495888677609E-5</v>
+        <v>5.0594820844262513E-5</v>
       </c>
       <c r="F11">
-        <v>1.3630436341688541E-4</v>
+        <v>3.3647306042407146E-4</v>
       </c>
       <c r="G11">
-        <v>9.65608970357175E-7</v>
+        <v>-2.3179006153353451E-6</v>
       </c>
       <c r="H11">
-        <v>-3.5831864102675077E-6</v>
+        <v>-8.2385285952475001E-6</v>
       </c>
       <c r="I11">
-        <v>8.5916091035933087E-5</v>
+        <v>1.1247580307965785E-4</v>
       </c>
       <c r="J11">
-        <v>-3.6894990315287771E-5</v>
+        <v>1.9228052371415621E-5</v>
       </c>
       <c r="K11">
-        <v>6.4113088199739467E-4</v>
+        <v>2.6227231594993784E-2</v>
       </c>
       <c r="L11">
-        <v>2.7145899790468581E-2</v>
+        <v>2.6993069109755439E-2</v>
       </c>
       <c r="M11">
-        <v>2.416632024807883E-2</v>
+        <v>2.6207885502623218E-2</v>
       </c>
       <c r="N11">
-        <v>2.417284025222096E-2</v>
+        <v>2.6207442797508588E-2</v>
       </c>
       <c r="O11">
-        <v>2.4164779484611987E-2</v>
+        <v>-2.2272572685332824E-5</v>
       </c>
       <c r="P11">
-        <v>-4.3511745447819775E-5</v>
+        <v>-1.6103112843012982E-4</v>
       </c>
       <c r="Q11">
-        <v>-1.2451458129297173E-4</v>
+        <v>-2.6262388426841324E-5</v>
       </c>
       <c r="R11">
-        <v>-2.3895083698823417E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-2.5876145475329234E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>14</v>
       </c>
       <c r="B12">
-        <v>0.37045912590376845</v>
+        <v>0.85327973552441561</v>
       </c>
       <c r="C12">
-        <v>-1.7722852483142526E-5</v>
+        <v>-2.8435297296814602E-5</v>
       </c>
       <c r="D12">
-        <v>1.6573333884871471E-7</v>
+        <v>4.3749198867188072E-7</v>
       </c>
       <c r="E12">
-        <v>-1.4809025360811631E-4</v>
+        <v>-9.6358046068047327E-5</v>
       </c>
       <c r="F12">
-        <v>-3.6833780042395264E-5</v>
+        <v>2.2963155423698887E-4</v>
       </c>
       <c r="G12">
-        <v>3.8908610140461715E-6</v>
+        <v>3.3557652164308536E-6</v>
       </c>
       <c r="H12">
-        <v>1.8971812953018493E-6</v>
+        <v>-2.4480805110979251E-6</v>
       </c>
       <c r="I12">
-        <v>6.5573049203160132E-5</v>
+        <v>9.3653435233481463E-5</v>
       </c>
       <c r="J12">
-        <v>-3.8929411697125982E-5</v>
+        <v>5.9805891836788895E-7</v>
       </c>
       <c r="K12">
-        <v>1.773018955508571E-3</v>
+        <v>2.618660514630201E-2</v>
       </c>
       <c r="L12">
-        <v>2.416632024807883E-2</v>
+        <v>2.6207885502623218E-2</v>
       </c>
       <c r="M12">
-        <v>2.4855854064682638E-2</v>
+        <v>2.6670950281781874E-2</v>
       </c>
       <c r="N12">
-        <v>2.4375594604409627E-2</v>
+        <v>2.6434664048651513E-2</v>
       </c>
       <c r="O12">
-        <v>2.4373320669575978E-2</v>
+        <v>-4.2999207208603465E-5</v>
       </c>
       <c r="P12">
-        <v>-3.0101589347229698E-5</v>
+        <v>-1.6069875271365651E-4</v>
       </c>
       <c r="Q12">
-        <v>-1.2528619834091724E-4</v>
+        <v>-4.4609874328044541E-5</v>
       </c>
       <c r="R12">
-        <v>-2.3912419704164009E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-2.5981243346811452E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>15</v>
       </c>
       <c r="B13">
-        <v>0.37477684048021226</v>
+        <v>0.93071159153555294</v>
       </c>
       <c r="C13">
-        <v>-3.0902379440253818E-5</v>
+        <v>3.1384791243555996E-5</v>
       </c>
       <c r="D13">
-        <v>3.9297546229457309E-7</v>
+        <v>-2.6305327230516223E-8</v>
       </c>
       <c r="E13">
-        <v>-1.9570848811492191E-4</v>
+        <v>2.2467893025046332E-4</v>
       </c>
       <c r="F13">
-        <v>-1.0346245973351723E-4</v>
+        <v>8.8489719203771293E-4</v>
       </c>
       <c r="G13">
-        <v>6.1194540076434377E-6</v>
+        <v>-1.2699107549425225E-6</v>
       </c>
       <c r="H13">
-        <v>5.435267808649922E-6</v>
+        <v>-1.3217495158695858E-5</v>
       </c>
       <c r="I13">
-        <v>6.9846197270008524E-5</v>
+        <v>1.4294985330686223E-4</v>
       </c>
       <c r="J13">
-        <v>-5.0989985708779718E-5</v>
+        <v>3.4565714879205059E-5</v>
       </c>
       <c r="K13">
-        <v>1.9371097687477144E-3</v>
+        <v>2.6167030994803019E-2</v>
       </c>
       <c r="L13">
-        <v>2.417284025222096E-2</v>
+        <v>2.6207442797508588E-2</v>
       </c>
       <c r="M13">
-        <v>2.4375594604409627E-2</v>
+        <v>2.6434664048651513E-2</v>
       </c>
       <c r="N13">
-        <v>2.4699587133598013E-2</v>
+        <v>2.7739771674771495E-2</v>
       </c>
       <c r="O13">
-        <v>2.4571768072977312E-2</v>
+        <v>1.3533615118948921E-5</v>
       </c>
       <c r="P13">
-        <v>-3.4759765935937894E-5</v>
+        <v>-9.8436638499224227E-5</v>
       </c>
       <c r="Q13">
-        <v>-1.1518681715978285E-4</v>
+        <v>-4.0234747877882881E-5</v>
       </c>
       <c r="R13">
-        <v>-2.3968829803228911E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-2.7957684441060806E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>16</v>
       </c>
       <c r="B14">
-        <v>0.66536599311032674</v>
+        <v>-1.0703874171378511E-2</v>
       </c>
       <c r="C14">
-        <v>1.2152529841430904E-5</v>
+        <v>-2.1841890148576881E-6</v>
       </c>
       <c r="D14">
-        <v>1.2703387055540379E-8</v>
+        <v>9.7517832901967176E-9</v>
       </c>
       <c r="E14">
-        <v>-8.5895010958281053E-5</v>
+        <v>-2.5400756610220905E-4</v>
       </c>
       <c r="F14">
-        <v>1.4049486863351637E-4</v>
+        <v>-1.7975201920246875E-4</v>
       </c>
       <c r="G14">
-        <v>4.8301945640284418E-6</v>
+        <v>9.8366461349245973E-7</v>
       </c>
       <c r="H14">
-        <v>1.6968265440685997E-6</v>
+        <v>-9.1097592598350188E-7</v>
       </c>
       <c r="I14">
-        <v>8.0520769629509694E-5</v>
+        <v>3.1945383379322319E-6</v>
       </c>
       <c r="J14">
-        <v>-4.8274318898793418E-5</v>
+        <v>-1.8552032417175831E-5</v>
       </c>
       <c r="K14">
-        <v>1.915080660766651E-3</v>
+        <v>-8.5590652280930033E-5</v>
       </c>
       <c r="L14">
-        <v>2.4164779484611987E-2</v>
+        <v>-2.2272572685332824E-5</v>
       </c>
       <c r="M14">
-        <v>2.4373320669575978E-2</v>
+        <v>-4.2999207208603465E-5</v>
       </c>
       <c r="N14">
-        <v>2.4571768072977312E-2</v>
+        <v>1.3533615118948921E-5</v>
       </c>
       <c r="O14">
-        <v>2.5421596730853108E-2</v>
+        <v>1.7255604901343141E-3</v>
       </c>
       <c r="P14">
-        <v>-2.3811409742752795E-6</v>
+        <v>1.1086557368587234E-3</v>
       </c>
       <c r="Q14">
-        <v>-7.9082329404998788E-5</v>
+        <v>-2.1725078401831019E-6</v>
       </c>
       <c r="R14">
-        <v>-2.5215331870324677E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-8.1752704419772119E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>17</v>
       </c>
       <c r="B15">
-        <v>-4.3262044104285427E-2</v>
+        <v>-4.1844115104036406E-2</v>
       </c>
       <c r="C15">
-        <v>2.1481347739229437E-6</v>
+        <v>6.1640780045583254E-6</v>
       </c>
       <c r="D15">
-        <v>-3.191408989754877E-8</v>
+        <v>-6.9698550982882291E-8</v>
       </c>
       <c r="E15">
-        <v>-1.5334698222548346E-4</v>
+        <v>-2.3522823903594222E-4</v>
       </c>
       <c r="F15">
-        <v>-1.4106631261330693E-4</v>
+        <v>-1.881971516892555E-4</v>
       </c>
       <c r="G15">
-        <v>8.4788966855237874E-7</v>
+        <v>9.7757585494703074E-7</v>
       </c>
       <c r="H15">
-        <v>1.9688965621162179E-7</v>
+        <v>-1.2122219056883042E-6</v>
       </c>
       <c r="I15">
-        <v>-3.5724152791381781E-6</v>
+        <v>-3.6538811385585051E-5</v>
       </c>
       <c r="J15">
-        <v>-1.1195026956656622E-5</v>
+        <v>-3.0434076236871742E-5</v>
       </c>
       <c r="K15">
-        <v>-2.2622541980037467E-5</v>
+        <v>-1.9808607909128207E-4</v>
       </c>
       <c r="L15">
-        <v>-4.3511745447819775E-5</v>
+        <v>-1.6103112843012982E-4</v>
       </c>
       <c r="M15">
-        <v>-3.0101589347229698E-5</v>
+        <v>-1.6069875271365651E-4</v>
       </c>
       <c r="N15">
-        <v>-3.4759765935937894E-5</v>
+        <v>-9.8436638499224227E-5</v>
       </c>
       <c r="O15">
-        <v>-2.3811409742752795E-6</v>
+        <v>1.1086557368587234E-3</v>
       </c>
       <c r="P15">
-        <v>1.023233342379744E-3</v>
+        <v>1.456048132104454E-3</v>
       </c>
       <c r="Q15">
-        <v>6.5932664982538936E-4</v>
+        <v>-3.7581999867306333E-6</v>
       </c>
       <c r="R15">
-        <v>-5.5026768546349207E-4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-8.7980687324734803E-4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B16">
-        <v>-3.6201205600387788E-2</v>
+        <v>0.27892753135497234</v>
       </c>
       <c r="C16">
-        <v>8.1734365381689261E-6</v>
+        <v>2.1208562743559133E-5</v>
       </c>
       <c r="D16">
-        <v>-8.6788219579794393E-8</v>
+        <v>-2.7107965348503815E-7</v>
       </c>
       <c r="E16">
-        <v>-1.1527795402893314E-4</v>
+        <v>1.0806845340908015E-4</v>
       </c>
       <c r="F16">
-        <v>-1.0020977904269616E-4</v>
+        <v>4.0837503960346384E-6</v>
       </c>
       <c r="G16">
-        <v>2.5525066676766119E-7</v>
+        <v>-3.4493323826957822E-6</v>
       </c>
       <c r="H16">
-        <v>-8.7138031752735286E-7</v>
+        <v>-1.7328183545869865E-6</v>
       </c>
       <c r="I16">
-        <v>-3.4616149440854319E-5</v>
+        <v>7.0038946951474492E-5</v>
       </c>
       <c r="J16">
-        <v>-2.0112442527853019E-5</v>
+        <v>-5.1903182124989929E-5</v>
       </c>
       <c r="K16">
-        <v>-2.7175779574259259E-5</v>
+        <v>6.1429457743990604E-7</v>
       </c>
       <c r="L16">
-        <v>-1.2451458129297173E-4</v>
+        <v>-2.6262388426841324E-5</v>
       </c>
       <c r="M16">
-        <v>-1.2528619834091724E-4</v>
+        <v>-4.4609874328044541E-5</v>
       </c>
       <c r="N16">
-        <v>-1.1518681715978285E-4</v>
+        <v>-4.0234747877882881E-5</v>
       </c>
       <c r="O16">
-        <v>-7.9082329404998788E-5</v>
+        <v>-2.1725078401831019E-6</v>
       </c>
       <c r="P16">
-        <v>6.5932664982538936E-4</v>
+        <v>-3.7581999867306333E-6</v>
       </c>
       <c r="Q16">
-        <v>8.7728845160220783E-4</v>
+        <v>3.7438767739455137E-3</v>
       </c>
       <c r="R16">
-        <v>-6.0589237474363187E-4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+        <v>-5.1232994444973983E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>3</v>
       </c>
       <c r="B17">
-        <v>-1.2086141112023341</v>
+        <v>-2.2559630131276682</v>
       </c>
       <c r="C17">
-        <v>-1.4087183286513388E-3</v>
+        <v>-2.4483841478452105E-3</v>
       </c>
       <c r="D17">
-        <v>1.3075498575651646E-5</v>
+        <v>2.3107281941569843E-5</v>
       </c>
       <c r="E17">
-        <v>-1.20575732975589E-2</v>
+        <v>-2.0103855978975023E-2</v>
       </c>
       <c r="F17">
-        <v>-1.3881236120587585E-2</v>
+        <v>-2.3586525274693296E-2</v>
       </c>
       <c r="G17">
-        <v>2.5688971663025649E-4</v>
+        <v>4.2455279019085722E-4</v>
       </c>
       <c r="H17">
-        <v>2.9723814330323892E-4</v>
+        <v>5.0348902261089447E-4</v>
       </c>
       <c r="I17">
-        <v>6.1905793652870767E-4</v>
+        <v>4.4056376662862732E-4</v>
       </c>
       <c r="J17">
-        <v>6.6343801497852702E-4</v>
+        <v>2.1234088483335655E-3</v>
       </c>
       <c r="K17">
-        <v>-2.1014895049823994E-3</v>
+        <v>-2.5988676741413676E-2</v>
       </c>
       <c r="L17">
-        <v>-2.3895083698823417E-2</v>
+        <v>-2.5876145475329234E-2</v>
       </c>
       <c r="M17">
-        <v>-2.3912419704164009E-2</v>
+        <v>-2.5981243346811452E-2</v>
       </c>
       <c r="N17">
-        <v>-2.3968829803228911E-2</v>
+        <v>-2.7957684441060806E-2</v>
       </c>
       <c r="O17">
-        <v>-2.5215331870324677E-2</v>
+        <v>-8.1752704419772119E-4</v>
       </c>
       <c r="P17">
-        <v>-5.5026768546349207E-4</v>
+        <v>-8.7980687324734803E-4</v>
       </c>
       <c r="Q17">
-        <v>-6.0589237474363187E-4</v>
+        <v>-5.1232994444973983E-4</v>
       </c>
       <c r="R17">
-        <v>5.9439481936509247E-2</v>
+        <v>8.6858909566368214E-2</v>
       </c>
     </row>
   </sheetData>

--- a/input/reg_employmentSelection.xlsx
+++ b/input/reg_employmentSelection.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF100000-47FA-41D0-B6CE-DC4DB0B384D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F2A70B-FB9E-4718-A0BF-5440B701C9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" tabRatio="904" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" tabRatio="904" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -113,21 +113,6 @@
     <t>Deh_c3_Low_Dag</t>
   </si>
   <si>
-    <t>IT_EmploymentSelection_FemaleNE</t>
-  </si>
-  <si>
-    <t>IT_EmploymentSelection_MaleNE</t>
-  </si>
-  <si>
-    <t>IT_EmploymentSelection_FemaleE</t>
-  </si>
-  <si>
-    <t>IT_EmploymentSelection_MaleE</t>
-  </si>
-  <si>
-    <t>Regions: ITF = South, ITG = Islands, ITH = Northeast, ITI = Central. Northwest (ITC) is the omitted region.</t>
-  </si>
-  <si>
     <t>ITF</t>
   </si>
   <si>
@@ -138,6 +123,21 @@
   </si>
   <si>
     <t>ITI</t>
+  </si>
+  <si>
+    <t>EL_EmploymentSelection_FemaleNE</t>
+  </si>
+  <si>
+    <t>EL_EmploymentSelection_MaleNE</t>
+  </si>
+  <si>
+    <t>EL_EmploymentSelection_FemaleE</t>
+  </si>
+  <si>
+    <t>EL_EmploymentSelection_MaleE</t>
+  </si>
+  <si>
+    <t>Regions: EL3 = Attika (omitted), EL4 = Aegean Islands, EL7 = Central and Northern Greece</t>
   </si>
 </sst>
 </file>
@@ -527,9 +527,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -537,7 +537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -545,39 +545,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>6</v>
       </c>
@@ -585,22 +585,22 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
         <v>10</v>
       </c>
@@ -613,13 +613,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5440224-65B9-42C3-BDF1-EC73DB722098}">
   <dimension ref="A1:V21"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.9296875" style="2" customWidth="1"/>
-    <col min="2" max="16384" width="9.06640625" style="2"/>
+    <col min="1" max="1" width="23" style="2" customWidth="1"/>
+    <col min="2" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -666,16 +666,16 @@
         <v>23</v>
       </c>
       <c r="P1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="Q1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="R1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="S1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="T1" t="s">
         <v>24</v>
@@ -687,7 +687,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -755,7 +755,7 @@
         <v>1.7248638636402369E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -823,7 +823,7 @@
         <v>-1.0949341663041032E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -891,7 +891,7 @@
         <v>1.0811166992187685E-5</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -959,7 +959,7 @@
         <v>-7.9092310393618689E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -1027,7 +1027,7 @@
         <v>-7.5302828888323186E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -1095,7 +1095,7 @@
         <v>1.7931262215968425E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -1163,7 +1163,7 @@
         <v>1.6624589291442966E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>5.9218191460279508E-4</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -1299,7 +1299,7 @@
         <v>1.3550557304967494E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -1367,7 +1367,7 @@
         <v>-2.8705309677373732E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -1435,7 +1435,7 @@
         <v>-2.8903065279276982E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>-2.9067148530632813E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -1571,9 +1571,9 @@
         <v>-2.9452246561758398E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B15">
         <v>-0.26786040980057807</v>
@@ -1639,9 +1639,9 @@
         <v>-2.1542445107446186E-4</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B16">
         <v>-0.35286588340456737</v>
@@ -1707,9 +1707,9 @@
         <v>-1.7349226236123026E-4</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B17">
         <v>0.11105600720176947</v>
@@ -1775,9 +1775,9 @@
         <v>-5.7456784469772507E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B18">
         <v>1.0630422478857995E-2</v>
@@ -1843,7 +1843,7 @@
         <v>-3.97230615542016E-4</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -1911,7 +1911,7 @@
         <v>-2.7972814222336625E-4</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -1979,7 +1979,7 @@
         <v>-1.5803694773224814E-4</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -2055,12 +2055,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D773F3FA-C4BA-4705-8D71-D1937FA78488}">
   <dimension ref="A1:V21"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="9.06640625" style="2"/>
+    <col min="1" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -2107,16 +2107,16 @@
         <v>23</v>
       </c>
       <c r="P1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="Q1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="R1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="S1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="T1" t="s">
         <v>24</v>
@@ -2128,7 +2128,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -2196,7 +2196,7 @@
         <v>2.1135761796003765E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -2264,7 +2264,7 @@
         <v>-1.2135338648586232E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -2332,7 +2332,7 @@
         <v>1.1492040000878157E-5</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -2400,7 +2400,7 @@
         <v>-1.1369411803076617E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -2468,7 +2468,7 @@
         <v>-1.1473974449422114E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -2536,7 +2536,7 @@
         <v>2.4707410183791111E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -2604,7 +2604,7 @@
         <v>2.4214364679901816E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -2672,7 +2672,7 @@
         <v>-2.9233462774163265E-4</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -2740,7 +2740,7 @@
         <v>2.0015908231555864E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -2808,7 +2808,7 @@
         <v>-2.2975361075814695E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -2876,7 +2876,7 @@
         <v>-2.3331216461684356E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -2944,7 +2944,7 @@
         <v>-2.3645733642601016E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -3012,9 +3012,9 @@
         <v>-2.3999813120483337E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B15">
         <v>-0.21272709898745751</v>
@@ -3080,9 +3080,9 @@
         <v>-9.1834213578172443E-5</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B16">
         <v>-0.27662918378841866</v>
@@ -3148,9 +3148,9 @@
         <v>-1.1405156490463008E-4</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B17">
         <v>4.3866084354798308E-2</v>
@@ -3216,9 +3216,9 @@
         <v>-7.0291373168100766E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B18">
         <v>-4.4588438657485623E-2</v>
@@ -3284,7 +3284,7 @@
         <v>-4.1005178251279922E-4</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -3352,7 +3352,7 @@
         <v>-1.3732499076637424E-4</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -3420,7 +3420,7 @@
         <v>-2.2586603147181343E-4</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -3496,12 +3496,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3272626D-9706-4C43-8EC8-444422CC481A}">
   <dimension ref="A1:U20"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="9.06640625" style="2"/>
+    <col min="1" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -3545,16 +3545,16 @@
         <v>23</v>
       </c>
       <c r="O1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="P1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="Q1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="R1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="S1" t="s">
         <v>24</v>
@@ -3566,7 +3566,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -3631,7 +3631,7 @@
         <v>-1.3017969006119149E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -3696,7 +3696,7 @@
         <v>1.3152903791723208E-5</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -3761,7 +3761,7 @@
         <v>-7.8901706852183284E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -3826,7 +3826,7 @@
         <v>-5.5102373468521471E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -3891,7 +3891,7 @@
         <v>1.7102762788115533E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -3956,7 +3956,7 @@
         <v>1.2250917552511335E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -4021,7 +4021,7 @@
         <v>1.7718965949682538E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -4086,7 +4086,7 @@
         <v>1.2363120055002817E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -4151,7 +4151,7 @@
         <v>-2.1672893123388236E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -4216,7 +4216,7 @@
         <v>-2.1740359090585807E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -4281,7 +4281,7 @@
         <v>-2.1931130404519227E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -4346,9 +4346,9 @@
         <v>-2.2303177917484072E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B14">
         <v>-0.28975681460033459</v>
@@ -4411,9 +4411,9 @@
         <v>-3.4902188633207249E-4</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B15">
         <v>-0.16673440033087025</v>
@@ -4476,9 +4476,9 @@
         <v>-2.3281971535627936E-4</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B16">
         <v>-1.0741569520603693E-2</v>
@@ -4541,9 +4541,9 @@
         <v>-3.5895503614843157E-4</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B17">
         <v>-7.9276933491462906E-2</v>
@@ -4606,7 +4606,7 @@
         <v>-2.4817774997782104E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -4671,7 +4671,7 @@
         <v>-4.4860342118591259E-4</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -4736,7 +4736,7 @@
         <v>-2.1973236060633149E-4</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>26</v>
       </c>
@@ -4809,12 +4809,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43153968-584D-43BC-8C7D-7725BE1C9391}">
   <dimension ref="A1:U20"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="9.06640625" style="2"/>
+    <col min="1" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -4858,16 +4858,16 @@
         <v>23</v>
       </c>
       <c r="O1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="P1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="Q1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="R1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="S1" t="s">
         <v>24</v>
@@ -4879,7 +4879,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -4944,7 +4944,7 @@
         <v>-1.1135601312801011E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -5009,7 +5009,7 @@
         <v>1.0553055313925292E-5</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -5074,7 +5074,7 @@
         <v>-9.6714204456533823E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -5139,7 +5139,7 @@
         <v>-8.1509002182341833E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>27</v>
       </c>
@@ -5204,7 +5204,7 @@
         <v>2.0260508682320348E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -5269,7 +5269,7 @@
         <v>1.7272721890891285E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -5334,7 +5334,7 @@
         <v>-6.9602413068016615E-5</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -5399,7 +5399,7 @@
         <v>1.1597034318128123E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -5464,7 +5464,7 @@
         <v>-1.8265334684390032E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -5529,7 +5529,7 @@
         <v>-1.8232071887149381E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -5594,7 +5594,7 @@
         <v>-1.8328144779612615E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -5659,9 +5659,9 @@
         <v>-1.8658961389699226E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B14">
         <v>-0.17388542857539849</v>
@@ -5724,9 +5724,9 @@
         <v>-3.3089833030840703E-4</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B15">
         <v>-0.21949401773440641</v>
@@ -5789,9 +5789,9 @@
         <v>-3.9387172454949349E-4</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B16">
         <v>5.7814928672014425E-2</v>
@@ -5854,9 +5854,9 @@
         <v>-3.9968679920780769E-4</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B17">
         <v>-2.1913673614024333E-2</v>
@@ -5919,7 +5919,7 @@
         <v>-2.4854654835416664E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -5984,7 +5984,7 @@
         <v>-2.8476340521160862E-4</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -6049,7 +6049,7 @@
         <v>-1.6900310894604875E-4</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>26</v>
       </c>

--- a/input/reg_employmentSelection.xlsx
+++ b/input/reg_employmentSelection.xlsx
@@ -8,23 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F2A70B-FB9E-4718-A0BF-5440B701C9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B4C2AA8-421F-4B3F-8E8C-471936C9B663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" tabRatio="904" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="904" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
-    <sheet name="IT_EmploymentSelection_FemaleNE" sheetId="6" r:id="rId2"/>
-    <sheet name="IT_EmploymentSelection_MaleNE" sheetId="7" r:id="rId3"/>
-    <sheet name="IT_EmploymentSelection_FemaleE" sheetId="8" r:id="rId4"/>
-    <sheet name="IT_EmploymentSelection_MaleE" sheetId="9" r:id="rId5"/>
+    <sheet name="EL_EmploymentSelection_FemaleNE" sheetId="10" r:id="rId2"/>
+    <sheet name="EL_EmploymentSelection_MaleNE" sheetId="11" r:id="rId3"/>
+    <sheet name="EL_EmploymentSelection_FemaleE" sheetId="12" r:id="rId4"/>
+    <sheet name="EL_EmploymentSelection_MaleE" sheetId="13" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="36">
   <si>
     <t>Description:</t>
   </si>
@@ -113,18 +113,6 @@
     <t>Deh_c3_Low_Dag</t>
   </si>
   <si>
-    <t>ITF</t>
-  </si>
-  <si>
-    <t>ITG</t>
-  </si>
-  <si>
-    <t>ITH</t>
-  </si>
-  <si>
-    <t>ITI</t>
-  </si>
-  <si>
     <t>EL_EmploymentSelection_FemaleNE</t>
   </si>
   <si>
@@ -138,6 +126,12 @@
   </si>
   <si>
     <t>Regions: EL3 = Attika (omitted), EL4 = Aegean Islands, EL7 = Central and Northern Greece</t>
+  </si>
+  <si>
+    <t>EL4</t>
+  </si>
+  <si>
+    <t>EL7</t>
   </si>
 </sst>
 </file>
@@ -187,10 +181,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -547,7 +540,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
@@ -555,7 +548,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
         <v>3</v>
@@ -563,7 +556,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
         <v>4</v>
@@ -571,7 +564,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s">
         <v>5</v>
@@ -597,7 +590,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -611,15 +604,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5440224-65B9-42C3-BDF1-EC73DB722098}">
-  <dimension ref="A1:V21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="23" style="2" customWidth="1"/>
-    <col min="2" max="16384" width="9" style="2"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF1FB57E-A5D4-4226-8E15-470CEA8B04AE}">
+  <dimension ref="A1:T19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -666,1385 +655,1135 @@
         <v>23</v>
       </c>
       <c r="P1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="Q1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="R1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="S1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="T1" t="s">
-        <v>24</v>
-      </c>
-      <c r="U1" t="s">
-        <v>25</v>
-      </c>
-      <c r="V1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2">
-        <v>0.46335676627740596</v>
+        <v>0.14007101780580777</v>
       </c>
       <c r="C2">
-        <v>1.5435863862118364E-3</v>
+        <v>2.9464686152392227E-3</v>
       </c>
       <c r="D2">
-        <v>-1.2504923304975019E-4</v>
+        <v>-1.8579370931965476E-4</v>
       </c>
       <c r="E2">
-        <v>1.1671004634461169E-6</v>
+        <v>1.9678881193696774E-6</v>
       </c>
       <c r="F2">
-        <v>-3.6111682278359763E-4</v>
+        <v>5.8985471342367377E-4</v>
       </c>
       <c r="G2">
-        <v>-6.4022361490976112E-4</v>
+        <v>4.0960824067561409E-4</v>
       </c>
       <c r="H2">
-        <v>7.2799609887154787E-6</v>
+        <v>-1.1491878602406743E-5</v>
       </c>
       <c r="I2">
-        <v>1.2591713226124463E-5</v>
+        <v>-8.4491508072647811E-6</v>
       </c>
       <c r="J2">
-        <v>-5.8710248775663032E-5</v>
+        <v>-7.4790107136615369E-5</v>
       </c>
       <c r="K2">
-        <v>-7.0114164738754268E-5</v>
+        <v>-1.0692334807299995E-4</v>
       </c>
       <c r="L2">
-        <v>3.1276833432214413E-5</v>
+        <v>-6.2365672662842517E-7</v>
       </c>
       <c r="M2">
-        <v>4.2119498031995711E-5</v>
+        <v>-2.0710278703949848E-6</v>
       </c>
       <c r="N2">
-        <v>5.4475538407166191E-5</v>
+        <v>2.6204775444267983E-5</v>
       </c>
       <c r="O2">
-        <v>6.1294099615593917E-5</v>
+        <v>3.1269100227479638E-5</v>
       </c>
       <c r="P2">
-        <v>-1.6273547434868112E-5</v>
+        <v>-6.1464108917885527E-5</v>
       </c>
       <c r="Q2">
-        <v>-3.3760732814085383E-5</v>
+        <v>-6.5924661821387381E-5</v>
       </c>
       <c r="R2">
-        <v>1.0901398922579113E-5</v>
+        <v>3.8061812814572471E-5</v>
       </c>
       <c r="S2">
-        <v>1.8385479859766073E-5</v>
+        <v>-1.0493851478589366E-4</v>
       </c>
       <c r="T2">
-        <v>1.8874347566381409E-5</v>
-      </c>
-      <c r="U2">
-        <v>-8.375054267015991E-5</v>
-      </c>
-      <c r="V2">
-        <v>1.7248638636402369E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1.398899001211567E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
       <c r="B3">
-        <v>0.16540131631263999</v>
+        <v>0.13079000569462945</v>
       </c>
       <c r="C3">
-        <v>-1.2504923304975019E-4</v>
+        <v>-1.8579370931965476E-4</v>
       </c>
       <c r="D3">
-        <v>5.6068449301461554E-5</v>
+        <v>7.732091952280932E-5</v>
       </c>
       <c r="E3">
-        <v>-5.9002250875483476E-7</v>
+        <v>-8.466791777586037E-7</v>
       </c>
       <c r="F3">
-        <v>2.6242525048187677E-4</v>
+        <v>2.5863204661499129E-4</v>
       </c>
       <c r="G3">
-        <v>2.4220134123064519E-4</v>
+        <v>5.4500084723729466E-7</v>
       </c>
       <c r="H3">
-        <v>-6.0792272134212774E-6</v>
+        <v>-6.230116003711243E-6</v>
       </c>
       <c r="I3">
-        <v>-5.458067085799236E-6</v>
+        <v>-3.499154356769894E-7</v>
       </c>
       <c r="J3">
-        <v>-2.3254151443183878E-5</v>
+        <v>-4.4490589298739298E-5</v>
       </c>
       <c r="K3">
-        <v>-7.2565541280196223E-5</v>
+        <v>-8.2788623376568146E-5</v>
       </c>
       <c r="L3">
-        <v>1.4333714595701243E-5</v>
+        <v>3.0889224604654843E-6</v>
       </c>
       <c r="M3">
-        <v>2.1046496127730303E-5</v>
+        <v>1.8499175204303052E-5</v>
       </c>
       <c r="N3">
-        <v>2.1369356423503049E-5</v>
+        <v>1.6050384723396028E-5</v>
       </c>
       <c r="O3">
-        <v>3.4103201837190687E-5</v>
+        <v>2.2950209451772321E-5</v>
       </c>
       <c r="P3">
-        <v>-1.2710962844650933E-5</v>
+        <v>5.5709331938870594E-6</v>
       </c>
       <c r="Q3">
-        <v>-1.4503501652579277E-5</v>
+        <v>2.1975487630731088E-6</v>
       </c>
       <c r="R3">
-        <v>5.200568741801719E-6</v>
+        <v>4.5136649462140327E-6</v>
       </c>
       <c r="S3">
-        <v>-4.4712132475915855E-6</v>
+        <v>1.1263997760435979E-5</v>
       </c>
       <c r="T3">
-        <v>6.0106180845996498E-6</v>
-      </c>
-      <c r="U3">
-        <v>7.2175247270978005E-6</v>
-      </c>
-      <c r="V3">
-        <v>-1.0949341663041032E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-1.4220714248964733E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
       <c r="B4">
-        <v>-2.0336181933372499E-3</v>
+        <v>-1.8069767544117389E-3</v>
       </c>
       <c r="C4">
-        <v>1.1671004634461169E-6</v>
+        <v>1.9678881193696774E-6</v>
       </c>
       <c r="D4">
-        <v>-5.9002250875483476E-7</v>
+        <v>-8.466791777586037E-7</v>
       </c>
       <c r="E4">
-        <v>6.7078428832845831E-9</v>
+        <v>9.8482394845469842E-9</v>
       </c>
       <c r="F4">
-        <v>-1.4093668735716778E-6</v>
+        <v>-1.3151687574911107E-6</v>
       </c>
       <c r="G4">
-        <v>-1.0818018947545622E-6</v>
+        <v>1.8611482240932876E-6</v>
       </c>
       <c r="H4">
-        <v>2.8397952745156898E-8</v>
+        <v>2.9258243404604707E-8</v>
       </c>
       <c r="I4">
-        <v>1.9440313801539262E-8</v>
+        <v>-4.2576656574669153E-8</v>
       </c>
       <c r="J4">
-        <v>1.6225459777841805E-7</v>
+        <v>2.9168546260432729E-7</v>
       </c>
       <c r="K4">
-        <v>8.9176930540818223E-7</v>
+        <v>1.0557520798008551E-6</v>
       </c>
       <c r="L4">
-        <v>-2.1692729883776145E-7</v>
+        <v>-3.3711309708704459E-8</v>
       </c>
       <c r="M4">
-        <v>-2.5408930616998066E-7</v>
+        <v>-2.0060551526731855E-7</v>
       </c>
       <c r="N4">
-        <v>-2.1260569360864621E-7</v>
+        <v>-1.4816264473924984E-7</v>
       </c>
       <c r="O4">
-        <v>-3.1483168902974696E-7</v>
+        <v>-1.1852410199472996E-7</v>
       </c>
       <c r="P4">
-        <v>1.7568667788743859E-7</v>
+        <v>-2.0604148177634348E-8</v>
       </c>
       <c r="Q4">
-        <v>1.9680529485039731E-7</v>
+        <v>6.708790667743035E-9</v>
       </c>
       <c r="R4">
-        <v>-4.4623846144080106E-8</v>
+        <v>-8.2842459819615595E-8</v>
       </c>
       <c r="S4">
-        <v>5.8990064685819371E-8</v>
+        <v>-2.0805479477080352E-7</v>
       </c>
       <c r="T4">
-        <v>-8.7631537029292095E-8</v>
-      </c>
-      <c r="U4">
-        <v>-1.2715301218480037E-7</v>
-      </c>
-      <c r="V4">
-        <v>1.0811166992187685E-5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1.4627140391797511E-5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
       <c r="B5">
-        <v>-0.17684239703940843</v>
+        <v>-0.70596868422228121</v>
       </c>
       <c r="C5">
-        <v>-3.6111682278359763E-4</v>
+        <v>5.8985471342367377E-4</v>
       </c>
       <c r="D5">
-        <v>2.6242525048187677E-4</v>
+        <v>2.5863204661499129E-4</v>
       </c>
       <c r="E5">
-        <v>-1.4093668735716778E-6</v>
+        <v>-1.3151687574911107E-6</v>
       </c>
       <c r="F5">
-        <v>7.9921920250955857E-3</v>
+        <v>9.8823225194020307E-3</v>
       </c>
       <c r="G5">
-        <v>6.0135294831348282E-3</v>
+        <v>6.2623975754895981E-3</v>
       </c>
       <c r="H5">
-        <v>-1.8715420156073794E-4</v>
+        <v>-2.2879574707393088E-4</v>
       </c>
       <c r="I5">
-        <v>-1.4161207410009585E-4</v>
+        <v>-1.4759410557533019E-4</v>
       </c>
       <c r="J5">
-        <v>-4.4929974634866685E-5</v>
+        <v>-1.2882274131138295E-4</v>
       </c>
       <c r="K5">
-        <v>-2.3677460783008233E-4</v>
+        <v>-3.5999952285553676E-4</v>
       </c>
       <c r="L5">
-        <v>-1.3918453420883395E-4</v>
+        <v>1.6582110750674485E-5</v>
       </c>
       <c r="M5">
-        <v>-2.4913693008450644E-5</v>
+        <v>6.6257513146336308E-5</v>
       </c>
       <c r="N5">
-        <v>-2.2099117022402436E-5</v>
+        <v>6.484777364518593E-5</v>
       </c>
       <c r="O5">
-        <v>4.8152370062228347E-6</v>
+        <v>5.7443552731727479E-5</v>
       </c>
       <c r="P5">
-        <v>4.0023139970560851E-6</v>
+        <v>-1.1648871285234452E-5</v>
       </c>
       <c r="Q5">
-        <v>-4.8154454327020829E-5</v>
+        <v>1.0186587643995531E-6</v>
       </c>
       <c r="R5">
-        <v>4.1104211242475963E-5</v>
+        <v>1.6256812978985142E-5</v>
       </c>
       <c r="S5">
-        <v>2.5764357838610949E-6</v>
+        <v>-1.212529593334397E-4</v>
       </c>
       <c r="T5">
-        <v>2.2720434751779484E-5</v>
-      </c>
-      <c r="U5">
-        <v>-5.5264533989758388E-6</v>
-      </c>
-      <c r="V5">
-        <v>-7.9092310393618689E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-8.8072451803098608E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
       <c r="B6">
-        <v>-0.58989247676387635</v>
+        <v>-1.6526907371819044</v>
       </c>
       <c r="C6">
-        <v>-6.4022361490976112E-4</v>
+        <v>4.0960824067561409E-4</v>
       </c>
       <c r="D6">
-        <v>2.4220134123064519E-4</v>
+        <v>5.4500084723729466E-7</v>
       </c>
       <c r="E6">
-        <v>-1.0818018947545622E-6</v>
+        <v>1.8611482240932876E-6</v>
       </c>
       <c r="F6">
-        <v>6.0135294831348282E-3</v>
+        <v>6.2623975754895981E-3</v>
       </c>
       <c r="G6">
-        <v>1.0763306687424014E-2</v>
+        <v>1.9720352400149112E-2</v>
       </c>
       <c r="H6">
-        <v>-1.4203407925366841E-4</v>
+        <v>-1.475499699811687E-4</v>
       </c>
       <c r="I6">
-        <v>-2.3786245822807135E-4</v>
+        <v>-4.0617967125098492E-4</v>
       </c>
       <c r="J6">
-        <v>-8.3715814955317511E-5</v>
+        <v>-2.8158975772197328E-4</v>
       </c>
       <c r="K6">
-        <v>-3.8698700529060008E-4</v>
+        <v>-3.958208029078258E-4</v>
       </c>
       <c r="L6">
-        <v>2.5802462688416343E-5</v>
+        <v>2.2673898902636578E-4</v>
       </c>
       <c r="M6">
-        <v>1.4142972648414562E-4</v>
+        <v>2.7145719983362828E-4</v>
       </c>
       <c r="N6">
-        <v>1.1384887701735343E-4</v>
+        <v>2.1199576058920726E-4</v>
       </c>
       <c r="O6">
-        <v>1.6280603293120435E-4</v>
+        <v>3.0435724752003539E-4</v>
       </c>
       <c r="P6">
-        <v>-7.9728706141940229E-6</v>
+        <v>2.1429340788409727E-5</v>
       </c>
       <c r="Q6">
-        <v>-5.8679412485442828E-5</v>
+        <v>4.755229528934607E-5</v>
       </c>
       <c r="R6">
-        <v>6.7840350773593061E-5</v>
+        <v>-4.7112705801565487E-5</v>
       </c>
       <c r="S6">
-        <v>3.7141872487147568E-5</v>
+        <v>-1.9636586633964823E-4</v>
       </c>
       <c r="T6">
-        <v>-2.8166262021654259E-5</v>
-      </c>
-      <c r="U6">
-        <v>-4.644099810281029E-5</v>
-      </c>
-      <c r="V6">
-        <v>-7.5302828888323186E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-3.9453805781703658E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>27</v>
       </c>
       <c r="B7">
-        <v>-4.513171101235087E-3</v>
+        <v>1.127343958284362E-2</v>
       </c>
       <c r="C7">
-        <v>7.2799609887154787E-6</v>
+        <v>-1.1491878602406743E-5</v>
       </c>
       <c r="D7">
-        <v>-6.0792272134212774E-6</v>
+        <v>-6.230116003711243E-6</v>
       </c>
       <c r="E7">
-        <v>2.8397952745156898E-8</v>
+        <v>2.9258243404604707E-8</v>
       </c>
       <c r="F7">
-        <v>-1.8715420156073794E-4</v>
+        <v>-2.2879574707393088E-4</v>
       </c>
       <c r="G7">
-        <v>-1.4203407925366841E-4</v>
+        <v>-1.475499699811687E-4</v>
       </c>
       <c r="H7">
-        <v>4.8142490979285956E-6</v>
+        <v>5.744890557961447E-6</v>
       </c>
       <c r="I7">
-        <v>3.6613111703606023E-6</v>
+        <v>3.7864670762023296E-6</v>
       </c>
       <c r="J7">
-        <v>-1.6255022595239125E-8</v>
+        <v>1.6925989254423569E-6</v>
       </c>
       <c r="K7">
-        <v>5.3532136233390231E-6</v>
+        <v>8.375142042137323E-6</v>
       </c>
       <c r="L7">
-        <v>4.2226720045827594E-6</v>
+        <v>-4.7037236717802685E-7</v>
       </c>
       <c r="M7">
-        <v>8.9974122662252632E-7</v>
+        <v>-1.4273183560363826E-6</v>
       </c>
       <c r="N7">
-        <v>1.2302983280304514E-6</v>
+        <v>-9.8749228491375695E-7</v>
       </c>
       <c r="O7">
-        <v>9.4069080877933538E-7</v>
+        <v>1.5392332398127446E-7</v>
       </c>
       <c r="P7">
-        <v>-6.3437651811458171E-7</v>
+        <v>-1.7956057731458988E-6</v>
       </c>
       <c r="Q7">
-        <v>5.3921373440098488E-7</v>
+        <v>-1.4943505850686548E-6</v>
       </c>
       <c r="R7">
-        <v>-1.1880234746643158E-6</v>
+        <v>-4.5779660277754077E-7</v>
       </c>
       <c r="S7">
-        <v>-2.5786038222979386E-7</v>
+        <v>3.1735206397113143E-6</v>
       </c>
       <c r="T7">
-        <v>-2.9237019994472268E-7</v>
-      </c>
-      <c r="U7">
-        <v>8.7581850161201109E-7</v>
-      </c>
-      <c r="V7">
-        <v>1.7931262215968425E-4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+        <v>2.0263866971255971E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>28</v>
       </c>
       <c r="B8">
-        <v>-2.2577741407271069E-4</v>
+        <v>3.059639083095796E-2</v>
       </c>
       <c r="C8">
-        <v>1.2591713226124463E-5</v>
+        <v>-8.4491508072647811E-6</v>
       </c>
       <c r="D8">
-        <v>-5.458067085799236E-6</v>
+        <v>-3.499154356769894E-7</v>
       </c>
       <c r="E8">
-        <v>1.9440313801539262E-8</v>
+        <v>-4.2576656574669153E-8</v>
       </c>
       <c r="F8">
-        <v>-1.4161207410009585E-4</v>
+        <v>-1.4759410557533019E-4</v>
       </c>
       <c r="G8">
-        <v>-2.3786245822807135E-4</v>
+        <v>-4.0617967125098492E-4</v>
       </c>
       <c r="H8">
-        <v>3.6613111703606023E-6</v>
+        <v>3.7864670762023296E-6</v>
       </c>
       <c r="I8">
-        <v>5.7357431213662359E-6</v>
+        <v>8.960358033638958E-6</v>
       </c>
       <c r="J8">
-        <v>1.2464137767334874E-7</v>
+        <v>3.8886776484400268E-6</v>
       </c>
       <c r="K8">
-        <v>8.9433355873355682E-6</v>
+        <v>9.7578673493630894E-6</v>
       </c>
       <c r="L8">
-        <v>6.2834767556988781E-7</v>
+        <v>-3.7714471637996288E-6</v>
       </c>
       <c r="M8">
-        <v>-2.0069384270770071E-6</v>
+        <v>-3.7325338553792801E-6</v>
       </c>
       <c r="N8">
-        <v>-9.3653660933269885E-8</v>
+        <v>-7.0324498123132206E-7</v>
       </c>
       <c r="O8">
-        <v>-6.4048083255781861E-7</v>
+        <v>-6.4443121226778635E-7</v>
       </c>
       <c r="P8">
-        <v>-9.7910868654901164E-7</v>
+        <v>-4.1702834453565751E-6</v>
       </c>
       <c r="Q8">
-        <v>-3.7198490483373514E-7</v>
+        <v>-4.6446011006754738E-6</v>
       </c>
       <c r="R8">
-        <v>-1.6902565344256375E-6</v>
+        <v>1.0691929446943723E-6</v>
       </c>
       <c r="S8">
-        <v>-7.6104182566894405E-7</v>
+        <v>5.5466681339082879E-6</v>
       </c>
       <c r="T8">
-        <v>1.314433249950561E-6</v>
-      </c>
-      <c r="U8">
-        <v>2.4602606338683487E-6</v>
-      </c>
-      <c r="V8">
-        <v>1.6624589291442966E-4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+        <v>8.9241642087114091E-5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>18</v>
       </c>
       <c r="B9">
-        <v>-0.3517299148837813</v>
+        <v>-4.5678913192719987E-2</v>
       </c>
       <c r="C9">
-        <v>-5.8710248775663032E-5</v>
+        <v>-7.4790107136615369E-5</v>
       </c>
       <c r="D9">
-        <v>-2.3254151443183878E-5</v>
+        <v>-4.4490589298739298E-5</v>
       </c>
       <c r="E9">
-        <v>1.6225459777841805E-7</v>
+        <v>2.9168546260432729E-7</v>
       </c>
       <c r="F9">
-        <v>-4.4929974634866685E-5</v>
+        <v>-1.2882274131138295E-4</v>
       </c>
       <c r="G9">
-        <v>-8.3715814955317511E-5</v>
+        <v>-2.8158975772197328E-4</v>
       </c>
       <c r="H9">
-        <v>-1.6255022595239125E-8</v>
+        <v>1.6925989254423569E-6</v>
       </c>
       <c r="I9">
-        <v>1.2464137767334874E-7</v>
+        <v>3.8886776484400268E-6</v>
       </c>
       <c r="J9">
-        <v>6.6232085255163908E-4</v>
+        <v>9.807210448604341E-4</v>
       </c>
       <c r="K9">
-        <v>-2.9091025866186517E-4</v>
+        <v>-3.8469642717043641E-4</v>
       </c>
       <c r="L9">
-        <v>-5.8870436755601287E-5</v>
+        <v>-9.162130282035154E-5</v>
       </c>
       <c r="M9">
-        <v>-8.3107675598259454E-5</v>
+        <v>-1.5171751770740114E-4</v>
       </c>
       <c r="N9">
-        <v>-1.168573043405057E-4</v>
+        <v>-2.2566024535764501E-4</v>
       </c>
       <c r="O9">
-        <v>-1.2207331365468731E-4</v>
+        <v>-2.4379470539813509E-4</v>
       </c>
       <c r="P9">
-        <v>1.4757664045180552E-5</v>
+        <v>-3.4112190159680423E-5</v>
       </c>
       <c r="Q9">
-        <v>1.7320730165917126E-5</v>
+        <v>-2.7491097852160848E-5</v>
       </c>
       <c r="R9">
-        <v>-1.2016158282798979E-5</v>
+        <v>-4.5840737823717262E-7</v>
       </c>
       <c r="S9">
-        <v>9.1399701098882153E-6</v>
+        <v>2.759855204656511E-5</v>
       </c>
       <c r="T9">
-        <v>9.7447062474013729E-6</v>
-      </c>
-      <c r="U9">
-        <v>2.8430271963535789E-5</v>
-      </c>
-      <c r="V9">
-        <v>5.9218191460279508E-4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1.1703376287154708E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
       <c r="B10">
-        <v>-7.9171630578653937E-2</v>
+        <v>-3.3467060008684123E-2</v>
       </c>
       <c r="C10">
-        <v>-7.0114164738754268E-5</v>
+        <v>-1.0692334807299995E-4</v>
       </c>
       <c r="D10">
-        <v>-7.2565541280196223E-5</v>
+        <v>-8.2788623376568146E-5</v>
       </c>
       <c r="E10">
-        <v>8.9176930540818223E-7</v>
+        <v>1.0557520798008551E-6</v>
       </c>
       <c r="F10">
-        <v>-2.3677460783008233E-4</v>
+        <v>-3.5999952285553676E-4</v>
       </c>
       <c r="G10">
-        <v>-3.8698700529060008E-4</v>
+        <v>-3.958208029078258E-4</v>
       </c>
       <c r="H10">
-        <v>5.3532136233390231E-6</v>
+        <v>8.375142042137323E-6</v>
       </c>
       <c r="I10">
-        <v>8.9433355873355682E-6</v>
+        <v>9.7578673493630894E-6</v>
       </c>
       <c r="J10">
-        <v>-2.9091025866186517E-4</v>
+        <v>-3.8469642717043641E-4</v>
       </c>
       <c r="K10">
-        <v>7.8520761965663124E-4</v>
+        <v>9.6451554475622536E-4</v>
       </c>
       <c r="L10">
-        <v>-1.9378442211467222E-5</v>
+        <v>4.9537546456034066E-5</v>
       </c>
       <c r="M10">
-        <v>-5.3247826944245367E-5</v>
+        <v>3.0596541732600866E-5</v>
       </c>
       <c r="N10">
-        <v>-6.2483294193535531E-5</v>
+        <v>2.7273387927048416E-5</v>
       </c>
       <c r="O10">
-        <v>-7.1894845293149902E-5</v>
+        <v>2.2746651508509389E-5</v>
       </c>
       <c r="P10">
-        <v>9.2075989556389232E-6</v>
+        <v>-1.8271538025578626E-5</v>
       </c>
       <c r="Q10">
-        <v>1.6661628211515884E-5</v>
+        <v>-3.3035681801429531E-6</v>
       </c>
       <c r="R10">
-        <v>-7.1545244131183002E-6</v>
+        <v>-1.1422744848480132E-5</v>
       </c>
       <c r="S10">
-        <v>-2.5040033411454349E-6</v>
+        <v>-1.0511514962281496E-5</v>
       </c>
       <c r="T10">
-        <v>-9.5444570478221848E-6</v>
-      </c>
-      <c r="U10">
-        <v>-4.8815517316311754E-7</v>
-      </c>
-      <c r="V10">
-        <v>1.3550557304967494E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1.4444425413847272E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
       <c r="B11">
-        <v>0.56346220273035441</v>
+        <v>4.2044358635998251E-2</v>
       </c>
       <c r="C11">
-        <v>3.1276833432214413E-5</v>
+        <v>-6.2365672662842517E-7</v>
       </c>
       <c r="D11">
-        <v>1.4333714595701243E-5</v>
+        <v>3.0889224604654843E-6</v>
       </c>
       <c r="E11">
-        <v>-2.1692729883776145E-7</v>
+        <v>-3.3711309708704459E-8</v>
       </c>
       <c r="F11">
-        <v>-1.3918453420883395E-4</v>
+        <v>1.6582110750674485E-5</v>
       </c>
       <c r="G11">
-        <v>2.5802462688416343E-5</v>
+        <v>2.2673898902636578E-4</v>
       </c>
       <c r="H11">
-        <v>4.2226720045827594E-6</v>
+        <v>-4.7037236717802685E-7</v>
       </c>
       <c r="I11">
-        <v>6.2834767556988781E-7</v>
+        <v>-3.7714471637996288E-6</v>
       </c>
       <c r="J11">
-        <v>-5.8870436755601287E-5</v>
+        <v>-9.162130282035154E-5</v>
       </c>
       <c r="K11">
-        <v>-1.9378442211467222E-5</v>
+        <v>4.9537546456034066E-5</v>
       </c>
       <c r="L11">
-        <v>3.1485219411282642E-2</v>
+        <v>2.292972346672752E-2</v>
       </c>
       <c r="M11">
-        <v>2.8523861388075618E-2</v>
+        <v>1.723078672931885E-2</v>
       </c>
       <c r="N11">
-        <v>2.8514241461723353E-2</v>
+        <v>1.7233880855336919E-2</v>
       </c>
       <c r="O11">
-        <v>2.8509157708383026E-2</v>
+        <v>1.7215377659342602E-2</v>
       </c>
       <c r="P11">
-        <v>-3.1297203751018426E-5</v>
+        <v>6.32364938371161E-5</v>
       </c>
       <c r="Q11">
-        <v>-2.0589748228410872E-5</v>
+        <v>1.5166887083754079E-5</v>
       </c>
       <c r="R11">
-        <v>-2.1386120416329335E-5</v>
+        <v>3.7033924186573579E-6</v>
       </c>
       <c r="S11">
-        <v>-1.2886341011788887E-5</v>
+        <v>1.1912172788867128E-5</v>
       </c>
       <c r="T11">
-        <v>-1.1216279089027993E-5</v>
-      </c>
-      <c r="U11">
-        <v>2.766801843273788E-5</v>
-      </c>
-      <c r="V11">
-        <v>-2.8705309677373732E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-1.7272656449471829E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
       <c r="B12">
-        <v>0.69788142775458906</v>
+        <v>0.32428072921244672</v>
       </c>
       <c r="C12">
-        <v>4.2119498031995711E-5</v>
+        <v>-2.0710278703949848E-6</v>
       </c>
       <c r="D12">
-        <v>2.1046496127730303E-5</v>
+        <v>1.8499175204303052E-5</v>
       </c>
       <c r="E12">
-        <v>-2.5408930616998066E-7</v>
+        <v>-2.0060551526731855E-7</v>
       </c>
       <c r="F12">
-        <v>-2.4913693008450644E-5</v>
+        <v>6.6257513146336308E-5</v>
       </c>
       <c r="G12">
-        <v>1.4142972648414562E-4</v>
+        <v>2.7145719983362828E-4</v>
       </c>
       <c r="H12">
-        <v>8.9974122662252632E-7</v>
+        <v>-1.4273183560363826E-6</v>
       </c>
       <c r="I12">
-        <v>-2.0069384270770071E-6</v>
+        <v>-3.7325338553792801E-6</v>
       </c>
       <c r="J12">
-        <v>-8.3107675598259454E-5</v>
+        <v>-1.5171751770740114E-4</v>
       </c>
       <c r="K12">
-        <v>-5.3247826944245367E-5</v>
+        <v>3.0596541732600866E-5</v>
       </c>
       <c r="L12">
-        <v>2.8523861388075618E-2</v>
+        <v>1.723078672931885E-2</v>
       </c>
       <c r="M12">
-        <v>2.9222752991677786E-2</v>
+        <v>1.8720833326409607E-2</v>
       </c>
       <c r="N12">
-        <v>2.8535009572933263E-2</v>
+        <v>1.7258083503771914E-2</v>
       </c>
       <c r="O12">
-        <v>2.8536141005215909E-2</v>
+        <v>1.7247552955246426E-2</v>
       </c>
       <c r="P12">
-        <v>-3.540449539820411E-5</v>
+        <v>4.316117901410061E-5</v>
       </c>
       <c r="Q12">
-        <v>-1.6701005917109117E-5</v>
+        <v>3.3141408100464216E-5</v>
       </c>
       <c r="R12">
-        <v>-1.8626532137844417E-5</v>
+        <v>-3.9166414312357233E-6</v>
       </c>
       <c r="S12">
-        <v>-3.1134741049297139E-5</v>
+        <v>9.7714829693170918E-6</v>
       </c>
       <c r="T12">
-        <v>-3.1241202171240057E-5</v>
-      </c>
-      <c r="U12">
-        <v>2.9616187938088475E-5</v>
-      </c>
-      <c r="V12">
-        <v>-2.8903065279276982E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-1.7604989738692553E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>22</v>
       </c>
       <c r="B13">
-        <v>0.80473324921608669</v>
+        <v>0.45682877054780197</v>
       </c>
       <c r="C13">
-        <v>5.4475538407166191E-5</v>
+        <v>2.6204775444267983E-5</v>
       </c>
       <c r="D13">
-        <v>2.1369356423503049E-5</v>
+        <v>1.6050384723396028E-5</v>
       </c>
       <c r="E13">
-        <v>-2.1260569360864621E-7</v>
+        <v>-1.4816264473924984E-7</v>
       </c>
       <c r="F13">
-        <v>-2.2099117022402436E-5</v>
+        <v>6.484777364518593E-5</v>
       </c>
       <c r="G13">
-        <v>1.1384887701735343E-4</v>
+        <v>2.1199576058920726E-4</v>
       </c>
       <c r="H13">
-        <v>1.2302983280304514E-6</v>
+        <v>-9.8749228491375695E-7</v>
       </c>
       <c r="I13">
-        <v>-9.3653660933269885E-8</v>
+        <v>-7.0324498123132206E-7</v>
       </c>
       <c r="J13">
-        <v>-1.168573043405057E-4</v>
+        <v>-2.2566024535764501E-4</v>
       </c>
       <c r="K13">
-        <v>-6.2483294193535531E-5</v>
+        <v>2.7273387927048416E-5</v>
       </c>
       <c r="L13">
-        <v>2.8514241461723353E-2</v>
+        <v>1.7233880855336919E-2</v>
       </c>
       <c r="M13">
-        <v>2.8535009572933263E-2</v>
+        <v>1.7258083503771914E-2</v>
       </c>
       <c r="N13">
-        <v>2.8733488632776007E-2</v>
+        <v>1.7707305084165782E-2</v>
       </c>
       <c r="O13">
-        <v>2.8616041737490997E-2</v>
+        <v>1.7324690720149732E-2</v>
       </c>
       <c r="P13">
-        <v>-2.6204895517368548E-5</v>
+        <v>5.6619157188817133E-5</v>
       </c>
       <c r="Q13">
-        <v>-8.7433813287080112E-6</v>
+        <v>5.509216180771395E-6</v>
       </c>
       <c r="R13">
-        <v>-2.5758271829982751E-5</v>
+        <v>-2.856006320035246E-5</v>
       </c>
       <c r="S13">
-        <v>-1.6721963451605068E-5</v>
+        <v>-2.3261638219552246E-5</v>
       </c>
       <c r="T13">
-        <v>4.5840177877870983E-5</v>
-      </c>
-      <c r="U13">
-        <v>1.5002953793197569E-5</v>
-      </c>
-      <c r="V13">
-        <v>-2.9067148530632813E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-1.7651534394641632E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>23</v>
       </c>
       <c r="B14">
-        <v>0.91363293020904823</v>
+        <v>0.49122146912925674</v>
       </c>
       <c r="C14">
-        <v>6.1294099615593917E-5</v>
+        <v>3.1269100227479638E-5</v>
       </c>
       <c r="D14">
-        <v>3.4103201837190687E-5</v>
+        <v>2.2950209451772321E-5</v>
       </c>
       <c r="E14">
-        <v>-3.1483168902974696E-7</v>
+        <v>-1.1852410199472996E-7</v>
       </c>
       <c r="F14">
-        <v>4.8152370062228347E-6</v>
+        <v>5.7443552731727479E-5</v>
       </c>
       <c r="G14">
-        <v>1.6280603293120435E-4</v>
+        <v>3.0435724752003539E-4</v>
       </c>
       <c r="H14">
-        <v>9.4069080877933538E-7</v>
+        <v>1.5392332398127446E-7</v>
       </c>
       <c r="I14">
-        <v>-6.4048083255781861E-7</v>
+        <v>-6.4443121226778635E-7</v>
       </c>
       <c r="J14">
-        <v>-1.2207331365468731E-4</v>
+        <v>-2.4379470539813509E-4</v>
       </c>
       <c r="K14">
-        <v>-7.1894845293149902E-5</v>
+        <v>2.2746651508509389E-5</v>
       </c>
       <c r="L14">
-        <v>2.8509157708383026E-2</v>
+        <v>1.7215377659342602E-2</v>
       </c>
       <c r="M14">
-        <v>2.8536141005215909E-2</v>
+        <v>1.7247552955246426E-2</v>
       </c>
       <c r="N14">
-        <v>2.8616041737490997E-2</v>
+        <v>1.7324690720149732E-2</v>
       </c>
       <c r="O14">
-        <v>2.920107038444909E-2</v>
+        <v>1.7681132043213862E-2</v>
       </c>
       <c r="P14">
-        <v>-3.6111970164550347E-5</v>
+        <v>2.1452182486609547E-5</v>
       </c>
       <c r="Q14">
-        <v>-2.5111196804845367E-5</v>
+        <v>-5.4023507875570939E-5</v>
       </c>
       <c r="R14">
-        <v>-1.3646116657277342E-6</v>
+        <v>-4.3798029877907511E-5</v>
       </c>
       <c r="S14">
-        <v>9.9481991930745447E-6</v>
+        <v>-4.4838887993216332E-5</v>
       </c>
       <c r="T14">
-        <v>6.1766942069248909E-5</v>
-      </c>
-      <c r="U14">
-        <v>-3.2684015263871087E-5</v>
-      </c>
-      <c r="V14">
-        <v>-2.9452246561758398E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-1.8090847727421502E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B15">
-        <v>-0.26786040980057807</v>
+        <v>9.1512444742123417E-2</v>
       </c>
       <c r="C15">
-        <v>-1.6273547434868112E-5</v>
+        <v>-6.1464108917885527E-5</v>
       </c>
       <c r="D15">
-        <v>-1.2710962844650933E-5</v>
+        <v>5.5709331938870594E-6</v>
       </c>
       <c r="E15">
-        <v>1.7568667788743859E-7</v>
+        <v>-2.0604148177634348E-8</v>
       </c>
       <c r="F15">
-        <v>4.0023139970560851E-6</v>
+        <v>-1.1648871285234452E-5</v>
       </c>
       <c r="G15">
-        <v>-7.9728706141940229E-6</v>
+        <v>2.1429340788409727E-5</v>
       </c>
       <c r="H15">
-        <v>-6.3437651811458171E-7</v>
+        <v>-1.7956057731458988E-6</v>
       </c>
       <c r="I15">
-        <v>-9.7910868654901164E-7</v>
+        <v>-4.1702834453565751E-6</v>
       </c>
       <c r="J15">
-        <v>1.4757664045180552E-5</v>
+        <v>-3.4112190159680423E-5</v>
       </c>
       <c r="K15">
-        <v>9.2075989556389232E-6</v>
+        <v>-1.8271538025578626E-5</v>
       </c>
       <c r="L15">
-        <v>-3.1297203751018426E-5</v>
+        <v>6.32364938371161E-5</v>
       </c>
       <c r="M15">
-        <v>-3.540449539820411E-5</v>
+        <v>4.316117901410061E-5</v>
       </c>
       <c r="N15">
-        <v>-2.6204895517368548E-5</v>
+        <v>5.6619157188817133E-5</v>
       </c>
       <c r="O15">
-        <v>-3.6111970164550347E-5</v>
+        <v>2.1452182486609547E-5</v>
       </c>
       <c r="P15">
-        <v>8.9046143811138154E-4</v>
+        <v>1.2620728569009733E-3</v>
       </c>
       <c r="Q15">
-        <v>4.8503287544574816E-4</v>
+        <v>5.2503466645868139E-4</v>
       </c>
       <c r="R15">
-        <v>4.6932516112699779E-4</v>
+        <v>-4.7824327244749909E-5</v>
       </c>
       <c r="S15">
-        <v>4.7216743744985358E-4</v>
+        <v>2.7615157789853265E-5</v>
       </c>
       <c r="T15">
-        <v>7.4525230080244647E-8</v>
-      </c>
-      <c r="U15">
-        <v>-2.6341046621636003E-5</v>
-      </c>
-      <c r="V15">
-        <v>-2.1542445107446186E-4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-5.7381444879667687E-4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B16">
-        <v>-0.35286588340456737</v>
+        <v>-2.5226814404011727E-2</v>
       </c>
       <c r="C16">
-        <v>-3.3760732814085383E-5</v>
+        <v>-6.5924661821387381E-5</v>
       </c>
       <c r="D16">
-        <v>-1.4503501652579277E-5</v>
+        <v>2.1975487630731088E-6</v>
       </c>
       <c r="E16">
-        <v>1.9680529485039731E-7</v>
+        <v>6.708790667743035E-9</v>
       </c>
       <c r="F16">
-        <v>-4.8154454327020829E-5</v>
+        <v>1.0186587643995531E-6</v>
       </c>
       <c r="G16">
-        <v>-5.8679412485442828E-5</v>
+        <v>4.755229528934607E-5</v>
       </c>
       <c r="H16">
-        <v>5.3921373440098488E-7</v>
+        <v>-1.4943505850686548E-6</v>
       </c>
       <c r="I16">
-        <v>-3.7198490483373514E-7</v>
+        <v>-4.6446011006754738E-6</v>
       </c>
       <c r="J16">
-        <v>1.7320730165917126E-5</v>
+        <v>-2.7491097852160848E-5</v>
       </c>
       <c r="K16">
-        <v>1.6661628211515884E-5</v>
+        <v>-3.3035681801429531E-6</v>
       </c>
       <c r="L16">
-        <v>-2.0589748228410872E-5</v>
+        <v>1.5166887083754079E-5</v>
       </c>
       <c r="M16">
-        <v>-1.6701005917109117E-5</v>
+        <v>3.3141408100464216E-5</v>
       </c>
       <c r="N16">
-        <v>-8.7433813287080112E-6</v>
+        <v>5.509216180771395E-6</v>
       </c>
       <c r="O16">
-        <v>-2.5111196804845367E-5</v>
+        <v>-5.4023507875570939E-5</v>
       </c>
       <c r="P16">
-        <v>4.8503287544574816E-4</v>
+        <v>5.2503466645868139E-4</v>
       </c>
       <c r="Q16">
-        <v>1.5599421873778159E-3</v>
+        <v>7.4016057012875433E-4</v>
       </c>
       <c r="R16">
-        <v>4.6870793355038116E-4</v>
+        <v>-3.9519783256638604E-5</v>
       </c>
       <c r="S16">
-        <v>4.717639827649966E-4</v>
+        <v>2.299233525337744E-5</v>
       </c>
       <c r="T16">
-        <v>-1.7747917821755539E-5</v>
-      </c>
-      <c r="U16">
-        <v>-3.7355662258887558E-5</v>
-      </c>
-      <c r="V16">
-        <v>-1.7349226236123026E-4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-4.4107429845300234E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B17">
-        <v>0.11105600720176947</v>
+        <v>6.7342262227950062E-2</v>
       </c>
       <c r="C17">
-        <v>1.0901398922579113E-5</v>
+        <v>3.8061812814572471E-5</v>
       </c>
       <c r="D17">
-        <v>5.200568741801719E-6</v>
+        <v>4.5136649462140327E-6</v>
       </c>
       <c r="E17">
-        <v>-4.4623846144080106E-8</v>
+        <v>-8.2842459819615595E-8</v>
       </c>
       <c r="F17">
-        <v>4.1104211242475963E-5</v>
+        <v>1.6256812978985142E-5</v>
       </c>
       <c r="G17">
-        <v>6.7840350773593061E-5</v>
+        <v>-4.7112705801565487E-5</v>
       </c>
       <c r="H17">
-        <v>-1.1880234746643158E-6</v>
+        <v>-4.5779660277754077E-7</v>
       </c>
       <c r="I17">
-        <v>-1.6902565344256375E-6</v>
+        <v>1.0691929446943723E-6</v>
       </c>
       <c r="J17">
-        <v>-1.2016158282798979E-5</v>
+        <v>-4.5840737823717262E-7</v>
       </c>
       <c r="K17">
-        <v>-7.1545244131183002E-6</v>
+        <v>-1.1422744848480132E-5</v>
       </c>
       <c r="L17">
-        <v>-2.1386120416329335E-5</v>
+        <v>3.7033924186573579E-6</v>
       </c>
       <c r="M17">
-        <v>-1.8626532137844417E-5</v>
+        <v>-3.9166414312357233E-6</v>
       </c>
       <c r="N17">
-        <v>-2.5758271829982751E-5</v>
+        <v>-2.856006320035246E-5</v>
       </c>
       <c r="O17">
-        <v>-1.3646116657277342E-6</v>
+        <v>-4.3798029877907511E-5</v>
       </c>
       <c r="P17">
-        <v>4.6932516112699779E-4</v>
+        <v>-4.7824327244749909E-5</v>
       </c>
       <c r="Q17">
-        <v>4.6870793355038116E-4</v>
+        <v>-3.9519783256638604E-5</v>
       </c>
       <c r="R17">
-        <v>8.9581920400995689E-4</v>
+        <v>1.7141767877578424E-3</v>
       </c>
       <c r="S17">
-        <v>4.715721068588092E-4</v>
+        <v>1.7119065496610381E-4</v>
       </c>
       <c r="T17">
-        <v>4.1714795415615405E-6</v>
-      </c>
-      <c r="U17">
-        <v>-1.4172805172583029E-5</v>
-      </c>
-      <c r="V17">
-        <v>-5.7456784469772507E-4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-1.6142263027614008E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B18">
-        <v>1.0630422478857995E-2</v>
+        <v>1.0637848839892006</v>
       </c>
       <c r="C18">
-        <v>1.8385479859766073E-5</v>
+        <v>-1.0493851478589366E-4</v>
       </c>
       <c r="D18">
-        <v>-4.4712132475915855E-6</v>
+        <v>1.1263997760435979E-5</v>
       </c>
       <c r="E18">
-        <v>5.8990064685819371E-8</v>
+        <v>-2.0805479477080352E-7</v>
       </c>
       <c r="F18">
-        <v>2.5764357838610949E-6</v>
+        <v>-1.212529593334397E-4</v>
       </c>
       <c r="G18">
-        <v>3.7141872487147568E-5</v>
+        <v>-1.9636586633964823E-4</v>
       </c>
       <c r="H18">
-        <v>-2.5786038222979386E-7</v>
+        <v>3.1735206397113143E-6</v>
       </c>
       <c r="I18">
-        <v>-7.6104182566894405E-7</v>
+        <v>5.5466681339082879E-6</v>
       </c>
       <c r="J18">
-        <v>9.1399701098882153E-6</v>
+        <v>2.759855204656511E-5</v>
       </c>
       <c r="K18">
-        <v>-2.5040033411454349E-6</v>
+        <v>-1.0511514962281496E-5</v>
       </c>
       <c r="L18">
-        <v>-1.2886341011788887E-5</v>
+        <v>1.1912172788867128E-5</v>
       </c>
       <c r="M18">
-        <v>-3.1134741049297139E-5</v>
+        <v>9.7714829693170918E-6</v>
       </c>
       <c r="N18">
-        <v>-1.6721963451605068E-5</v>
+        <v>-2.3261638219552246E-5</v>
       </c>
       <c r="O18">
-        <v>9.9481991930745447E-6</v>
+        <v>-4.4838887993216332E-5</v>
       </c>
       <c r="P18">
-        <v>4.7216743744985358E-4</v>
+        <v>2.7615157789853265E-5</v>
       </c>
       <c r="Q18">
-        <v>4.717639827649966E-4</v>
+        <v>2.299233525337744E-5</v>
       </c>
       <c r="R18">
-        <v>4.715721068588092E-4</v>
+        <v>1.7119065496610381E-4</v>
       </c>
       <c r="S18">
-        <v>8.6286103973166038E-4</v>
+        <v>8.8965185154678771E-4</v>
       </c>
       <c r="T18">
-        <v>-4.868256881313039E-6</v>
-      </c>
-      <c r="U18">
-        <v>-2.4427910689053081E-5</v>
-      </c>
-      <c r="V18">
-        <v>-3.97230615542016E-4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-1.6795397407608627E-4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B19">
-        <v>0.17956432953708484</v>
+        <v>-3.8343825381182262</v>
       </c>
       <c r="C19">
-        <v>1.8874347566381409E-5</v>
+        <v>1.398899001211567E-3</v>
       </c>
       <c r="D19">
-        <v>6.0106180845996498E-6</v>
+        <v>-1.4220714248964733E-3</v>
       </c>
       <c r="E19">
-        <v>-8.7631537029292095E-8</v>
+        <v>1.4627140391797511E-5</v>
       </c>
       <c r="F19">
-        <v>2.2720434751779484E-5</v>
+        <v>-8.8072451803098608E-3</v>
       </c>
       <c r="G19">
-        <v>-2.8166262021654259E-5</v>
+        <v>-3.9453805781703658E-3</v>
       </c>
       <c r="H19">
-        <v>-2.9237019994472268E-7</v>
+        <v>2.0263866971255971E-4</v>
       </c>
       <c r="I19">
-        <v>1.314433249950561E-6</v>
+        <v>8.9241642087114091E-5</v>
       </c>
       <c r="J19">
-        <v>9.7447062474013729E-6</v>
+        <v>1.1703376287154708E-3</v>
       </c>
       <c r="K19">
-        <v>-9.5444570478221848E-6</v>
+        <v>1.4444425413847272E-3</v>
       </c>
       <c r="L19">
-        <v>-1.1216279089027993E-5</v>
+        <v>-1.7272656449471829E-2</v>
       </c>
       <c r="M19">
-        <v>-3.1241202171240057E-5</v>
+        <v>-1.7604989738692553E-2</v>
       </c>
       <c r="N19">
-        <v>4.5840177877870983E-5</v>
+        <v>-1.7651534394641632E-2</v>
       </c>
       <c r="O19">
-        <v>6.1766942069248909E-5</v>
+        <v>-1.8090847727421502E-2</v>
       </c>
       <c r="P19">
-        <v>7.4525230080244647E-8</v>
+        <v>-5.7381444879667687E-4</v>
       </c>
       <c r="Q19">
-        <v>-1.7747917821755539E-5</v>
+        <v>-4.4107429845300234E-4</v>
       </c>
       <c r="R19">
-        <v>4.1714795415615405E-6</v>
+        <v>-1.6142263027614008E-4</v>
       </c>
       <c r="S19">
-        <v>-4.868256881313039E-6</v>
+        <v>-1.6795397407608627E-4</v>
       </c>
       <c r="T19">
-        <v>1.3818716919700869E-3</v>
-      </c>
-      <c r="U19">
-        <v>1.2969727063383236E-4</v>
-      </c>
-      <c r="V19">
-        <v>-2.7972814222336625E-4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20">
-        <v>0.62374525577498652</v>
-      </c>
-      <c r="C20">
-        <v>-8.375054267015991E-5</v>
-      </c>
-      <c r="D20">
-        <v>7.2175247270978005E-6</v>
-      </c>
-      <c r="E20">
-        <v>-1.2715301218480037E-7</v>
-      </c>
-      <c r="F20">
-        <v>-5.5264533989758388E-6</v>
-      </c>
-      <c r="G20">
-        <v>-4.644099810281029E-5</v>
-      </c>
-      <c r="H20">
-        <v>8.7581850161201109E-7</v>
-      </c>
-      <c r="I20">
-        <v>2.4602606338683487E-6</v>
-      </c>
-      <c r="J20">
-        <v>2.8430271963535789E-5</v>
-      </c>
-      <c r="K20">
-        <v>-4.8815517316311754E-7</v>
-      </c>
-      <c r="L20">
-        <v>2.766801843273788E-5</v>
-      </c>
-      <c r="M20">
-        <v>2.9616187938088475E-5</v>
-      </c>
-      <c r="N20">
-        <v>1.5002953793197569E-5</v>
-      </c>
-      <c r="O20">
-        <v>-3.2684015263871087E-5</v>
-      </c>
-      <c r="P20">
-        <v>-2.6341046621636003E-5</v>
-      </c>
-      <c r="Q20">
-        <v>-3.7355662258887558E-5</v>
-      </c>
-      <c r="R20">
-        <v>-1.4172805172583029E-5</v>
-      </c>
-      <c r="S20">
-        <v>-2.4427910689053081E-5</v>
-      </c>
-      <c r="T20">
-        <v>1.2969727063383236E-4</v>
-      </c>
-      <c r="U20">
-        <v>7.4577641535213373E-4</v>
-      </c>
-      <c r="V20">
-        <v>-1.5803694773224814E-4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21">
-        <v>-4.7501456095551307</v>
-      </c>
-      <c r="C21">
-        <v>1.7248638636402369E-3</v>
-      </c>
-      <c r="D21">
-        <v>-1.0949341663041032E-3</v>
-      </c>
-      <c r="E21">
-        <v>1.0811166992187685E-5</v>
-      </c>
-      <c r="F21">
-        <v>-7.9092310393618689E-3</v>
-      </c>
-      <c r="G21">
-        <v>-7.5302828888323186E-3</v>
-      </c>
-      <c r="H21">
-        <v>1.7931262215968425E-4</v>
-      </c>
-      <c r="I21">
-        <v>1.6624589291442966E-4</v>
-      </c>
-      <c r="J21">
-        <v>5.9218191460279508E-4</v>
-      </c>
-      <c r="K21">
-        <v>1.3550557304967494E-3</v>
-      </c>
-      <c r="L21">
-        <v>-2.8705309677373732E-2</v>
-      </c>
-      <c r="M21">
-        <v>-2.8903065279276982E-2</v>
-      </c>
-      <c r="N21">
-        <v>-2.9067148530632813E-2</v>
-      </c>
-      <c r="O21">
-        <v>-2.9452246561758398E-2</v>
-      </c>
-      <c r="P21">
-        <v>-2.1542445107446186E-4</v>
-      </c>
-      <c r="Q21">
-        <v>-1.7349226236123026E-4</v>
-      </c>
-      <c r="R21">
-        <v>-5.7456784469772507E-4</v>
-      </c>
-      <c r="S21">
-        <v>-3.97230615542016E-4</v>
-      </c>
-      <c r="T21">
-        <v>-2.7972814222336625E-4</v>
-      </c>
-      <c r="U21">
-        <v>-1.5803694773224814E-4</v>
-      </c>
-      <c r="V21">
-        <v>5.2525142654521406E-2</v>
+        <v>4.7692134851323488E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2053,14 +1792,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D773F3FA-C4BA-4705-8D71-D1937FA78488}">
-  <dimension ref="A1:V21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="16384" width="9" style="2"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6EB2D24-7CBE-41F9-A89C-D253E7F2E47A}">
+  <dimension ref="A1:T19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -2107,1385 +1843,1135 @@
         <v>23</v>
       </c>
       <c r="P1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="Q1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="R1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="S1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="T1" t="s">
-        <v>24</v>
-      </c>
-      <c r="U1" t="s">
-        <v>25</v>
-      </c>
-      <c r="V1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2">
-        <v>0.50425118491352194</v>
+        <v>0.43668587059260894</v>
       </c>
       <c r="C2">
-        <v>1.5513349142365351E-3</v>
+        <v>2.5568957447742566E-3</v>
       </c>
       <c r="D2">
-        <v>-1.3839886611606171E-4</v>
+        <v>-1.6160753526637807E-4</v>
       </c>
       <c r="E2">
-        <v>1.2826860469353707E-6</v>
+        <v>1.6630418308507975E-6</v>
       </c>
       <c r="F2">
-        <v>-5.931138215543631E-4</v>
+        <v>-1.8765853218495219E-6</v>
       </c>
       <c r="G2">
-        <v>-9.3056703202818976E-4</v>
+        <v>-2.0343342878252778E-4</v>
       </c>
       <c r="H2">
-        <v>1.1099925893861188E-5</v>
+        <v>2.2507208681650878E-7</v>
       </c>
       <c r="I2">
-        <v>1.765062343616857E-5</v>
+        <v>4.0641519674414828E-6</v>
       </c>
       <c r="J2">
-        <v>-4.125012782869953E-5</v>
+        <v>-1.0747543723589726E-5</v>
       </c>
       <c r="K2">
-        <v>6.2813879773172807E-5</v>
+        <v>6.9632110029629532E-5</v>
       </c>
       <c r="L2">
-        <v>8.8037436689705241E-7</v>
+        <v>2.4213498727547304E-5</v>
       </c>
       <c r="M2">
-        <v>-3.6639078037964314E-7</v>
+        <v>8.1352511901958569E-6</v>
       </c>
       <c r="N2">
-        <v>1.2341474702685278E-5</v>
+        <v>-7.0994083861100794E-7</v>
       </c>
       <c r="O2">
-        <v>2.4404058788132137E-5</v>
+        <v>2.0909066397714095E-5</v>
       </c>
       <c r="P2">
-        <v>-5.633428379076934E-5</v>
+        <v>-3.6218105011012633E-5</v>
       </c>
       <c r="Q2">
-        <v>-6.7981893989445038E-5</v>
+        <v>-7.7127632971599975E-5</v>
       </c>
       <c r="R2">
-        <v>1.8240103666792586E-5</v>
+        <v>3.6716428573918818E-5</v>
       </c>
       <c r="S2">
-        <v>2.8082263203433976E-6</v>
+        <v>-1.16798750228618E-4</v>
       </c>
       <c r="T2">
-        <v>4.8433491299694167E-5</v>
-      </c>
-      <c r="U2">
-        <v>-8.7821648003127406E-5</v>
-      </c>
-      <c r="V2">
-        <v>2.1135761796003765E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1.2561212095509088E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
       <c r="B3">
-        <v>0.18252363936729663</v>
+        <v>0.15627337833411392</v>
       </c>
       <c r="C3">
-        <v>-1.3839886611606171E-4</v>
+        <v>-1.6160753526637807E-4</v>
       </c>
       <c r="D3">
-        <v>5.9760636271713984E-5</v>
+        <v>7.4634436364664309E-5</v>
       </c>
       <c r="E3">
-        <v>-6.1489608569122539E-7</v>
+        <v>-7.9997725870035146E-7</v>
       </c>
       <c r="F3">
-        <v>3.6223209976182682E-4</v>
+        <v>3.7301225142939817E-4</v>
       </c>
       <c r="G3">
-        <v>3.7614218102040916E-4</v>
+        <v>2.3810953538269442E-4</v>
       </c>
       <c r="H3">
-        <v>-8.2037297785451395E-6</v>
+        <v>-8.4993407060088949E-6</v>
       </c>
       <c r="I3">
-        <v>-8.3227219028984411E-6</v>
+        <v>-5.3483665428287653E-6</v>
       </c>
       <c r="J3">
-        <v>3.2817800098948027E-5</v>
+        <v>2.2719795015497259E-5</v>
       </c>
       <c r="K3">
-        <v>-1.0863311401088721E-4</v>
+        <v>-1.2045215415441539E-4</v>
       </c>
       <c r="L3">
-        <v>9.7619381314763146E-6</v>
+        <v>9.4970488661783774E-6</v>
       </c>
       <c r="M3">
-        <v>2.6624947335463921E-5</v>
+        <v>3.138395005509954E-5</v>
       </c>
       <c r="N3">
-        <v>3.0659319750468662E-5</v>
+        <v>2.9523282920097826E-5</v>
       </c>
       <c r="O3">
-        <v>4.1142373071674878E-5</v>
+        <v>3.9833238287565701E-5</v>
       </c>
       <c r="P3">
-        <v>-2.007379904970174E-5</v>
+        <v>1.1522062061736558E-5</v>
       </c>
       <c r="Q3">
-        <v>-2.0168265853773191E-5</v>
+        <v>3.7763215884643533E-6</v>
       </c>
       <c r="R3">
-        <v>6.6670395586744199E-6</v>
+        <v>4.1953302497180385E-6</v>
       </c>
       <c r="S3">
-        <v>-7.183730504462563E-6</v>
+        <v>1.763653129127575E-5</v>
       </c>
       <c r="T3">
-        <v>2.8424227399921806E-6</v>
-      </c>
-      <c r="U3">
-        <v>5.5876513712006746E-6</v>
-      </c>
-      <c r="V3">
-        <v>-1.2135338648586232E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-1.4667889021322644E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>15</v>
       </c>
       <c r="B4">
-        <v>-2.214246665597574E-3</v>
+        <v>-2.0892098091465521E-3</v>
       </c>
       <c r="C4">
-        <v>1.2826860469353707E-6</v>
+        <v>1.6630418308507975E-6</v>
       </c>
       <c r="D4">
-        <v>-6.1489608569122539E-7</v>
+        <v>-7.9997725870035146E-7</v>
       </c>
       <c r="E4">
-        <v>6.9732536386415657E-9</v>
+        <v>9.253029863264477E-9</v>
       </c>
       <c r="F4">
-        <v>-1.9771375784643424E-6</v>
+        <v>-2.2766510740058394E-6</v>
       </c>
       <c r="G4">
-        <v>-2.0594750884581404E-6</v>
+        <v>-6.1258075043670786E-7</v>
       </c>
       <c r="H4">
-        <v>4.0392049027023244E-8</v>
+        <v>5.0062483964468494E-8</v>
       </c>
       <c r="I4">
-        <v>4.0497469153106058E-8</v>
+        <v>1.17958428418316E-8</v>
       </c>
       <c r="J4">
-        <v>-6.5337892095292143E-7</v>
+        <v>-7.2423410720815564E-7</v>
       </c>
       <c r="K4">
-        <v>1.366273101928776E-6</v>
+        <v>1.5612052945631879E-6</v>
       </c>
       <c r="L4">
-        <v>-1.1986396671098024E-7</v>
+        <v>-9.041048451205464E-8</v>
       </c>
       <c r="M4">
-        <v>-3.0907359851283554E-7</v>
+        <v>-3.3488745598163991E-7</v>
       </c>
       <c r="N4">
-        <v>-3.0106395144344097E-7</v>
+        <v>-2.9897615101005556E-7</v>
       </c>
       <c r="O4">
-        <v>-3.7607325233588207E-7</v>
+        <v>-2.6137860812812735E-7</v>
       </c>
       <c r="P4">
-        <v>2.3923092225659446E-7</v>
+        <v>-1.4210239934862992E-7</v>
       </c>
       <c r="Q4">
-        <v>2.5717182237881744E-7</v>
+        <v>-5.0455997392773559E-8</v>
       </c>
       <c r="R4">
-        <v>-8.1045343476648411E-8</v>
+        <v>-9.3693630356179366E-8</v>
       </c>
       <c r="S4">
-        <v>6.8983389491732019E-8</v>
+        <v>-2.6428300745777232E-7</v>
       </c>
       <c r="T4">
-        <v>-6.3144177830298084E-8</v>
-      </c>
-      <c r="U4">
-        <v>-8.7324628151455999E-8</v>
-      </c>
-      <c r="V4">
-        <v>1.1492040000878157E-5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1.455269325693747E-5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
       <c r="B5">
-        <v>0.40098030006401664</v>
+        <v>-0.32649593215279021</v>
       </c>
       <c r="C5">
-        <v>-5.931138215543631E-4</v>
+        <v>-1.8765853218495219E-6</v>
       </c>
       <c r="D5">
-        <v>3.6223209976182682E-4</v>
+        <v>3.7301225142939817E-4</v>
       </c>
       <c r="E5">
-        <v>-1.9771375784643424E-6</v>
+        <v>-2.2766510740058394E-6</v>
       </c>
       <c r="F5">
-        <v>1.0686127117571963E-2</v>
+        <v>1.1149045807578323E-2</v>
       </c>
       <c r="G5">
-        <v>8.7528362832745704E-3</v>
+        <v>8.1378823187552816E-3</v>
       </c>
       <c r="H5">
-        <v>-2.4116604787555347E-4</v>
+        <v>-2.4675740113501389E-4</v>
       </c>
       <c r="I5">
-        <v>-1.9456879046660271E-4</v>
+        <v>-1.7664502058843863E-4</v>
       </c>
       <c r="J5">
-        <v>5.6826785998785644E-5</v>
+        <v>-1.6135059323317469E-5</v>
       </c>
       <c r="K5">
-        <v>-3.2316933414532013E-4</v>
+        <v>-3.3292941757046604E-4</v>
       </c>
       <c r="L5">
-        <v>-2.0950495167222812E-5</v>
+        <v>2.5664612894364062E-5</v>
       </c>
       <c r="M5">
-        <v>6.9806039587732779E-5</v>
+        <v>1.593253300776476E-4</v>
       </c>
       <c r="N5">
-        <v>8.9478972701394731E-5</v>
+        <v>1.1321726496671273E-4</v>
       </c>
       <c r="O5">
-        <v>1.1006158296243511E-4</v>
+        <v>1.5240668848018335E-4</v>
       </c>
       <c r="P5">
-        <v>-1.1692509693025001E-4</v>
+        <v>-9.501688195880773E-5</v>
       </c>
       <c r="Q5">
-        <v>-6.525042069148821E-5</v>
+        <v>-8.7376357364359593E-5</v>
       </c>
       <c r="R5">
-        <v>4.7106546890782924E-5</v>
+        <v>-9.0170410835784648E-5</v>
       </c>
       <c r="S5">
-        <v>-5.6116741086540336E-5</v>
+        <v>-8.7468115630738298E-5</v>
       </c>
       <c r="T5">
-        <v>1.1726714774824312E-5</v>
-      </c>
-      <c r="U5">
-        <v>7.0282592051261968E-5</v>
-      </c>
-      <c r="V5">
-        <v>-1.1369411803076617E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-1.1908552948735926E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
       <c r="B6">
-        <v>6.5404936912107525E-2</v>
+        <v>-0.90470392580219616</v>
       </c>
       <c r="C6">
-        <v>-9.3056703202818976E-4</v>
+        <v>-2.0343342878252778E-4</v>
       </c>
       <c r="D6">
-        <v>3.7614218102040916E-4</v>
+        <v>2.3810953538269442E-4</v>
       </c>
       <c r="E6">
-        <v>-2.0594750884581404E-6</v>
+        <v>-6.1258075043670786E-7</v>
       </c>
       <c r="F6">
-        <v>8.7528362832745704E-3</v>
+        <v>8.1378823187552816E-3</v>
       </c>
       <c r="G6">
-        <v>1.253725975838803E-2</v>
+        <v>1.8467353360314007E-2</v>
       </c>
       <c r="H6">
-        <v>-1.9507298255068848E-4</v>
+        <v>-1.7706151212886046E-4</v>
       </c>
       <c r="I6">
-        <v>-2.7202895111399443E-4</v>
+        <v>-3.7844256378232822E-4</v>
       </c>
       <c r="J6">
-        <v>8.6797660915085141E-5</v>
+        <v>-1.1969337510339627E-4</v>
       </c>
       <c r="K6">
-        <v>-5.1582805026451843E-4</v>
+        <v>-6.17660450088344E-4</v>
       </c>
       <c r="L6">
-        <v>-2.1170127628869322E-5</v>
+        <v>2.280431481064514E-4</v>
       </c>
       <c r="M6">
-        <v>8.5465301788708453E-5</v>
+        <v>4.3006484791024589E-4</v>
       </c>
       <c r="N6">
-        <v>6.7528964189649855E-5</v>
+        <v>3.4290517103337075E-4</v>
       </c>
       <c r="O6">
-        <v>1.106191733463522E-4</v>
+        <v>5.0847549359970797E-4</v>
       </c>
       <c r="P6">
-        <v>-1.5682799681585014E-4</v>
+        <v>-2.2208813120456615E-4</v>
       </c>
       <c r="Q6">
-        <v>-1.6614940935216939E-4</v>
+        <v>-1.3022826275288512E-4</v>
       </c>
       <c r="R6">
-        <v>3.2224543308459523E-5</v>
+        <v>-1.2587884694016077E-4</v>
       </c>
       <c r="S6">
-        <v>-5.6462187147624115E-5</v>
+        <v>-1.043152686738882E-4</v>
       </c>
       <c r="T6">
-        <v>-8.9688314900029012E-6</v>
-      </c>
-      <c r="U6">
-        <v>6.7002040305126593E-5</v>
-      </c>
-      <c r="V6">
-        <v>-1.1473974449422114E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-9.4408583191362885E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>27</v>
       </c>
       <c r="B7">
-        <v>-1.3997905106199048E-2</v>
+        <v>4.8298493919890226E-3</v>
       </c>
       <c r="C7">
-        <v>1.1099925893861188E-5</v>
+        <v>2.2507208681650878E-7</v>
       </c>
       <c r="D7">
-        <v>-8.2037297785451395E-6</v>
+        <v>-8.4993407060088949E-6</v>
       </c>
       <c r="E7">
-        <v>4.0392049027023244E-8</v>
+        <v>5.0062483964468494E-8</v>
       </c>
       <c r="F7">
-        <v>-2.4116604787555347E-4</v>
+        <v>-2.4675740113501389E-4</v>
       </c>
       <c r="G7">
-        <v>-1.9507298255068848E-4</v>
+        <v>-1.7706151212886046E-4</v>
       </c>
       <c r="H7">
-        <v>6.0919925626952542E-6</v>
+        <v>6.0261462184450586E-6</v>
       </c>
       <c r="I7">
-        <v>4.8115847506615147E-6</v>
+        <v>4.2288324238880603E-6</v>
       </c>
       <c r="J7">
-        <v>-1.9325420505484026E-6</v>
+        <v>-3.6564833097395101E-7</v>
       </c>
       <c r="K7">
-        <v>7.4323861709993005E-6</v>
+        <v>7.7722255608046816E-6</v>
       </c>
       <c r="L7">
-        <v>9.3094560155329673E-7</v>
+        <v>-3.4190198312184839E-8</v>
       </c>
       <c r="M7">
-        <v>-9.3861862338363573E-7</v>
+        <v>-2.9977510555807634E-6</v>
       </c>
       <c r="N7">
-        <v>-5.2400702685129294E-7</v>
+        <v>-1.4720681913171242E-6</v>
       </c>
       <c r="O7">
-        <v>-5.2062384240019811E-7</v>
+        <v>-6.4975789373493973E-7</v>
       </c>
       <c r="P7">
-        <v>2.2614496534139019E-6</v>
+        <v>3.4877770036912801E-7</v>
       </c>
       <c r="Q7">
-        <v>9.3509865662360169E-7</v>
+        <v>-5.1745731171826654E-7</v>
       </c>
       <c r="R7">
-        <v>-9.800781479070649E-7</v>
+        <v>1.7691335950913147E-6</v>
       </c>
       <c r="S7">
-        <v>1.2114894671584932E-6</v>
+        <v>2.2621939103586556E-6</v>
       </c>
       <c r="T7">
-        <v>2.3998349377131326E-7</v>
-      </c>
-      <c r="U7">
-        <v>-1.4058295414173764E-6</v>
-      </c>
-      <c r="V7">
-        <v>2.4707410183791111E-4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+        <v>2.5815627808192549E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>28</v>
       </c>
       <c r="B8">
-        <v>-9.7540869036671918E-3</v>
+        <v>1.6828999560925144E-2</v>
       </c>
       <c r="C8">
-        <v>1.765062343616857E-5</v>
+        <v>4.0641519674414828E-6</v>
       </c>
       <c r="D8">
-        <v>-8.3227219028984411E-6</v>
+        <v>-5.3483665428287653E-6</v>
       </c>
       <c r="E8">
-        <v>4.0497469153106058E-8</v>
+        <v>1.17958428418316E-8</v>
       </c>
       <c r="F8">
-        <v>-1.9456879046660271E-4</v>
+        <v>-1.7664502058843863E-4</v>
       </c>
       <c r="G8">
-        <v>-2.7202895111399443E-4</v>
+        <v>-3.7844256378232822E-4</v>
       </c>
       <c r="H8">
-        <v>4.8115847506615147E-6</v>
+        <v>4.2288324238880603E-6</v>
       </c>
       <c r="I8">
-        <v>6.5592980289774702E-6</v>
+        <v>8.4425961509244019E-6</v>
       </c>
       <c r="J8">
-        <v>-3.2966427201053343E-6</v>
+        <v>1.74521382029835E-6</v>
       </c>
       <c r="K8">
-        <v>1.1440087575023646E-5</v>
+        <v>1.3169600399856455E-5</v>
       </c>
       <c r="L8">
-        <v>2.5745688592189729E-6</v>
+        <v>-4.1841318875874864E-6</v>
       </c>
       <c r="M8">
-        <v>1.130909262816635E-6</v>
+        <v>-6.9659153241002927E-6</v>
       </c>
       <c r="N8">
-        <v>3.8311463178585838E-6</v>
+        <v>-2.2662637667758854E-6</v>
       </c>
       <c r="O8">
-        <v>3.8738021320321777E-6</v>
+        <v>-2.9694043181968205E-6</v>
       </c>
       <c r="P8">
-        <v>1.8994797715959573E-6</v>
+        <v>4.3057799521690276E-7</v>
       </c>
       <c r="Q8">
-        <v>1.5564253335045741E-6</v>
+        <v>-1.9016170975918895E-6</v>
       </c>
       <c r="R8">
-        <v>-6.1179497848918737E-7</v>
+        <v>3.2997823652622863E-6</v>
       </c>
       <c r="S8">
-        <v>1.3138775231535278E-6</v>
+        <v>3.2499500820182957E-6</v>
       </c>
       <c r="T8">
-        <v>9.0943341480079639E-7</v>
-      </c>
-      <c r="U8">
-        <v>-3.5319060234169612E-7</v>
-      </c>
-      <c r="V8">
-        <v>2.4214364679901816E-4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1.965224241221195E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>18</v>
       </c>
       <c r="B9">
-        <v>0.18446348100628215</v>
+        <v>0.24868447822912776</v>
       </c>
       <c r="C9">
-        <v>-4.125012782869953E-5</v>
+        <v>-1.0747543723589726E-5</v>
       </c>
       <c r="D9">
-        <v>3.2817800098948027E-5</v>
+        <v>2.2719795015497259E-5</v>
       </c>
       <c r="E9">
-        <v>-6.5337892095292143E-7</v>
+        <v>-7.2423410720815564E-7</v>
       </c>
       <c r="F9">
-        <v>5.6826785998785644E-5</v>
+        <v>-1.6135059323317469E-5</v>
       </c>
       <c r="G9">
-        <v>8.6797660915085141E-5</v>
+        <v>-1.1969337510339627E-4</v>
       </c>
       <c r="H9">
-        <v>-1.9325420505484026E-6</v>
+        <v>-3.6564833097395101E-7</v>
       </c>
       <c r="I9">
-        <v>-3.2966427201053343E-6</v>
+        <v>1.74521382029835E-6</v>
       </c>
       <c r="J9">
-        <v>1.3800933407625835E-3</v>
+        <v>1.767643663722017E-3</v>
       </c>
       <c r="K9">
-        <v>-9.4808757728889889E-4</v>
+        <v>-1.0539904763044426E-3</v>
       </c>
       <c r="L9">
-        <v>-1.4008095564216043E-4</v>
+        <v>-9.5282465612656653E-5</v>
       </c>
       <c r="M9">
-        <v>-1.5398616794187173E-4</v>
+        <v>-1.9098934676144689E-4</v>
       </c>
       <c r="N9">
-        <v>-1.5679509086251602E-4</v>
+        <v>-2.3929280528861078E-4</v>
       </c>
       <c r="O9">
-        <v>-1.413266154437816E-4</v>
+        <v>-2.301748254374476E-4</v>
       </c>
       <c r="P9">
-        <v>2.2375872693351891E-5</v>
+        <v>-2.5076848702504313E-6</v>
       </c>
       <c r="Q9">
-        <v>1.2283449777824471E-5</v>
+        <v>1.0147818512118499E-5</v>
       </c>
       <c r="R9">
-        <v>2.0744213983872447E-5</v>
+        <v>3.2398557324411248E-5</v>
       </c>
       <c r="S9">
-        <v>3.3687887360288884E-5</v>
+        <v>1.9261140376020396E-5</v>
       </c>
       <c r="T9">
-        <v>6.8004106459347097E-5</v>
-      </c>
-      <c r="U9">
-        <v>3.3400116638942346E-5</v>
-      </c>
-      <c r="V9">
-        <v>-2.9233462774163265E-4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+        <v>9.2616363813803935E-5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
       <c r="B10">
-        <v>0.19145587494713057</v>
+        <v>0.12845708186841398</v>
       </c>
       <c r="C10">
-        <v>6.2813879773172807E-5</v>
+        <v>6.9632110029629532E-5</v>
       </c>
       <c r="D10">
-        <v>-1.0863311401088721E-4</v>
+        <v>-1.2045215415441539E-4</v>
       </c>
       <c r="E10">
-        <v>1.366273101928776E-6</v>
+        <v>1.5612052945631879E-6</v>
       </c>
       <c r="F10">
-        <v>-3.2316933414532013E-4</v>
+        <v>-3.3292941757046604E-4</v>
       </c>
       <c r="G10">
-        <v>-5.1582805026451843E-4</v>
+        <v>-6.17660450088344E-4</v>
       </c>
       <c r="H10">
-        <v>7.4323861709993005E-6</v>
+        <v>7.7722255608046816E-6</v>
       </c>
       <c r="I10">
-        <v>1.1440087575023646E-5</v>
+        <v>1.3169600399856455E-5</v>
       </c>
       <c r="J10">
-        <v>-9.4808757728889889E-4</v>
+        <v>-1.0539904763044426E-3</v>
       </c>
       <c r="K10">
-        <v>1.8101260902535622E-3</v>
+        <v>1.8115187682896012E-3</v>
       </c>
       <c r="L10">
-        <v>-2.7516307362102348E-5</v>
+        <v>-4.8499750928214275E-5</v>
       </c>
       <c r="M10">
-        <v>-5.4029907755533645E-5</v>
+        <v>-4.066647766134599E-5</v>
       </c>
       <c r="N10">
-        <v>-9.1579121602614532E-5</v>
+        <v>-5.0047647171482207E-5</v>
       </c>
       <c r="O10">
-        <v>-9.2751549404130012E-5</v>
+        <v>-6.4067870757137844E-5</v>
       </c>
       <c r="P10">
-        <v>-1.0239731905631585E-5</v>
+        <v>-2.6186504703842429E-5</v>
       </c>
       <c r="Q10">
-        <v>-1.6708044031186229E-5</v>
+        <v>-1.794263341084748E-7</v>
       </c>
       <c r="R10">
-        <v>-1.1771057760015703E-5</v>
+        <v>-1.482211225860103E-7</v>
       </c>
       <c r="S10">
-        <v>-3.7509506585605932E-6</v>
+        <v>-5.1166959546987749E-5</v>
       </c>
       <c r="T10">
-        <v>-1.3297267849727595E-5</v>
-      </c>
-      <c r="U10">
-        <v>-4.407866611521999E-5</v>
-      </c>
-      <c r="V10">
-        <v>2.0015908231555864E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+        <v>2.1446093728786321E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
       <c r="B11">
-        <v>0.39518746898999313</v>
+        <v>6.2563100929980256E-2</v>
       </c>
       <c r="C11">
-        <v>8.8037436689705241E-7</v>
+        <v>2.4213498727547304E-5</v>
       </c>
       <c r="D11">
-        <v>9.7619381314763146E-6</v>
+        <v>9.4970488661783774E-6</v>
       </c>
       <c r="E11">
-        <v>-1.1986396671098024E-7</v>
+        <v>-9.041048451205464E-8</v>
       </c>
       <c r="F11">
-        <v>-2.0950495167222812E-5</v>
+        <v>2.5664612894364062E-5</v>
       </c>
       <c r="G11">
-        <v>-2.1170127628869322E-5</v>
+        <v>2.280431481064514E-4</v>
       </c>
       <c r="H11">
-        <v>9.3094560155329673E-7</v>
+        <v>-3.4190198312184839E-8</v>
       </c>
       <c r="I11">
-        <v>2.5745688592189729E-6</v>
+        <v>-4.1841318875874864E-6</v>
       </c>
       <c r="J11">
-        <v>-1.4008095564216043E-4</v>
+        <v>-9.5282465612656653E-5</v>
       </c>
       <c r="K11">
-        <v>-2.7516307362102348E-5</v>
+        <v>-4.8499750928214275E-5</v>
       </c>
       <c r="L11">
-        <v>2.7010697371817181E-2</v>
+        <v>2.1220813215489458E-2</v>
       </c>
       <c r="M11">
-        <v>2.2855249211247507E-2</v>
+        <v>1.5093399038015742E-2</v>
       </c>
       <c r="N11">
-        <v>2.2856575685607436E-2</v>
+        <v>1.5094584282061767E-2</v>
       </c>
       <c r="O11">
-        <v>2.2847225575647161E-2</v>
+        <v>1.508438752988253E-2</v>
       </c>
       <c r="P11">
-        <v>-5.9772559815235478E-5</v>
+        <v>-3.1012892523894981E-5</v>
       </c>
       <c r="Q11">
-        <v>-4.8983450408092186E-5</v>
+        <v>-4.6482086377957284E-5</v>
       </c>
       <c r="R11">
-        <v>-7.5777641825174188E-5</v>
+        <v>1.1609987814602234E-5</v>
       </c>
       <c r="S11">
-        <v>-3.9933613418909579E-5</v>
+        <v>1.9098968733139942E-5</v>
       </c>
       <c r="T11">
-        <v>-1.0445932773522623E-4</v>
-      </c>
-      <c r="U11">
-        <v>7.8286199803674503E-5</v>
-      </c>
-      <c r="V11">
-        <v>-2.2975361075814695E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-1.5268884155399374E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
       <c r="B12">
-        <v>0.85563044492769669</v>
+        <v>0.50964323885394702</v>
       </c>
       <c r="C12">
-        <v>-3.6639078037964314E-7</v>
+        <v>8.1352511901958569E-6</v>
       </c>
       <c r="D12">
-        <v>2.6624947335463921E-5</v>
+        <v>3.138395005509954E-5</v>
       </c>
       <c r="E12">
-        <v>-3.0907359851283554E-7</v>
+        <v>-3.3488745598163991E-7</v>
       </c>
       <c r="F12">
-        <v>6.9806039587732779E-5</v>
+        <v>1.593253300776476E-4</v>
       </c>
       <c r="G12">
-        <v>8.5465301788708453E-5</v>
+        <v>4.3006484791024589E-4</v>
       </c>
       <c r="H12">
-        <v>-9.3861862338363573E-7</v>
+        <v>-2.9977510555807634E-6</v>
       </c>
       <c r="I12">
-        <v>1.130909262816635E-6</v>
+        <v>-6.9659153241002927E-6</v>
       </c>
       <c r="J12">
-        <v>-1.5398616794187173E-4</v>
+        <v>-1.9098934676144689E-4</v>
       </c>
       <c r="K12">
-        <v>-5.4029907755533645E-5</v>
+        <v>-4.066647766134599E-5</v>
       </c>
       <c r="L12">
-        <v>2.2855249211247507E-2</v>
+        <v>1.5093399038015742E-2</v>
       </c>
       <c r="M12">
-        <v>2.3886932477869278E-2</v>
+        <v>1.7209043073311236E-2</v>
       </c>
       <c r="N12">
-        <v>2.2882371928567305E-2</v>
+        <v>1.5141844528265383E-2</v>
       </c>
       <c r="O12">
-        <v>2.2875243795740453E-2</v>
+        <v>1.5101147885119955E-2</v>
       </c>
       <c r="P12">
-        <v>-8.0031989788873007E-5</v>
+        <v>5.8640897497250503E-6</v>
       </c>
       <c r="Q12">
-        <v>-7.1663656884999786E-5</v>
+        <v>-7.3386886848249777E-6</v>
       </c>
       <c r="R12">
-        <v>-5.064840622069557E-5</v>
+        <v>-2.9467657478653099E-5</v>
       </c>
       <c r="S12">
-        <v>-7.2024739302124769E-5</v>
+        <v>2.4243599676069535E-5</v>
       </c>
       <c r="T12">
-        <v>-1.7758867580389809E-4</v>
-      </c>
-      <c r="U12">
-        <v>6.4477605278316738E-5</v>
-      </c>
-      <c r="V12">
-        <v>-2.3331216461684356E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-1.5733268934418437E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>22</v>
       </c>
       <c r="B13">
-        <v>1.0213114002698978</v>
+        <v>0.79897018659843799</v>
       </c>
       <c r="C13">
-        <v>1.2341474702685278E-5</v>
+        <v>-7.0994083861100794E-7</v>
       </c>
       <c r="D13">
-        <v>3.0659319750468662E-5</v>
+        <v>2.9523282920097826E-5</v>
       </c>
       <c r="E13">
-        <v>-3.0106395144344097E-7</v>
+        <v>-2.9897615101005556E-7</v>
       </c>
       <c r="F13">
-        <v>8.9478972701394731E-5</v>
+        <v>1.1321726496671273E-4</v>
       </c>
       <c r="G13">
-        <v>6.7528964189649855E-5</v>
+        <v>3.4290517103337075E-4</v>
       </c>
       <c r="H13">
-        <v>-5.2400702685129294E-7</v>
+        <v>-1.4720681913171242E-6</v>
       </c>
       <c r="I13">
-        <v>3.8311463178585838E-6</v>
+        <v>-2.2662637667758854E-6</v>
       </c>
       <c r="J13">
-        <v>-1.5679509086251602E-4</v>
+        <v>-2.3929280528861078E-4</v>
       </c>
       <c r="K13">
-        <v>-9.1579121602614532E-5</v>
+        <v>-5.0047647171482207E-5</v>
       </c>
       <c r="L13">
-        <v>2.2856575685607436E-2</v>
+        <v>1.5094584282061767E-2</v>
       </c>
       <c r="M13">
-        <v>2.2882371928567305E-2</v>
+        <v>1.5141844528265383E-2</v>
       </c>
       <c r="N13">
-        <v>2.3161744799829305E-2</v>
+        <v>1.5754200350493512E-2</v>
       </c>
       <c r="O13">
-        <v>2.2995441148033625E-2</v>
+        <v>1.517405437532849E-2</v>
       </c>
       <c r="P13">
-        <v>-7.0262021007175003E-5</v>
+        <v>5.5116149781322022E-6</v>
       </c>
       <c r="Q13">
-        <v>-5.3619272400097809E-5</v>
+        <v>-6.7044699282742541E-6</v>
       </c>
       <c r="R13">
-        <v>-5.5026446452091995E-5</v>
+        <v>1.6773975955524211E-5</v>
       </c>
       <c r="S13">
-        <v>-4.9412785582452829E-5</v>
+        <v>1.8559218631835925E-5</v>
       </c>
       <c r="T13">
-        <v>-1.0811945172308149E-4</v>
-      </c>
-      <c r="U13">
-        <v>5.3045527671642307E-5</v>
-      </c>
-      <c r="V13">
-        <v>-2.3645733642601016E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-1.5789934481233829E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>23</v>
       </c>
       <c r="B14">
-        <v>1.0743219816317251</v>
+        <v>0.85600478888287312</v>
       </c>
       <c r="C14">
-        <v>2.4404058788132137E-5</v>
+        <v>2.0909066397714095E-5</v>
       </c>
       <c r="D14">
-        <v>4.1142373071674878E-5</v>
+        <v>3.9833238287565701E-5</v>
       </c>
       <c r="E14">
-        <v>-3.7607325233588207E-7</v>
+        <v>-2.6137860812812735E-7</v>
       </c>
       <c r="F14">
-        <v>1.1006158296243511E-4</v>
+        <v>1.5240668848018335E-4</v>
       </c>
       <c r="G14">
-        <v>1.106191733463522E-4</v>
+        <v>5.0847549359970797E-4</v>
       </c>
       <c r="H14">
-        <v>-5.2062384240019811E-7</v>
+        <v>-6.4975789373493973E-7</v>
       </c>
       <c r="I14">
-        <v>3.8738021320321777E-6</v>
+        <v>-2.9694043181968205E-6</v>
       </c>
       <c r="J14">
-        <v>-1.413266154437816E-4</v>
+        <v>-2.301748254374476E-4</v>
       </c>
       <c r="K14">
-        <v>-9.2751549404130012E-5</v>
+        <v>-6.4067870757137844E-5</v>
       </c>
       <c r="L14">
-        <v>2.2847225575647161E-2</v>
+        <v>1.508438752988253E-2</v>
       </c>
       <c r="M14">
-        <v>2.2875243795740453E-2</v>
+        <v>1.5101147885119955E-2</v>
       </c>
       <c r="N14">
-        <v>2.2995441148033625E-2</v>
+        <v>1.517405437532849E-2</v>
       </c>
       <c r="O14">
-        <v>2.3674787032247471E-2</v>
+        <v>1.5634818751410925E-2</v>
       </c>
       <c r="P14">
-        <v>-9.7389581051697018E-5</v>
+        <v>-4.4624994489172272E-5</v>
       </c>
       <c r="Q14">
-        <v>-8.5660130887410681E-5</v>
+        <v>-8.2860701312791074E-5</v>
       </c>
       <c r="R14">
-        <v>-4.4259160603565004E-5</v>
+        <v>5.5713724829264521E-6</v>
       </c>
       <c r="S14">
-        <v>-3.1951355554313103E-5</v>
+        <v>-2.7493214078036889E-6</v>
       </c>
       <c r="T14">
-        <v>-9.0140111153013877E-5</v>
-      </c>
-      <c r="U14">
-        <v>-1.5997370824539332E-6</v>
-      </c>
-      <c r="V14">
-        <v>-2.3999813120483337E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-1.6443972897776965E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B15">
-        <v>-0.21272709898745751</v>
+        <v>0.20560545019694437</v>
       </c>
       <c r="C15">
-        <v>-5.633428379076934E-5</v>
+        <v>-3.6218105011012633E-5</v>
       </c>
       <c r="D15">
-        <v>-2.007379904970174E-5</v>
+        <v>1.1522062061736558E-5</v>
       </c>
       <c r="E15">
-        <v>2.3923092225659446E-7</v>
+        <v>-1.4210239934862992E-7</v>
       </c>
       <c r="F15">
-        <v>-1.1692509693025001E-4</v>
+        <v>-9.501688195880773E-5</v>
       </c>
       <c r="G15">
-        <v>-1.5682799681585014E-4</v>
+        <v>-2.2208813120456615E-4</v>
       </c>
       <c r="H15">
-        <v>2.2614496534139019E-6</v>
+        <v>3.4877770036912801E-7</v>
       </c>
       <c r="I15">
-        <v>1.8994797715959573E-6</v>
+        <v>4.3057799521690276E-7</v>
       </c>
       <c r="J15">
-        <v>2.2375872693351891E-5</v>
+        <v>-2.5076848702504313E-6</v>
       </c>
       <c r="K15">
-        <v>-1.0239731905631585E-5</v>
+        <v>-2.6186504703842429E-5</v>
       </c>
       <c r="L15">
-        <v>-5.9772559815235478E-5</v>
+        <v>-3.1012892523894981E-5</v>
       </c>
       <c r="M15">
-        <v>-8.0031989788873007E-5</v>
+        <v>5.8640897497250503E-6</v>
       </c>
       <c r="N15">
-        <v>-7.0262021007175003E-5</v>
+        <v>5.5116149781322022E-6</v>
       </c>
       <c r="O15">
-        <v>-9.7389581051697018E-5</v>
+        <v>-4.4624994489172272E-5</v>
       </c>
       <c r="P15">
-        <v>1.1402939354001654E-3</v>
+        <v>1.657860172678702E-3</v>
       </c>
       <c r="Q15">
-        <v>6.4678810926814057E-4</v>
+        <v>6.136477255074403E-4</v>
       </c>
       <c r="R15">
-        <v>6.084316778790258E-4</v>
+        <v>-6.7713525713102019E-5</v>
       </c>
       <c r="S15">
-        <v>6.1888792144435705E-4</v>
+        <v>4.5014522592680853E-5</v>
       </c>
       <c r="T15">
-        <v>1.299597588448592E-7</v>
-      </c>
-      <c r="U15">
-        <v>-2.799249259923491E-5</v>
-      </c>
-      <c r="V15">
-        <v>-9.1834213578172443E-5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-6.5506869827253059E-4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B16">
-        <v>-0.27662918378841866</v>
+        <v>3.6818941962343976E-2</v>
       </c>
       <c r="C16">
-        <v>-6.7981893989445038E-5</v>
+        <v>-7.7127632971599975E-5</v>
       </c>
       <c r="D16">
-        <v>-2.0168265853773191E-5</v>
+        <v>3.7763215884643533E-6</v>
       </c>
       <c r="E16">
-        <v>2.5717182237881744E-7</v>
+        <v>-5.0455997392773559E-8</v>
       </c>
       <c r="F16">
-        <v>-6.525042069148821E-5</v>
+        <v>-8.7376357364359593E-5</v>
       </c>
       <c r="G16">
-        <v>-1.6614940935216939E-4</v>
+        <v>-1.3022826275288512E-4</v>
       </c>
       <c r="H16">
-        <v>9.3509865662360169E-7</v>
+        <v>-5.1745731171826654E-7</v>
       </c>
       <c r="I16">
-        <v>1.5564253335045741E-6</v>
+        <v>-1.9016170975918895E-6</v>
       </c>
       <c r="J16">
-        <v>1.2283449777824471E-5</v>
+        <v>1.0147818512118499E-5</v>
       </c>
       <c r="K16">
-        <v>-1.6708044031186229E-5</v>
+        <v>-1.794263341084748E-7</v>
       </c>
       <c r="L16">
-        <v>-4.8983450408092186E-5</v>
+        <v>-4.6482086377957284E-5</v>
       </c>
       <c r="M16">
-        <v>-7.1663656884999786E-5</v>
+        <v>-7.3386886848249777E-6</v>
       </c>
       <c r="N16">
-        <v>-5.3619272400097809E-5</v>
+        <v>-6.7044699282742541E-6</v>
       </c>
       <c r="O16">
-        <v>-8.5660130887410681E-5</v>
+        <v>-8.2860701312791074E-5</v>
       </c>
       <c r="P16">
-        <v>6.4678810926814057E-4</v>
+        <v>6.136477255074403E-4</v>
       </c>
       <c r="Q16">
-        <v>1.8442309145110054E-3</v>
+        <v>8.928540681039165E-4</v>
       </c>
       <c r="R16">
-        <v>6.075242879772471E-4</v>
+        <v>-2.9536102488484974E-5</v>
       </c>
       <c r="S16">
-        <v>6.1865534824100121E-4</v>
+        <v>4.28528362613488E-5</v>
       </c>
       <c r="T16">
-        <v>-7.3955902325627544E-6</v>
-      </c>
-      <c r="U16">
-        <v>-2.7930035290223836E-5</v>
-      </c>
-      <c r="V16">
-        <v>-1.1405156490463008E-4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-4.4193676792771223E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B17">
-        <v>4.3866084354798308E-2</v>
+        <v>-3.1978663935709885E-3</v>
       </c>
       <c r="C17">
-        <v>1.8240103666792586E-5</v>
+        <v>3.6716428573918818E-5</v>
       </c>
       <c r="D17">
-        <v>6.6670395586744199E-6</v>
+        <v>4.1953302497180385E-6</v>
       </c>
       <c r="E17">
-        <v>-8.1045343476648411E-8</v>
+        <v>-9.3693630356179366E-8</v>
       </c>
       <c r="F17">
-        <v>4.7106546890782924E-5</v>
+        <v>-9.0170410835784648E-5</v>
       </c>
       <c r="G17">
-        <v>3.2224543308459523E-5</v>
+        <v>-1.2587884694016077E-4</v>
       </c>
       <c r="H17">
-        <v>-9.800781479070649E-7</v>
+        <v>1.7691335950913147E-6</v>
       </c>
       <c r="I17">
-        <v>-6.1179497848918737E-7</v>
+        <v>3.2997823652622863E-6</v>
       </c>
       <c r="J17">
-        <v>2.0744213983872447E-5</v>
+        <v>3.2398557324411248E-5</v>
       </c>
       <c r="K17">
-        <v>-1.1771057760015703E-5</v>
+        <v>-1.482211225860103E-7</v>
       </c>
       <c r="L17">
-        <v>-7.5777641825174188E-5</v>
+        <v>1.1609987814602234E-5</v>
       </c>
       <c r="M17">
-        <v>-5.064840622069557E-5</v>
+        <v>-2.9467657478653099E-5</v>
       </c>
       <c r="N17">
-        <v>-5.5026446452091995E-5</v>
+        <v>1.6773975955524211E-5</v>
       </c>
       <c r="O17">
-        <v>-4.4259160603565004E-5</v>
+        <v>5.5713724829264521E-6</v>
       </c>
       <c r="P17">
-        <v>6.084316778790258E-4</v>
+        <v>-6.7713525713102019E-5</v>
       </c>
       <c r="Q17">
-        <v>6.075242879772471E-4</v>
+        <v>-2.9536102488484974E-5</v>
       </c>
       <c r="R17">
-        <v>1.2602814767659184E-3</v>
+        <v>2.7533759793937525E-3</v>
       </c>
       <c r="S17">
-        <v>6.1414852490284126E-4</v>
+        <v>2.1525477264098487E-4</v>
       </c>
       <c r="T17">
-        <v>-7.169439012291503E-6</v>
-      </c>
-      <c r="U17">
-        <v>-2.105865972295085E-5</v>
-      </c>
-      <c r="V17">
-        <v>-7.0291373168100766E-4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-2.3153901198738218E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B18">
-        <v>-4.4588438657485623E-2</v>
+        <v>1.2640273221396421</v>
       </c>
       <c r="C18">
-        <v>2.8082263203433976E-6</v>
+        <v>-1.16798750228618E-4</v>
       </c>
       <c r="D18">
-        <v>-7.183730504462563E-6</v>
+        <v>1.763653129127575E-5</v>
       </c>
       <c r="E18">
-        <v>6.8983389491732019E-8</v>
+        <v>-2.6428300745777232E-7</v>
       </c>
       <c r="F18">
-        <v>-5.6116741086540336E-5</v>
+        <v>-8.7468115630738298E-5</v>
       </c>
       <c r="G18">
-        <v>-5.6462187147624115E-5</v>
+        <v>-1.043152686738882E-4</v>
       </c>
       <c r="H18">
-        <v>1.2114894671584932E-6</v>
+        <v>2.2621939103586556E-6</v>
       </c>
       <c r="I18">
-        <v>1.3138775231535278E-6</v>
+        <v>3.2499500820182957E-6</v>
       </c>
       <c r="J18">
-        <v>3.3687887360288884E-5</v>
+        <v>1.9261140376020396E-5</v>
       </c>
       <c r="K18">
-        <v>-3.7509506585605932E-6</v>
+        <v>-5.1166959546987749E-5</v>
       </c>
       <c r="L18">
-        <v>-3.9933613418909579E-5</v>
+        <v>1.9098968733139942E-5</v>
       </c>
       <c r="M18">
-        <v>-7.2024739302124769E-5</v>
+        <v>2.4243599676069535E-5</v>
       </c>
       <c r="N18">
-        <v>-4.9412785582452829E-5</v>
+        <v>1.8559218631835925E-5</v>
       </c>
       <c r="O18">
-        <v>-3.1951355554313103E-5</v>
+        <v>-2.7493214078036889E-6</v>
       </c>
       <c r="P18">
-        <v>6.1888792144435705E-4</v>
+        <v>4.5014522592680853E-5</v>
       </c>
       <c r="Q18">
-        <v>6.1865534824100121E-4</v>
+        <v>4.28528362613488E-5</v>
       </c>
       <c r="R18">
-        <v>6.1414852490284126E-4</v>
+        <v>2.1525477264098487E-4</v>
       </c>
       <c r="S18">
-        <v>1.191251130574722E-3</v>
+        <v>1.0419614470127648E-3</v>
       </c>
       <c r="T18">
-        <v>-1.1026622636403508E-5</v>
-      </c>
-      <c r="U18">
-        <v>-2.6301103652678347E-5</v>
-      </c>
-      <c r="V18">
-        <v>-4.1005178251279922E-4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+        <v>-3.8562506313903399E-4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B19">
-        <v>0.10084414520475385</v>
+        <v>-4.952951424546205</v>
       </c>
       <c r="C19">
-        <v>4.8433491299694167E-5</v>
+        <v>1.2561212095509088E-3</v>
       </c>
       <c r="D19">
-        <v>2.8424227399921806E-6</v>
+        <v>-1.4667889021322644E-3</v>
       </c>
       <c r="E19">
-        <v>-6.3144177830298084E-8</v>
+        <v>1.455269325693747E-5</v>
       </c>
       <c r="F19">
-        <v>1.1726714774824312E-5</v>
+        <v>-1.1908552948735926E-2</v>
       </c>
       <c r="G19">
-        <v>-8.9688314900029012E-6</v>
+        <v>-9.4408583191362885E-3</v>
       </c>
       <c r="H19">
-        <v>2.3998349377131326E-7</v>
+        <v>2.5815627808192549E-4</v>
       </c>
       <c r="I19">
-        <v>9.0943341480079639E-7</v>
+        <v>1.965224241221195E-4</v>
       </c>
       <c r="J19">
-        <v>6.8004106459347097E-5</v>
+        <v>9.2616363813803935E-5</v>
       </c>
       <c r="K19">
-        <v>-1.3297267849727595E-5</v>
+        <v>2.1446093728786321E-3</v>
       </c>
       <c r="L19">
-        <v>-1.0445932773522623E-4</v>
+        <v>-1.5268884155399374E-2</v>
       </c>
       <c r="M19">
-        <v>-1.7758867580389809E-4</v>
+        <v>-1.5733268934418437E-2</v>
       </c>
       <c r="N19">
-        <v>-1.0811945172308149E-4</v>
+        <v>-1.5789934481233829E-2</v>
       </c>
       <c r="O19">
-        <v>-9.0140111153013877E-5</v>
+        <v>-1.6443972897776965E-2</v>
       </c>
       <c r="P19">
-        <v>1.299597588448592E-7</v>
+        <v>-6.5506869827253059E-4</v>
       </c>
       <c r="Q19">
-        <v>-7.3955902325627544E-6</v>
+        <v>-4.4193676792771223E-4</v>
       </c>
       <c r="R19">
-        <v>-7.169439012291503E-6</v>
+        <v>-2.3153901198738218E-4</v>
       </c>
       <c r="S19">
-        <v>-1.1026622636403508E-5</v>
+        <v>-3.8562506313903399E-4</v>
       </c>
       <c r="T19">
-        <v>2.056049251236626E-3</v>
-      </c>
-      <c r="U19">
-        <v>1.6966438376568081E-4</v>
-      </c>
-      <c r="V19">
-        <v>-1.3732499076637424E-4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20">
-        <v>0.73252391445086251</v>
-      </c>
-      <c r="C20">
-        <v>-8.7821648003127406E-5</v>
-      </c>
-      <c r="D20">
-        <v>5.5876513712006746E-6</v>
-      </c>
-      <c r="E20">
-        <v>-8.7324628151455999E-8</v>
-      </c>
-      <c r="F20">
-        <v>7.0282592051261968E-5</v>
-      </c>
-      <c r="G20">
-        <v>6.7002040305126593E-5</v>
-      </c>
-      <c r="H20">
-        <v>-1.4058295414173764E-6</v>
-      </c>
-      <c r="I20">
-        <v>-3.5319060234169612E-7</v>
-      </c>
-      <c r="J20">
-        <v>3.3400116638942346E-5</v>
-      </c>
-      <c r="K20">
-        <v>-4.407866611521999E-5</v>
-      </c>
-      <c r="L20">
-        <v>7.8286199803674503E-5</v>
-      </c>
-      <c r="M20">
-        <v>6.4477605278316738E-5</v>
-      </c>
-      <c r="N20">
-        <v>5.3045527671642307E-5</v>
-      </c>
-      <c r="O20">
-        <v>-1.5997370824539332E-6</v>
-      </c>
-      <c r="P20">
-        <v>-2.799249259923491E-5</v>
-      </c>
-      <c r="Q20">
-        <v>-2.7930035290223836E-5</v>
-      </c>
-      <c r="R20">
-        <v>-2.105865972295085E-5</v>
-      </c>
-      <c r="S20">
-        <v>-2.6301103652678347E-5</v>
-      </c>
-      <c r="T20">
-        <v>1.6966438376568081E-4</v>
-      </c>
-      <c r="U20">
-        <v>9.0334092537658133E-4</v>
-      </c>
-      <c r="V20">
-        <v>-2.2586603147181343E-4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21">
-        <v>-5.4485265779624417</v>
-      </c>
-      <c r="C21">
-        <v>2.1135761796003765E-3</v>
-      </c>
-      <c r="D21">
-        <v>-1.2135338648586232E-3</v>
-      </c>
-      <c r="E21">
-        <v>1.1492040000878157E-5</v>
-      </c>
-      <c r="F21">
-        <v>-1.1369411803076617E-2</v>
-      </c>
-      <c r="G21">
-        <v>-1.1473974449422114E-2</v>
-      </c>
-      <c r="H21">
-        <v>2.4707410183791111E-4</v>
-      </c>
-      <c r="I21">
-        <v>2.4214364679901816E-4</v>
-      </c>
-      <c r="J21">
-        <v>-2.9233462774163265E-4</v>
-      </c>
-      <c r="K21">
-        <v>2.0015908231555864E-3</v>
-      </c>
-      <c r="L21">
-        <v>-2.2975361075814695E-2</v>
-      </c>
-      <c r="M21">
-        <v>-2.3331216461684356E-2</v>
-      </c>
-      <c r="N21">
-        <v>-2.3645733642601016E-2</v>
-      </c>
-      <c r="O21">
-        <v>-2.3999813120483337E-2</v>
-      </c>
-      <c r="P21">
-        <v>-9.1834213578172443E-5</v>
-      </c>
-      <c r="Q21">
-        <v>-1.1405156490463008E-4</v>
-      </c>
-      <c r="R21">
-        <v>-7.0291373168100766E-4</v>
-      </c>
-      <c r="S21">
-        <v>-4.1005178251279922E-4</v>
-      </c>
-      <c r="T21">
-        <v>-1.3732499076637424E-4</v>
-      </c>
-      <c r="U21">
-        <v>-2.2586603147181343E-4</v>
-      </c>
-      <c r="V21">
-        <v>5.1097866323981431E-2</v>
+        <v>4.9029408820232254E-2</v>
       </c>
     </row>
   </sheetData>
@@ -3494,14 +2980,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3272626D-9706-4C43-8EC8-444422CC481A}">
-  <dimension ref="A1:U20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="16384" width="9" style="2"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BAB1F52-EB31-4054-98FC-32266C56B413}">
+  <dimension ref="A1:S18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -3545,1260 +3028,1022 @@
         <v>23</v>
       </c>
       <c r="O1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="P1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="Q1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="R1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="S1" t="s">
-        <v>24</v>
-      </c>
-      <c r="T1" t="s">
-        <v>25</v>
-      </c>
-      <c r="U1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2">
-        <v>0.18704810243833836</v>
+        <v>0.11869656234446822</v>
       </c>
       <c r="C2">
-        <v>6.1052862066270403E-5</v>
+        <v>1.1620427082808231E-4</v>
       </c>
       <c r="D2">
-        <v>-6.5632038282068916E-7</v>
+        <v>-1.3126794007819647E-6</v>
       </c>
       <c r="E2">
-        <v>2.2268469089414385E-4</v>
+        <v>2.5450607297863783E-4</v>
       </c>
       <c r="F2">
-        <v>1.0608194969778062E-4</v>
+        <v>-3.4308383314807754E-4</v>
       </c>
       <c r="G2">
-        <v>-4.9615095006584995E-6</v>
+        <v>-5.804595387655915E-6</v>
       </c>
       <c r="H2">
-        <v>-2.6184854426170965E-6</v>
+        <v>7.1907657487394662E-6</v>
       </c>
       <c r="I2">
-        <v>-1.1276445592708288E-5</v>
+        <v>-4.6265345014350123E-5</v>
       </c>
       <c r="J2">
-        <v>-6.7611293313808301E-5</v>
+        <v>-1.0805575823476899E-4</v>
       </c>
       <c r="K2">
-        <v>-4.3489554415706341E-6</v>
+        <v>-1.4840915354415E-6</v>
       </c>
       <c r="L2">
-        <v>-3.2949263282937334E-6</v>
+        <v>-9.5012869927310964E-6</v>
       </c>
       <c r="M2">
-        <v>-2.4440475045379474E-6</v>
+        <v>-1.8927567596249478E-5</v>
       </c>
       <c r="N2">
-        <v>7.9860537331287061E-6</v>
+        <v>-4.8318640070046763E-6</v>
       </c>
       <c r="O2">
-        <v>-5.874448606977783E-7</v>
+        <v>5.6812036114395512E-6</v>
       </c>
       <c r="P2">
-        <v>-2.370461326808416E-6</v>
+        <v>-2.699668852087052E-6</v>
       </c>
       <c r="Q2">
-        <v>2.0382471319313892E-6</v>
+        <v>1.22333733561202E-5</v>
       </c>
       <c r="R2">
-        <v>-4.9332346457790745E-6</v>
+        <v>4.8628104985100426E-6</v>
       </c>
       <c r="S2">
-        <v>4.3755737006589052E-6</v>
-      </c>
-      <c r="T2">
-        <v>6.9137596541856418E-6</v>
-      </c>
-      <c r="U2">
-        <v>-1.3017969006119149E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-2.3479700269470266E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
       <c r="B3">
-        <v>-1.8463980613548005E-3</v>
+        <v>-1.1462164126724054E-3</v>
       </c>
       <c r="C3">
-        <v>-6.5632038282068916E-7</v>
+        <v>-1.3126794007819647E-6</v>
       </c>
       <c r="D3">
-        <v>7.461125060620798E-9</v>
+        <v>1.5460115206606497E-8</v>
       </c>
       <c r="E3">
-        <v>-1.0005827080800816E-6</v>
+        <v>-9.1225409964579695E-7</v>
       </c>
       <c r="F3">
-        <v>3.3003838711537037E-7</v>
+        <v>6.1989788288571221E-6</v>
       </c>
       <c r="G3">
-        <v>2.0247688628077505E-8</v>
+        <v>1.792015393581326E-8</v>
       </c>
       <c r="H3">
-        <v>-6.3742820550141466E-9</v>
+        <v>-1.3608235117606357E-7</v>
       </c>
       <c r="I3">
-        <v>6.518102411908517E-8</v>
+        <v>3.4680678823217476E-7</v>
       </c>
       <c r="J3">
-        <v>8.0610293162485879E-7</v>
+        <v>1.3263516728745867E-6</v>
       </c>
       <c r="K3">
-        <v>7.0863787817114539E-8</v>
+        <v>-3.6731407154791149E-8</v>
       </c>
       <c r="L3">
-        <v>7.563956693970462E-8</v>
+        <v>6.3397210587937364E-8</v>
       </c>
       <c r="M3">
-        <v>1.0520389661900068E-7</v>
+        <v>1.9944447383915895E-7</v>
       </c>
       <c r="N3">
-        <v>3.7190029654120747E-8</v>
+        <v>1.5724909203482719E-7</v>
       </c>
       <c r="O3">
-        <v>-1.1851926018520669E-8</v>
+        <v>-5.9161369366297318E-8</v>
       </c>
       <c r="P3">
-        <v>-3.490458104336136E-9</v>
+        <v>2.5075372925537924E-8</v>
       </c>
       <c r="Q3">
-        <v>-1.8521597140781871E-8</v>
+        <v>-1.7304713036216376E-7</v>
       </c>
       <c r="R3">
-        <v>4.187286558905565E-8</v>
+        <v>-9.6691571055058368E-8</v>
       </c>
       <c r="S3">
-        <v>-6.6930739141457928E-8</v>
-      </c>
-      <c r="T3">
-        <v>-9.7778576614864938E-8</v>
-      </c>
-      <c r="U3">
-        <v>1.3152903791723208E-5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+        <v>2.5398498694099362E-5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
       <c r="B4">
-        <v>0.54572477344768788</v>
+        <v>0.3449598053845957</v>
       </c>
       <c r="C4">
-        <v>2.2268469089414385E-4</v>
+        <v>2.5450607297863783E-4</v>
       </c>
       <c r="D4">
-        <v>-1.0005827080800816E-6</v>
+        <v>-9.1225409964579695E-7</v>
       </c>
       <c r="E4">
-        <v>9.0274061109462747E-3</v>
+        <v>1.4571911135483085E-2</v>
       </c>
       <c r="F4">
-        <v>6.0855993079771218E-3</v>
+        <v>7.8578741933905804E-3</v>
       </c>
       <c r="G4">
-        <v>-1.976036913796061E-4</v>
+        <v>-3.2634004472357608E-4</v>
       </c>
       <c r="H4">
-        <v>-1.352004527836047E-4</v>
+        <v>-1.7987052497312711E-4</v>
       </c>
       <c r="I4">
-        <v>3.6784479051945294E-5</v>
+        <v>3.071999336612055E-5</v>
       </c>
       <c r="J4">
-        <v>-1.8793810187761256E-4</v>
+        <v>-4.3439230282710863E-4</v>
       </c>
       <c r="K4">
-        <v>1.1650809497714288E-5</v>
+        <v>-8.8997054119160923E-5</v>
       </c>
       <c r="L4">
-        <v>7.5802227897661927E-5</v>
+        <v>-2.1329876666223695E-4</v>
       </c>
       <c r="M4">
-        <v>7.4192995785255737E-5</v>
+        <v>-2.1131146306846687E-4</v>
       </c>
       <c r="N4">
-        <v>9.9845997510367591E-5</v>
+        <v>-2.2880665660915227E-4</v>
       </c>
       <c r="O4">
-        <v>-5.2351564043678057E-5</v>
+        <v>-1.7782835128710701E-4</v>
       </c>
       <c r="P4">
-        <v>-9.0891382868328873E-5</v>
+        <v>-7.8506181339398166E-5</v>
       </c>
       <c r="Q4">
-        <v>-5.0644929818794847E-6</v>
+        <v>6.4296524373620435E-5</v>
       </c>
       <c r="R4">
-        <v>-4.6231243748156477E-5</v>
+        <v>3.6843946171005158E-5</v>
       </c>
       <c r="S4">
-        <v>4.3978317524855901E-6</v>
-      </c>
-      <c r="T4">
-        <v>4.5058040437772991E-5</v>
-      </c>
-      <c r="U4">
-        <v>-7.8901706852183284E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-8.8396657131173031E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
       <c r="B5">
-        <v>0.40529754617253599</v>
+        <v>-0.16531847387747417</v>
       </c>
       <c r="C5">
-        <v>1.0608194969778062E-4</v>
+        <v>-3.4308383314807754E-4</v>
       </c>
       <c r="D5">
-        <v>3.3003838711537037E-7</v>
+        <v>6.1989788288571221E-6</v>
       </c>
       <c r="E5">
-        <v>6.0855993079771218E-3</v>
+        <v>7.8578741933905804E-3</v>
       </c>
       <c r="F5">
-        <v>1.4703775094133514E-2</v>
+        <v>3.2584443278686814E-2</v>
       </c>
       <c r="G5">
-        <v>-1.3545461544757446E-4</v>
+        <v>-1.818722416854085E-4</v>
       </c>
       <c r="H5">
-        <v>-3.0532050463348895E-4</v>
+        <v>-6.5875172396243976E-4</v>
       </c>
       <c r="I5">
-        <v>-4.6212164830295501E-6</v>
+        <v>-9.8212053675956381E-5</v>
       </c>
       <c r="J5">
-        <v>-2.7779514504327628E-4</v>
+        <v>-4.517212510851423E-4</v>
       </c>
       <c r="K5">
-        <v>1.2570185525183786E-4</v>
+        <v>2.5134404687109416E-4</v>
       </c>
       <c r="L5">
-        <v>1.2083645552443635E-4</v>
+        <v>3.0703503934583084E-4</v>
       </c>
       <c r="M5">
-        <v>1.0417902503753957E-4</v>
+        <v>1.1256784948309806E-4</v>
       </c>
       <c r="N5">
-        <v>1.8273299107816974E-4</v>
+        <v>7.9504679310139379E-5</v>
       </c>
       <c r="O5">
-        <v>-1.1463832608371572E-4</v>
+        <v>-2.3282468638893402E-4</v>
       </c>
       <c r="P5">
-        <v>-9.0984874086246927E-5</v>
+        <v>-6.6924387722497444E-5</v>
       </c>
       <c r="Q5">
-        <v>7.0164371315039047E-5</v>
+        <v>-4.7143615569185054E-5</v>
       </c>
       <c r="R5">
-        <v>1.4262870722837697E-5</v>
+        <v>2.5890221626737027E-5</v>
       </c>
       <c r="S5">
-        <v>-4.0191151188356101E-6</v>
-      </c>
-      <c r="T5">
-        <v>6.6073262206144793E-5</v>
-      </c>
-      <c r="U5">
-        <v>-5.5102373468521471E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+        <v>2.7603492709643461E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>27</v>
       </c>
       <c r="B6">
-        <v>-1.4340289125808358E-2</v>
+        <v>-1.2987922040696261E-2</v>
       </c>
       <c r="C6">
-        <v>-4.9615095006584995E-6</v>
+        <v>-5.804595387655915E-6</v>
       </c>
       <c r="D6">
-        <v>2.0247688628077505E-8</v>
+        <v>1.792015393581326E-8</v>
       </c>
       <c r="E6">
-        <v>-1.976036913796061E-4</v>
+        <v>-3.2634004472357608E-4</v>
       </c>
       <c r="F6">
-        <v>-1.3545461544757446E-4</v>
+        <v>-1.818722416854085E-4</v>
       </c>
       <c r="G6">
-        <v>4.6131815808684398E-6</v>
+        <v>7.7550407949996071E-6</v>
       </c>
       <c r="H6">
-        <v>3.204947422512426E-6</v>
+        <v>4.4266298611848962E-6</v>
       </c>
       <c r="I6">
-        <v>-1.0068579564593023E-6</v>
+        <v>-1.5074457438528372E-6</v>
       </c>
       <c r="J6">
-        <v>4.4050807546610091E-6</v>
+        <v>1.0541432324276365E-5</v>
       </c>
       <c r="K6">
-        <v>-9.7416349748998226E-8</v>
+        <v>1.0565168860113126E-6</v>
       </c>
       <c r="L6">
-        <v>-1.8431107225618995E-6</v>
+        <v>4.0913472474896046E-6</v>
       </c>
       <c r="M6">
-        <v>-1.3835708868088379E-6</v>
+        <v>4.5916618245089982E-6</v>
       </c>
       <c r="N6">
-        <v>-1.8703143743635444E-6</v>
+        <v>6.1317117557873913E-6</v>
       </c>
       <c r="O6">
-        <v>1.3961929086500478E-6</v>
+        <v>1.2155124910887065E-6</v>
       </c>
       <c r="P6">
-        <v>2.2773960754347802E-6</v>
+        <v>-1.8449811680657107E-8</v>
       </c>
       <c r="Q6">
-        <v>6.0303289434779521E-8</v>
+        <v>-1.2925881391400886E-6</v>
       </c>
       <c r="R6">
-        <v>1.22509434853718E-6</v>
+        <v>-8.8126272669295515E-7</v>
       </c>
       <c r="S6">
-        <v>4.4388299106721707E-7</v>
-      </c>
-      <c r="T6">
-        <v>-3.8038831695508604E-7</v>
-      </c>
-      <c r="U6">
-        <v>1.7102762788115533E-4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+        <v>1.9770158120992862E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>28</v>
       </c>
       <c r="B7">
-        <v>-1.6503187541224491E-2</v>
+        <v>-4.6028206060549194E-3</v>
       </c>
       <c r="C7">
-        <v>-2.6184854426170965E-6</v>
+        <v>7.1907657487394662E-6</v>
       </c>
       <c r="D7">
-        <v>-6.3742820550141466E-9</v>
+        <v>-1.3608235117606357E-7</v>
       </c>
       <c r="E7">
-        <v>-1.352004527836047E-4</v>
+        <v>-1.7987052497312711E-4</v>
       </c>
       <c r="F7">
-        <v>-3.0532050463348895E-4</v>
+        <v>-6.5875172396243976E-4</v>
       </c>
       <c r="G7">
-        <v>3.204947422512426E-6</v>
+        <v>4.4266298611848962E-6</v>
       </c>
       <c r="H7">
-        <v>6.7006999890117661E-6</v>
+        <v>1.3955413880951029E-5</v>
       </c>
       <c r="I7">
-        <v>-2.8983173585913381E-7</v>
+        <v>-9.8483048501756431E-7</v>
       </c>
       <c r="J7">
-        <v>6.5417365064356964E-6</v>
+        <v>1.1533008026165349E-5</v>
       </c>
       <c r="K7">
-        <v>-3.0982868779941619E-6</v>
+        <v>-6.8000745666927685E-6</v>
       </c>
       <c r="L7">
-        <v>-3.1198503952774593E-6</v>
+        <v>-7.8180079593074807E-6</v>
       </c>
       <c r="M7">
-        <v>-1.5413518461871183E-6</v>
+        <v>-1.8341685077622377E-6</v>
       </c>
       <c r="N7">
-        <v>-2.8538061070024936E-6</v>
+        <v>1.007920760121169E-6</v>
       </c>
       <c r="O7">
-        <v>2.2387385834125823E-6</v>
+        <v>-7.0592275891626165E-7</v>
       </c>
       <c r="P7">
-        <v>1.8721208974156822E-6</v>
+        <v>-3.3822248589595686E-6</v>
       </c>
       <c r="Q7">
-        <v>-1.3078571296251137E-6</v>
+        <v>2.021067213511433E-6</v>
       </c>
       <c r="R7">
-        <v>2.4122802097814307E-7</v>
+        <v>6.9933467941895502E-7</v>
       </c>
       <c r="S7">
-        <v>8.4269785749024716E-7</v>
-      </c>
-      <c r="T7">
-        <v>-6.4970161824140888E-7</v>
-      </c>
-      <c r="U7">
-        <v>1.2250917552511335E-4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-5.3924309508154289E-5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>18</v>
       </c>
       <c r="B8">
-        <v>4.1050761102292985E-2</v>
+        <v>2.2148711812847756E-2</v>
       </c>
       <c r="C8">
-        <v>-1.1276445592708288E-5</v>
+        <v>-4.6265345014350123E-5</v>
       </c>
       <c r="D8">
-        <v>6.518102411908517E-8</v>
+        <v>3.4680678823217476E-7</v>
       </c>
       <c r="E8">
-        <v>3.6784479051945294E-5</v>
+        <v>3.071999336612055E-5</v>
       </c>
       <c r="F8">
-        <v>-4.6212164830295501E-6</v>
+        <v>-9.8212053675956381E-5</v>
       </c>
       <c r="G8">
-        <v>-1.0068579564593023E-6</v>
+        <v>-1.5074457438528372E-6</v>
       </c>
       <c r="H8">
-        <v>-2.8983173585913381E-7</v>
+        <v>-9.8483048501756431E-7</v>
       </c>
       <c r="I8">
-        <v>4.767054364941626E-4</v>
+        <v>1.0297308455758326E-3</v>
       </c>
       <c r="J8">
-        <v>-2.0935934760817865E-4</v>
+        <v>-4.0645255253437087E-4</v>
       </c>
       <c r="K8">
-        <v>-7.7958098605357455E-6</v>
+        <v>6.0885379939157607E-5</v>
       </c>
       <c r="L8">
-        <v>-1.4455121989014942E-6</v>
+        <v>1.8546882322080288E-5</v>
       </c>
       <c r="M8">
-        <v>-1.1437545977928997E-5</v>
+        <v>-3.7780182929292327E-5</v>
       </c>
       <c r="N8">
-        <v>-1.4470597517028154E-5</v>
+        <v>-4.8129541424513837E-5</v>
       </c>
       <c r="O8">
-        <v>1.5336480504151906E-5</v>
+        <v>-2.999756267550689E-5</v>
       </c>
       <c r="P8">
-        <v>2.3337179548262194E-5</v>
+        <v>-5.2034205506917063E-5</v>
       </c>
       <c r="Q8">
-        <v>-1.0391956452389156E-5</v>
+        <v>3.1035534500310972E-5</v>
       </c>
       <c r="R8">
-        <v>1.648012596819359E-5</v>
+        <v>3.1463067265948054E-5</v>
       </c>
       <c r="S8">
-        <v>2.6693699782483039E-5</v>
-      </c>
-      <c r="T8">
-        <v>3.4216077500947404E-5</v>
-      </c>
-      <c r="U8">
-        <v>1.7718965949682538E-4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+        <v>8.8249276892101325E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>19</v>
       </c>
       <c r="B9">
-        <v>4.8827546471102407E-2</v>
+        <v>0.11952709845136218</v>
       </c>
       <c r="C9">
-        <v>-6.7611293313808301E-5</v>
+        <v>-1.0805575823476899E-4</v>
       </c>
       <c r="D9">
-        <v>8.0610293162485879E-7</v>
+        <v>1.3263516728745867E-6</v>
       </c>
       <c r="E9">
-        <v>-1.8793810187761256E-4</v>
+        <v>-4.3439230282710863E-4</v>
       </c>
       <c r="F9">
-        <v>-2.7779514504327628E-4</v>
+        <v>-4.517212510851423E-4</v>
       </c>
       <c r="G9">
-        <v>4.4050807546610091E-6</v>
+        <v>1.0541432324276365E-5</v>
       </c>
       <c r="H9">
-        <v>6.5417365064356964E-6</v>
+        <v>1.1533008026165349E-5</v>
       </c>
       <c r="I9">
-        <v>-2.0935934760817865E-4</v>
+        <v>-4.0645255253437087E-4</v>
       </c>
       <c r="J9">
-        <v>6.3823254089480906E-4</v>
+        <v>1.0760803779813156E-3</v>
       </c>
       <c r="K9">
-        <v>4.7405809535532072E-6</v>
+        <v>-1.4163150596040283E-5</v>
       </c>
       <c r="L9">
-        <v>-8.9803928327508243E-6</v>
+        <v>3.3040567912099531E-6</v>
       </c>
       <c r="M9">
-        <v>-2.1729575443915562E-5</v>
+        <v>1.2734662988107695E-5</v>
       </c>
       <c r="N9">
-        <v>-1.3829215534331193E-5</v>
+        <v>-2.3094323794856575E-6</v>
       </c>
       <c r="O9">
-        <v>-1.2862512497610979E-5</v>
+        <v>-3.5368201280159157E-5</v>
       </c>
       <c r="P9">
-        <v>-4.8741064750984798E-6</v>
+        <v>6.9176886847707262E-6</v>
       </c>
       <c r="Q9">
-        <v>-7.912065323884419E-6</v>
+        <v>-1.7616007650227323E-5</v>
       </c>
       <c r="R9">
-        <v>-3.548769262808528E-6</v>
+        <v>-4.2971397131888693E-5</v>
       </c>
       <c r="S9">
-        <v>-1.1251610601675641E-5</v>
-      </c>
-      <c r="T9">
-        <v>-6.271428616984261E-6</v>
-      </c>
-      <c r="U9">
-        <v>1.2363120055002817E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+        <v>1.9040669504226334E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>20</v>
       </c>
       <c r="B10">
-        <v>-6.1466108270543794E-2</v>
+        <v>-0.25884888321356159</v>
       </c>
       <c r="C10">
-        <v>-4.3489554415706341E-6</v>
+        <v>-1.4840915354415E-6</v>
       </c>
       <c r="D10">
-        <v>7.0863787817114539E-8</v>
+        <v>-3.6731407154791149E-8</v>
       </c>
       <c r="E10">
-        <v>1.1650809497714288E-5</v>
+        <v>-8.8997054119160923E-5</v>
       </c>
       <c r="F10">
-        <v>1.2570185525183786E-4</v>
+        <v>2.5134404687109416E-4</v>
       </c>
       <c r="G10">
-        <v>-9.7416349748998226E-8</v>
+        <v>1.0565168860113126E-6</v>
       </c>
       <c r="H10">
-        <v>-3.0982868779941619E-6</v>
+        <v>-6.8000745666927685E-6</v>
       </c>
       <c r="I10">
-        <v>-7.7958098605357455E-6</v>
+        <v>6.0885379939157607E-5</v>
       </c>
       <c r="J10">
-        <v>4.7405809535532072E-6</v>
+        <v>-1.4163150596040283E-5</v>
       </c>
       <c r="K10">
-        <v>2.4629399825644549E-2</v>
+        <v>5.6202161584564488E-2</v>
       </c>
       <c r="L10">
-        <v>2.1708149493978139E-2</v>
+        <v>4.8152514593481771E-2</v>
       </c>
       <c r="M10">
-        <v>2.1726922600520639E-2</v>
+        <v>4.8124248339565433E-2</v>
       </c>
       <c r="N10">
-        <v>2.1730834092034721E-2</v>
+        <v>4.8074008584290041E-2</v>
       </c>
       <c r="O10">
-        <v>1.4525557545968934E-5</v>
+        <v>-1.0955505973165159E-5</v>
       </c>
       <c r="P10">
-        <v>-3.41680497074353E-5</v>
+        <v>-7.870812555215486E-6</v>
       </c>
       <c r="Q10">
-        <v>-5.8067745537993427E-5</v>
+        <v>-8.1087431168268764E-5</v>
       </c>
       <c r="R10">
-        <v>-1.1783791123626454E-5</v>
+        <v>4.2151862295487018E-5</v>
       </c>
       <c r="S10">
-        <v>1.3989323821699163E-4</v>
-      </c>
-      <c r="T10">
-        <v>9.0078635385618686E-6</v>
-      </c>
-      <c r="U10">
-        <v>-2.1672893123388236E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-4.7936621386774542E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>21</v>
       </c>
       <c r="B11">
-        <v>8.2382815163422524E-2</v>
+        <v>6.5452613155134565E-2</v>
       </c>
       <c r="C11">
-        <v>-3.2949263282937334E-6</v>
+        <v>-9.5012869927310964E-6</v>
       </c>
       <c r="D11">
-        <v>7.563956693970462E-8</v>
+        <v>6.3397210587937364E-8</v>
       </c>
       <c r="E11">
-        <v>7.5802227897661927E-5</v>
+        <v>-2.1329876666223695E-4</v>
       </c>
       <c r="F11">
-        <v>1.2083645552443635E-4</v>
+        <v>3.0703503934583084E-4</v>
       </c>
       <c r="G11">
-        <v>-1.8431107225618995E-6</v>
+        <v>4.0913472474896046E-6</v>
       </c>
       <c r="H11">
-        <v>-3.1198503952774593E-6</v>
+        <v>-7.8180079593074807E-6</v>
       </c>
       <c r="I11">
-        <v>-1.4455121989014942E-6</v>
+        <v>1.8546882322080288E-5</v>
       </c>
       <c r="J11">
-        <v>-8.9803928327508243E-6</v>
+        <v>3.3040567912099531E-6</v>
       </c>
       <c r="K11">
-        <v>2.1708149493978139E-2</v>
+        <v>4.8152514593481771E-2</v>
       </c>
       <c r="L11">
-        <v>2.2309799062118711E-2</v>
+        <v>5.0391950306547494E-2</v>
       </c>
       <c r="M11">
-        <v>2.1745701327985846E-2</v>
+        <v>4.8126540922717634E-2</v>
       </c>
       <c r="N11">
-        <v>2.1754215307686946E-2</v>
+        <v>4.8084443640550451E-2</v>
       </c>
       <c r="O11">
-        <v>3.0325990744582611E-7</v>
+        <v>-2.3532895435269651E-5</v>
       </c>
       <c r="P11">
-        <v>-4.6504578633720637E-5</v>
+        <v>-1.7726117435842517E-5</v>
       </c>
       <c r="Q11">
-        <v>-5.6444198605575782E-5</v>
+        <v>-2.7282249208467638E-5</v>
       </c>
       <c r="R11">
-        <v>-1.5850351416079334E-5</v>
+        <v>4.4988047976931574E-5</v>
       </c>
       <c r="S11">
-        <v>1.8168174935302435E-4</v>
-      </c>
-      <c r="T11">
-        <v>5.3143497878306687E-6</v>
-      </c>
-      <c r="U11">
-        <v>-2.1740359090585807E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-4.7774960092169277E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>22</v>
       </c>
       <c r="B12">
-        <v>0.1492769741408011</v>
+        <v>5.760208959316563E-2</v>
       </c>
       <c r="C12">
-        <v>-2.4440475045379474E-6</v>
+        <v>-1.8927567596249478E-5</v>
       </c>
       <c r="D12">
-        <v>1.0520389661900068E-7</v>
+        <v>1.9944447383915895E-7</v>
       </c>
       <c r="E12">
-        <v>7.4192995785255737E-5</v>
+        <v>-2.1131146306846687E-4</v>
       </c>
       <c r="F12">
-        <v>1.0417902503753957E-4</v>
+        <v>1.1256784948309806E-4</v>
       </c>
       <c r="G12">
-        <v>-1.3835708868088379E-6</v>
+        <v>4.5916618245089982E-6</v>
       </c>
       <c r="H12">
-        <v>-1.5413518461871183E-6</v>
+        <v>-1.8341685077622377E-6</v>
       </c>
       <c r="I12">
-        <v>-1.1437545977928997E-5</v>
+        <v>-3.7780182929292327E-5</v>
       </c>
       <c r="J12">
-        <v>-2.1729575443915562E-5</v>
+        <v>1.2734662988107695E-5</v>
       </c>
       <c r="K12">
-        <v>2.1726922600520639E-2</v>
+        <v>4.8124248339565433E-2</v>
       </c>
       <c r="L12">
-        <v>2.1745701327985846E-2</v>
+        <v>4.8126540922717634E-2</v>
       </c>
       <c r="M12">
-        <v>2.195222823189754E-2</v>
+        <v>4.8631774101224691E-2</v>
       </c>
       <c r="N12">
-        <v>2.1847611231853914E-2</v>
+        <v>4.8131786176120114E-2</v>
       </c>
       <c r="O12">
-        <v>1.7988468324208737E-5</v>
+        <v>3.0053714946322459E-6</v>
       </c>
       <c r="P12">
-        <v>-4.4231402602473675E-5</v>
+        <v>-2.9092913732728815E-5</v>
       </c>
       <c r="Q12">
-        <v>-6.6267298817066259E-5</v>
+        <v>-9.4174411703365474E-5</v>
       </c>
       <c r="R12">
-        <v>-1.6121575520074879E-5</v>
+        <v>2.5690835976581856E-5</v>
       </c>
       <c r="S12">
-        <v>2.6960987265023162E-4</v>
-      </c>
-      <c r="T12">
-        <v>-1.538970380285192E-5</v>
-      </c>
-      <c r="U12">
-        <v>-2.1931130404519227E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-4.7660895305713297E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13">
-        <v>0.14576996546110621</v>
+        <v>6.6665632796734181E-2</v>
       </c>
       <c r="C13">
-        <v>7.9860537331287061E-6</v>
+        <v>-4.8318640070046763E-6</v>
       </c>
       <c r="D13">
-        <v>3.7190029654120747E-8</v>
+        <v>1.5724909203482719E-7</v>
       </c>
       <c r="E13">
-        <v>9.9845997510367591E-5</v>
+        <v>-2.2880665660915227E-4</v>
       </c>
       <c r="F13">
-        <v>1.8273299107816974E-4</v>
+        <v>7.9504679310139379E-5</v>
       </c>
       <c r="G13">
-        <v>-1.8703143743635444E-6</v>
+        <v>6.1317117557873913E-6</v>
       </c>
       <c r="H13">
-        <v>-2.8538061070024936E-6</v>
+        <v>1.007920760121169E-6</v>
       </c>
       <c r="I13">
-        <v>-1.4470597517028154E-5</v>
+        <v>-4.8129541424513837E-5</v>
       </c>
       <c r="J13">
-        <v>-1.3829215534331193E-5</v>
+        <v>-2.3094323794856575E-6</v>
       </c>
       <c r="K13">
-        <v>2.1730834092034721E-2</v>
+        <v>4.8074008584290041E-2</v>
       </c>
       <c r="L13">
-        <v>2.1754215307686946E-2</v>
+        <v>4.8084443640550451E-2</v>
       </c>
       <c r="M13">
-        <v>2.1847611231853914E-2</v>
+        <v>4.8131786176120114E-2</v>
       </c>
       <c r="N13">
-        <v>2.2523974521751117E-2</v>
+        <v>4.8497572237529263E-2</v>
       </c>
       <c r="O13">
-        <v>1.6446091126552767E-5</v>
+        <v>-4.3418095232025265E-5</v>
       </c>
       <c r="P13">
-        <v>-3.6205489759027492E-5</v>
+        <v>-1.0578519579900006E-4</v>
       </c>
       <c r="Q13">
-        <v>-3.6186888870671466E-5</v>
+        <v>-1.1013520374359047E-4</v>
       </c>
       <c r="R13">
-        <v>4.5663664514786553E-7</v>
+        <v>-5.7983268090683337E-6</v>
       </c>
       <c r="S13">
-        <v>2.8827803032285354E-4</v>
-      </c>
-      <c r="T13">
-        <v>-7.3831222229495079E-5</v>
-      </c>
-      <c r="U13">
-        <v>-2.2303177917484072E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-4.8240673407829768E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B14">
-        <v>-0.28975681460033459</v>
+        <v>9.7254611812260403E-2</v>
       </c>
       <c r="C14">
-        <v>-5.874448606977783E-7</v>
+        <v>5.6812036114395512E-6</v>
       </c>
       <c r="D14">
-        <v>-1.1851926018520669E-8</v>
+        <v>-5.9161369366297318E-8</v>
       </c>
       <c r="E14">
-        <v>-5.2351564043678057E-5</v>
+        <v>-1.7782835128710701E-4</v>
       </c>
       <c r="F14">
-        <v>-1.1463832608371572E-4</v>
+        <v>-2.3282468638893402E-4</v>
       </c>
       <c r="G14">
-        <v>1.3961929086500478E-6</v>
+        <v>1.2155124910887065E-6</v>
       </c>
       <c r="H14">
-        <v>2.2387385834125823E-6</v>
+        <v>-7.0592275891626165E-7</v>
       </c>
       <c r="I14">
-        <v>1.5336480504151906E-5</v>
+        <v>-2.999756267550689E-5</v>
       </c>
       <c r="J14">
-        <v>-1.2862512497610979E-5</v>
+        <v>-3.5368201280159157E-5</v>
       </c>
       <c r="K14">
-        <v>1.4525557545968934E-5</v>
+        <v>-1.0955505973165159E-5</v>
       </c>
       <c r="L14">
-        <v>3.0325990744582611E-7</v>
+        <v>-2.3532895435269651E-5</v>
       </c>
       <c r="M14">
-        <v>1.7988468324208737E-5</v>
+        <v>3.0053714946322459E-6</v>
       </c>
       <c r="N14">
-        <v>1.6446091126552767E-5</v>
+        <v>-4.3418095232025265E-5</v>
       </c>
       <c r="O14">
-        <v>9.2061444899844166E-4</v>
+        <v>1.6048405917284557E-3</v>
       </c>
       <c r="P14">
-        <v>3.7847398456178274E-4</v>
+        <v>6.7100745164973014E-4</v>
       </c>
       <c r="Q14">
-        <v>3.7482877026447802E-4</v>
+        <v>-8.0749886906728393E-5</v>
       </c>
       <c r="R14">
-        <v>3.7614804459486288E-4</v>
+        <v>3.5910878262805316E-5</v>
       </c>
       <c r="S14">
-        <v>1.6322630820980481E-5</v>
-      </c>
-      <c r="T14">
-        <v>1.7238551646609632E-6</v>
-      </c>
-      <c r="U14">
-        <v>-3.4902188633207249E-4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-6.0559210588760517E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B15">
-        <v>-0.16673440033087025</v>
+        <v>-8.7812082599735358E-2</v>
       </c>
       <c r="C15">
-        <v>-2.370461326808416E-6</v>
+        <v>-2.699668852087052E-6</v>
       </c>
       <c r="D15">
-        <v>-3.490458104336136E-9</v>
+        <v>2.5075372925537924E-8</v>
       </c>
       <c r="E15">
-        <v>-9.0891382868328873E-5</v>
+        <v>-7.8506181339398166E-5</v>
       </c>
       <c r="F15">
-        <v>-9.0984874086246927E-5</v>
+        <v>-6.6924387722497444E-5</v>
       </c>
       <c r="G15">
-        <v>2.2773960754347802E-6</v>
+        <v>-1.8449811680657107E-8</v>
       </c>
       <c r="H15">
-        <v>1.8721208974156822E-6</v>
+        <v>-3.3822248589595686E-6</v>
       </c>
       <c r="I15">
-        <v>2.3337179548262194E-5</v>
+        <v>-5.2034205506917063E-5</v>
       </c>
       <c r="J15">
-        <v>-4.8741064750984798E-6</v>
+        <v>6.9176886847707262E-6</v>
       </c>
       <c r="K15">
-        <v>-3.41680497074353E-5</v>
+        <v>-7.870812555215486E-6</v>
       </c>
       <c r="L15">
-        <v>-4.6504578633720637E-5</v>
+        <v>-1.7726117435842517E-5</v>
       </c>
       <c r="M15">
-        <v>-4.4231402602473675E-5</v>
+        <v>-2.9092913732728815E-5</v>
       </c>
       <c r="N15">
-        <v>-3.6205489759027492E-5</v>
+        <v>-1.0578519579900006E-4</v>
       </c>
       <c r="O15">
-        <v>3.7847398456178274E-4</v>
+        <v>6.7100745164973014E-4</v>
       </c>
       <c r="P15">
-        <v>1.8197848177492972E-3</v>
+        <v>9.3767884671196666E-4</v>
       </c>
       <c r="Q15">
-        <v>3.7601576446044845E-4</v>
+        <v>-7.4506601046342606E-6</v>
       </c>
       <c r="R15">
-        <v>3.7825199892652604E-4</v>
+        <v>3.6216425021380619E-5</v>
       </c>
       <c r="S15">
-        <v>-1.4794091353346807E-5</v>
-      </c>
-      <c r="T15">
-        <v>-3.8654294168277661E-5</v>
-      </c>
-      <c r="U15">
-        <v>-2.3281971535627936E-4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-3.9411960319341759E-4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B16">
-        <v>-1.0741569520603693E-2</v>
+        <v>-2.4586275315530708E-3</v>
       </c>
       <c r="C16">
-        <v>2.0382471319313892E-6</v>
+        <v>1.22333733561202E-5</v>
       </c>
       <c r="D16">
-        <v>-1.8521597140781871E-8</v>
+        <v>-1.7304713036216376E-7</v>
       </c>
       <c r="E16">
-        <v>-5.0644929818794847E-6</v>
+        <v>6.4296524373620435E-5</v>
       </c>
       <c r="F16">
-        <v>7.0164371315039047E-5</v>
+        <v>-4.7143615569185054E-5</v>
       </c>
       <c r="G16">
-        <v>6.0303289434779521E-8</v>
+        <v>-1.2925881391400886E-6</v>
       </c>
       <c r="H16">
-        <v>-1.3078571296251137E-6</v>
+        <v>2.021067213511433E-6</v>
       </c>
       <c r="I16">
-        <v>-1.0391956452389156E-5</v>
+        <v>3.1035534500310972E-5</v>
       </c>
       <c r="J16">
-        <v>-7.912065323884419E-6</v>
+        <v>-1.7616007650227323E-5</v>
       </c>
       <c r="K16">
-        <v>-5.8067745537993427E-5</v>
+        <v>-8.1087431168268764E-5</v>
       </c>
       <c r="L16">
-        <v>-5.6444198605575782E-5</v>
+        <v>-2.7282249208467638E-5</v>
       </c>
       <c r="M16">
-        <v>-6.6267298817066259E-5</v>
+        <v>-9.4174411703365474E-5</v>
       </c>
       <c r="N16">
-        <v>-3.6186888870671466E-5</v>
+        <v>-1.1013520374359047E-4</v>
       </c>
       <c r="O16">
-        <v>3.7482877026447802E-4</v>
+        <v>-8.0749886906728393E-5</v>
       </c>
       <c r="P16">
-        <v>3.7601576446044845E-4</v>
+        <v>-7.4506601046342606E-6</v>
       </c>
       <c r="Q16">
-        <v>7.1934907288709554E-4</v>
+        <v>1.7873108767640306E-3</v>
       </c>
       <c r="R16">
-        <v>3.770300720128167E-4</v>
+        <v>1.8314430267833806E-4</v>
       </c>
       <c r="S16">
-        <v>-7.9207727196650033E-6</v>
-      </c>
-      <c r="T16">
-        <v>-2.3477217605395335E-5</v>
-      </c>
-      <c r="U16">
-        <v>-3.5895503614843157E-4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-2.7418912632400983E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B17">
-        <v>-7.9276933491462906E-2</v>
+        <v>0.16622865977597612</v>
       </c>
       <c r="C17">
-        <v>-4.9332346457790745E-6</v>
+        <v>4.8628104985100426E-6</v>
       </c>
       <c r="D17">
-        <v>4.187286558905565E-8</v>
+        <v>-9.6691571055058368E-8</v>
       </c>
       <c r="E17">
-        <v>-4.6231243748156477E-5</v>
+        <v>3.6843946171005158E-5</v>
       </c>
       <c r="F17">
-        <v>1.4262870722837697E-5</v>
+        <v>2.5890221626737027E-5</v>
       </c>
       <c r="G17">
-        <v>1.22509434853718E-6</v>
+        <v>-8.8126272669295515E-7</v>
       </c>
       <c r="H17">
-        <v>2.4122802097814307E-7</v>
+        <v>6.9933467941895502E-7</v>
       </c>
       <c r="I17">
-        <v>1.648012596819359E-5</v>
+        <v>3.1463067265948054E-5</v>
       </c>
       <c r="J17">
-        <v>-3.548769262808528E-6</v>
+        <v>-4.2971397131888693E-5</v>
       </c>
       <c r="K17">
-        <v>-1.1783791123626454E-5</v>
+        <v>4.2151862295487018E-5</v>
       </c>
       <c r="L17">
-        <v>-1.5850351416079334E-5</v>
+        <v>4.4988047976931574E-5</v>
       </c>
       <c r="M17">
-        <v>-1.6121575520074879E-5</v>
+        <v>2.5690835976581856E-5</v>
       </c>
       <c r="N17">
-        <v>4.5663664514786553E-7</v>
+        <v>-5.7983268090683337E-6</v>
       </c>
       <c r="O17">
-        <v>3.7614804459486288E-4</v>
+        <v>3.5910878262805316E-5</v>
       </c>
       <c r="P17">
-        <v>3.7825199892652604E-4</v>
+        <v>3.6216425021380619E-5</v>
       </c>
       <c r="Q17">
-        <v>3.770300720128167E-4</v>
+        <v>1.8314430267833806E-4</v>
       </c>
       <c r="R17">
-        <v>7.3139807400286749E-4</v>
+        <v>6.0276657509005377E-3</v>
       </c>
       <c r="S17">
-        <v>-1.4748028228155458E-5</v>
-      </c>
-      <c r="T17">
-        <v>-1.4937605673638867E-5</v>
-      </c>
-      <c r="U17">
-        <v>-2.4817774997782104E-4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-2.4685426684023396E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B18">
-        <v>-0.10746238538034809</v>
+        <v>-1.5830485792421831</v>
       </c>
       <c r="C18">
-        <v>4.3755737006589052E-6</v>
+        <v>-2.3479700269470266E-3</v>
       </c>
       <c r="D18">
-        <v>-6.6930739141457928E-8</v>
+        <v>2.5398498694099362E-5</v>
       </c>
       <c r="E18">
-        <v>4.3978317524855901E-6</v>
+        <v>-8.8396657131173031E-3</v>
       </c>
       <c r="F18">
-        <v>-4.0191151188356101E-6</v>
+        <v>2.7603492709643461E-3</v>
       </c>
       <c r="G18">
-        <v>4.4388299106721707E-7</v>
+        <v>1.9770158120992862E-4</v>
       </c>
       <c r="H18">
-        <v>8.4269785749024716E-7</v>
+        <v>-5.3924309508154289E-5</v>
       </c>
       <c r="I18">
-        <v>2.6693699782483039E-5</v>
+        <v>8.8249276892101325E-4</v>
       </c>
       <c r="J18">
-        <v>-1.1251610601675641E-5</v>
+        <v>1.9040669504226334E-3</v>
       </c>
       <c r="K18">
-        <v>1.3989323821699163E-4</v>
+        <v>-4.7936621386774542E-2</v>
       </c>
       <c r="L18">
-        <v>1.8168174935302435E-4</v>
+        <v>-4.7774960092169277E-2</v>
       </c>
       <c r="M18">
-        <v>2.6960987265023162E-4</v>
+        <v>-4.7660895305713297E-2</v>
       </c>
       <c r="N18">
-        <v>2.8827803032285354E-4</v>
+        <v>-4.8240673407829768E-2</v>
       </c>
       <c r="O18">
-        <v>1.6322630820980481E-5</v>
+        <v>-6.0559210588760517E-4</v>
       </c>
       <c r="P18">
-        <v>-1.4794091353346807E-5</v>
+        <v>-3.9411960319341759E-4</v>
       </c>
       <c r="Q18">
-        <v>-7.9207727196650033E-6</v>
+        <v>-2.7418912632400983E-4</v>
       </c>
       <c r="R18">
-        <v>-1.4748028228155458E-5</v>
+        <v>-2.4685426684023396E-4</v>
       </c>
       <c r="S18">
-        <v>9.098742125547651E-4</v>
-      </c>
-      <c r="T18">
-        <v>1.1194869961548342E-4</v>
-      </c>
-      <c r="U18">
-        <v>-4.4860342118591259E-4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19">
-        <v>5.4185637017555952E-2</v>
-      </c>
-      <c r="C19">
-        <v>6.9137596541856418E-6</v>
-      </c>
-      <c r="D19">
-        <v>-9.7778576614864938E-8</v>
-      </c>
-      <c r="E19">
-        <v>4.5058040437772991E-5</v>
-      </c>
-      <c r="F19">
-        <v>6.6073262206144793E-5</v>
-      </c>
-      <c r="G19">
-        <v>-3.8038831695508604E-7</v>
-      </c>
-      <c r="H19">
-        <v>-6.4970161824140888E-7</v>
-      </c>
-      <c r="I19">
-        <v>3.4216077500947404E-5</v>
-      </c>
-      <c r="J19">
-        <v>-6.271428616984261E-6</v>
-      </c>
-      <c r="K19">
-        <v>9.0078635385618686E-6</v>
-      </c>
-      <c r="L19">
-        <v>5.3143497878306687E-6</v>
-      </c>
-      <c r="M19">
-        <v>-1.538970380285192E-5</v>
-      </c>
-      <c r="N19">
-        <v>-7.3831222229495079E-5</v>
-      </c>
-      <c r="O19">
-        <v>1.7238551646609632E-6</v>
-      </c>
-      <c r="P19">
-        <v>-3.8654294168277661E-5</v>
-      </c>
-      <c r="Q19">
-        <v>-2.3477217605395335E-5</v>
-      </c>
-      <c r="R19">
-        <v>-1.4937605673638867E-5</v>
-      </c>
-      <c r="S19">
-        <v>1.1194869961548342E-4</v>
-      </c>
-      <c r="T19">
-        <v>1.7798058548009674E-3</v>
-      </c>
-      <c r="U19">
-        <v>-2.1973236060633149E-4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20">
-        <v>-3.1985862706502113</v>
-      </c>
-      <c r="C20">
-        <v>-1.3017969006119149E-3</v>
-      </c>
-      <c r="D20">
-        <v>1.3152903791723208E-5</v>
-      </c>
-      <c r="E20">
-        <v>-7.8901706852183284E-3</v>
-      </c>
-      <c r="F20">
-        <v>-5.5102373468521471E-3</v>
-      </c>
-      <c r="G20">
-        <v>1.7102762788115533E-4</v>
-      </c>
-      <c r="H20">
-        <v>1.2250917552511335E-4</v>
-      </c>
-      <c r="I20">
-        <v>1.7718965949682538E-4</v>
-      </c>
-      <c r="J20">
-        <v>1.2363120055002817E-3</v>
-      </c>
-      <c r="K20">
-        <v>-2.1672893123388236E-2</v>
-      </c>
-      <c r="L20">
-        <v>-2.1740359090585807E-2</v>
-      </c>
-      <c r="M20">
-        <v>-2.1931130404519227E-2</v>
-      </c>
-      <c r="N20">
-        <v>-2.2303177917484072E-2</v>
-      </c>
-      <c r="O20">
-        <v>-3.4902188633207249E-4</v>
-      </c>
-      <c r="P20">
-        <v>-2.3281971535627936E-4</v>
-      </c>
-      <c r="Q20">
-        <v>-3.5895503614843157E-4</v>
-      </c>
-      <c r="R20">
-        <v>-2.4817774997782104E-4</v>
-      </c>
-      <c r="S20">
-        <v>-4.4860342118591259E-4</v>
-      </c>
-      <c r="T20">
-        <v>-2.1973236060633149E-4</v>
-      </c>
-      <c r="U20">
-        <v>5.2058515908797259E-2</v>
+        <v>9.8454141102265885E-2</v>
       </c>
     </row>
   </sheetData>
@@ -4807,14 +4052,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43153968-584D-43BC-8C7D-7725BE1C9391}">
-  <dimension ref="A1:U20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="16384" width="9" style="2"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87467EE5-0F0D-4950-9971-D3F3C5CEB29B}">
+  <dimension ref="A1:S18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -4858,1260 +4100,1022 @@
         <v>23</v>
       </c>
       <c r="O1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="P1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="Q1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="R1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="S1" t="s">
-        <v>24</v>
-      </c>
-      <c r="T1" t="s">
-        <v>25</v>
-      </c>
-      <c r="U1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2">
-        <v>0.16014153105381737</v>
+        <v>0.1353886144714484</v>
       </c>
       <c r="C2">
-        <v>5.0630821004363189E-5</v>
+        <v>9.1467621717142419E-5</v>
       </c>
       <c r="D2">
-        <v>-5.2368924155971429E-7</v>
+        <v>-9.7812014131072017E-7</v>
       </c>
       <c r="E2">
-        <v>2.668282822538313E-4</v>
+        <v>3.9084340551209345E-4</v>
       </c>
       <c r="F2">
-        <v>1.9176025177940423E-4</v>
+        <v>7.3965944038378083E-5</v>
       </c>
       <c r="G2">
-        <v>-5.7797276622590503E-6</v>
+        <v>-8.5743889954073267E-6</v>
       </c>
       <c r="H2">
-        <v>-4.299874114425828E-6</v>
+        <v>-1.8139255080146661E-6</v>
       </c>
       <c r="I2">
-        <v>2.364693101858865E-6</v>
+        <v>-1.1198122265820211E-7</v>
       </c>
       <c r="J2">
-        <v>-5.9997672812430052E-5</v>
+        <v>-9.989576313608215E-5</v>
       </c>
       <c r="K2">
-        <v>-1.5563009798783055E-5</v>
+        <v>4.0011559855158063E-5</v>
       </c>
       <c r="L2">
-        <v>-1.9766302118130697E-5</v>
+        <v>4.0881789881167517E-5</v>
       </c>
       <c r="M2">
-        <v>-2.2210318004473766E-5</v>
+        <v>1.9459011589502894E-5</v>
       </c>
       <c r="N2">
-        <v>-1.3480307993270603E-5</v>
+        <v>2.7580221923044317E-5</v>
       </c>
       <c r="O2">
-        <v>-1.722445078440298E-7</v>
+        <v>9.4556542375068059E-6</v>
       </c>
       <c r="P2">
-        <v>2.2621790227096362E-6</v>
+        <v>3.0829652103056914E-6</v>
       </c>
       <c r="Q2">
-        <v>2.3991446953912111E-6</v>
+        <v>7.3110629487688374E-6</v>
       </c>
       <c r="R2">
-        <v>-3.3191668018174263E-6</v>
+        <v>1.3631580733524158E-5</v>
       </c>
       <c r="S2">
-        <v>5.542133523911114E-7</v>
-      </c>
-      <c r="T2">
-        <v>5.2746190028111183E-6</v>
-      </c>
-      <c r="U2">
-        <v>-1.1135601312801011E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-2.0132406675531685E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>15</v>
       </c>
       <c r="B3">
-        <v>-1.6439895719806276E-3</v>
+        <v>-1.4764293224755897E-3</v>
       </c>
       <c r="C3">
-        <v>-5.2368924155971429E-7</v>
+        <v>-9.7812014131072017E-7</v>
       </c>
       <c r="D3">
-        <v>5.9032797005441358E-9</v>
+        <v>1.1019080875540933E-8</v>
       </c>
       <c r="E3">
-        <v>-1.0706543729300274E-6</v>
+        <v>-2.4031438048400712E-6</v>
       </c>
       <c r="F3">
-        <v>-2.1435211562259363E-7</v>
+        <v>1.1571805100087809E-6</v>
       </c>
       <c r="G3">
-        <v>2.0845105794682059E-8</v>
+        <v>5.1639630767174177E-8</v>
       </c>
       <c r="H3">
-        <v>4.0954443282871672E-9</v>
+        <v>-2.4074532971854831E-8</v>
       </c>
       <c r="I3">
-        <v>-1.4523625682413423E-7</v>
+        <v>-2.5637207646524764E-7</v>
       </c>
       <c r="J3">
-        <v>7.2766952902568039E-7</v>
+        <v>1.2381891837900468E-6</v>
       </c>
       <c r="K3">
-        <v>1.2231691700982213E-7</v>
+        <v>-4.8791034271895273E-7</v>
       </c>
       <c r="L3">
-        <v>1.8276580332176824E-7</v>
+        <v>-4.7617692409602678E-7</v>
       </c>
       <c r="M3">
-        <v>2.4623230069167793E-7</v>
+        <v>-2.1020494501931718E-7</v>
       </c>
       <c r="N3">
-        <v>1.92721574307935E-7</v>
+        <v>-1.9273104139859351E-7</v>
       </c>
       <c r="O3">
-        <v>-7.3415494540964995E-9</v>
+        <v>-1.157310678534181E-7</v>
       </c>
       <c r="P3">
-        <v>-4.1405463618942173E-8</v>
+        <v>-6.2995994491638683E-8</v>
       </c>
       <c r="Q3">
-        <v>-2.7963942818845067E-8</v>
+        <v>-1.0985379778191721E-7</v>
       </c>
       <c r="R3">
-        <v>2.3311869542606505E-8</v>
+        <v>-2.0467457236225154E-7</v>
       </c>
       <c r="S3">
-        <v>-1.1647933314582327E-8</v>
-      </c>
-      <c r="T3">
-        <v>-6.8873212652933109E-8</v>
-      </c>
-      <c r="U3">
-        <v>1.0553055313925292E-5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+        <v>2.0421382490313473E-5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
       <c r="B4">
-        <v>0.4950506285393847</v>
+        <v>-3.0784522865401204E-2</v>
       </c>
       <c r="C4">
-        <v>2.668282822538313E-4</v>
+        <v>3.9084340551209345E-4</v>
       </c>
       <c r="D4">
-        <v>-1.0706543729300274E-6</v>
+        <v>-2.4031438048400712E-6</v>
       </c>
       <c r="E4">
-        <v>1.0488686867303561E-2</v>
+        <v>1.2919843291610701E-2</v>
       </c>
       <c r="F4">
-        <v>8.0352202637165547E-3</v>
+        <v>8.0964949196880766E-3</v>
       </c>
       <c r="G4">
-        <v>-2.2530004734945248E-4</v>
+        <v>-2.7738187926644865E-4</v>
       </c>
       <c r="H4">
-        <v>-1.728127260434468E-4</v>
+        <v>-1.7141632009953298E-4</v>
       </c>
       <c r="I4">
-        <v>3.4988445745760429E-5</v>
+        <v>4.157632101062193E-5</v>
       </c>
       <c r="J4">
-        <v>-1.5548585841976872E-4</v>
+        <v>-2.7849206698020402E-4</v>
       </c>
       <c r="K4">
-        <v>-2.71262895294611E-4</v>
+        <v>1.4476827231387976E-4</v>
       </c>
       <c r="L4">
-        <v>-2.3446099711258838E-4</v>
+        <v>2.297317151055767E-4</v>
       </c>
       <c r="M4">
-        <v>-2.5014098609346452E-4</v>
+        <v>1.5130623853884355E-4</v>
       </c>
       <c r="N4">
-        <v>-2.2324790646733456E-4</v>
+        <v>1.737627423225984E-4</v>
       </c>
       <c r="O4">
-        <v>-4.3558166736141961E-5</v>
+        <v>-1.6564954706462288E-4</v>
       </c>
       <c r="P4">
-        <v>-5.4170447110038817E-5</v>
+        <v>-1.2150213826119868E-4</v>
       </c>
       <c r="Q4">
-        <v>-1.5659281569126556E-5</v>
+        <v>1.9240455357888676E-5</v>
       </c>
       <c r="R4">
-        <v>-3.6652921427093446E-5</v>
+        <v>-6.6312637477876813E-5</v>
       </c>
       <c r="S4">
-        <v>3.5847934905068052E-5</v>
-      </c>
-      <c r="T4">
-        <v>6.2512585385281915E-5</v>
-      </c>
-      <c r="U4">
-        <v>-9.6714204456533823E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-1.2815575569462336E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
       <c r="B5">
-        <v>0.4639662192829222</v>
+        <v>-0.25944981495187874</v>
       </c>
       <c r="C5">
-        <v>1.9176025177940423E-4</v>
+        <v>7.3965944038378083E-5</v>
       </c>
       <c r="D5">
-        <v>-2.1435211562259363E-7</v>
+        <v>1.1571805100087809E-6</v>
       </c>
       <c r="E5">
-        <v>8.0352202637165547E-3</v>
+        <v>8.0964949196880766E-3</v>
       </c>
       <c r="F5">
-        <v>1.2918061422724949E-2</v>
+        <v>2.1525157830316992E-2</v>
       </c>
       <c r="G5">
-        <v>-1.7301513144326152E-4</v>
+        <v>-1.7184729808732729E-4</v>
       </c>
       <c r="H5">
-        <v>-2.7024163412181881E-4</v>
+        <v>-4.3222155074238724E-4</v>
       </c>
       <c r="I5">
-        <v>1.8485427604320753E-5</v>
+        <v>6.9283985931128088E-5</v>
       </c>
       <c r="J5">
-        <v>-2.3418352221129033E-4</v>
+        <v>-4.6360055926254425E-4</v>
       </c>
       <c r="K5">
-        <v>-2.1929174340031563E-4</v>
+        <v>1.248552377121335E-4</v>
       </c>
       <c r="L5">
-        <v>-1.9364681770705008E-4</v>
+        <v>2.0560523316586485E-4</v>
       </c>
       <c r="M5">
-        <v>-2.2223399644873349E-4</v>
+        <v>8.7440728328730052E-5</v>
       </c>
       <c r="N5">
-        <v>-1.4496498569025818E-4</v>
+        <v>1.1715322306155712E-4</v>
       </c>
       <c r="O5">
-        <v>-6.0302569911059256E-5</v>
+        <v>-2.0571094759482385E-4</v>
       </c>
       <c r="P5">
-        <v>-6.838577944489543E-5</v>
+        <v>-1.2975359834338469E-4</v>
       </c>
       <c r="Q5">
-        <v>2.4455767231052672E-5</v>
+        <v>5.7537973327299321E-5</v>
       </c>
       <c r="R5">
-        <v>-3.1949093644481304E-5</v>
+        <v>-8.8148846299568074E-5</v>
       </c>
       <c r="S5">
-        <v>4.3159309391400518E-5</v>
-      </c>
-      <c r="T5">
-        <v>7.6604072547063409E-5</v>
-      </c>
-      <c r="U5">
-        <v>-8.1509002182341833E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-6.0950607968087E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>27</v>
       </c>
       <c r="B6">
-        <v>-1.0442361326860859E-2</v>
+        <v>4.9408966191714145E-5</v>
       </c>
       <c r="C6">
-        <v>-5.7797276622590503E-6</v>
+        <v>-8.5743889954073267E-6</v>
       </c>
       <c r="D6">
-        <v>2.0845105794682059E-8</v>
+        <v>5.1639630767174177E-8</v>
       </c>
       <c r="E6">
-        <v>-2.2530004734945248E-4</v>
+        <v>-2.7738187926644865E-4</v>
       </c>
       <c r="F6">
-        <v>-1.7301513144326152E-4</v>
+        <v>-1.7184729808732729E-4</v>
       </c>
       <c r="G6">
-        <v>5.1678780805307223E-6</v>
+        <v>6.3491173357979667E-6</v>
       </c>
       <c r="H6">
-        <v>3.9609843207209882E-6</v>
+        <v>3.886149325540114E-6</v>
       </c>
       <c r="I6">
-        <v>-1.0322553460433709E-6</v>
+        <v>-1.0661675351007915E-6</v>
       </c>
       <c r="J6">
-        <v>3.4227643185557299E-6</v>
+        <v>6.050977551665317E-6</v>
       </c>
       <c r="K6">
-        <v>6.7223929073088689E-6</v>
+        <v>-3.9526744459397761E-6</v>
       </c>
       <c r="L6">
-        <v>5.9345672049429814E-6</v>
+        <v>-6.4408209160362245E-6</v>
       </c>
       <c r="M6">
-        <v>6.6443942348316283E-6</v>
+        <v>-4.1182160470683684E-6</v>
       </c>
       <c r="N6">
-        <v>6.2436974521190222E-6</v>
+        <v>-3.8710776677730553E-6</v>
       </c>
       <c r="O6">
-        <v>9.9669961823471284E-7</v>
+        <v>1.1913499768653453E-6</v>
       </c>
       <c r="P6">
-        <v>1.2934976085714162E-6</v>
+        <v>3.1570715686370967E-7</v>
       </c>
       <c r="Q6">
-        <v>1.962202378184701E-7</v>
+        <v>-8.4086490503052985E-7</v>
       </c>
       <c r="R6">
-        <v>9.6077506648547138E-7</v>
+        <v>3.4796851448337864E-7</v>
       </c>
       <c r="S6">
-        <v>-5.1301654658652414E-7</v>
-      </c>
-      <c r="T6">
-        <v>-9.4346988155687637E-7</v>
-      </c>
-      <c r="U6">
-        <v>2.0260508682320348E-4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+        <v>2.7475551255166318E-4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>28</v>
       </c>
       <c r="B7">
-        <v>-1.3291166411001058E-2</v>
+        <v>2.9013585777012121E-3</v>
       </c>
       <c r="C7">
-        <v>-4.299874114425828E-6</v>
+        <v>-1.8139255080146661E-6</v>
       </c>
       <c r="D7">
-        <v>4.0954443282871672E-9</v>
+        <v>-2.4074532971854831E-8</v>
       </c>
       <c r="E7">
-        <v>-1.728127260434468E-4</v>
+        <v>-1.7141632009953298E-4</v>
       </c>
       <c r="F7">
-        <v>-2.7024163412181881E-4</v>
+        <v>-4.3222155074238724E-4</v>
       </c>
       <c r="G7">
-        <v>3.9609843207209882E-6</v>
+        <v>3.886149325540114E-6</v>
       </c>
       <c r="H7">
-        <v>6.0022265692729428E-6</v>
+        <v>9.1665955281701582E-6</v>
       </c>
       <c r="I7">
-        <v>-9.6762335643933934E-7</v>
+        <v>-1.9904157947006211E-6</v>
       </c>
       <c r="J7">
-        <v>5.1560093311154052E-6</v>
+        <v>1.0133633440555271E-5</v>
       </c>
       <c r="K7">
-        <v>4.7458459044915637E-6</v>
+        <v>-3.2952144281677418E-6</v>
       </c>
       <c r="L7">
-        <v>4.4280871576168228E-6</v>
+        <v>-4.6515957169408171E-6</v>
       </c>
       <c r="M7">
-        <v>6.0157985670712097E-6</v>
+        <v>-6.1243228836349876E-7</v>
       </c>
       <c r="N7">
-        <v>4.7929011884338587E-6</v>
+        <v>1.5409947899575917E-7</v>
       </c>
       <c r="O7">
-        <v>6.6355851705747697E-7</v>
+        <v>-4.1581866265821325E-7</v>
       </c>
       <c r="P7">
-        <v>6.5448357706602333E-7</v>
+        <v>-2.093768492365384E-6</v>
       </c>
       <c r="Q7">
-        <v>-4.5905722994325752E-7</v>
+        <v>-8.0973506603725822E-7</v>
       </c>
       <c r="R7">
-        <v>7.51976611483882E-7</v>
+        <v>2.1088534207859283E-6</v>
       </c>
       <c r="S7">
-        <v>-3.844878576548745E-7</v>
-      </c>
-      <c r="T7">
-        <v>-1.1530492061730575E-6</v>
-      </c>
-      <c r="U7">
-        <v>1.7272721890891285E-4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+        <v>1.2996263204848529E-4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>18</v>
       </c>
       <c r="B8">
-        <v>0.21384698151182899</v>
+        <v>0.24928376881874367</v>
       </c>
       <c r="C8">
-        <v>2.364693101858865E-6</v>
+        <v>-1.1198122265820211E-7</v>
       </c>
       <c r="D8">
-        <v>-1.4523625682413423E-7</v>
+        <v>-2.5637207646524764E-7</v>
       </c>
       <c r="E8">
-        <v>3.4988445745760429E-5</v>
+        <v>4.157632101062193E-5</v>
       </c>
       <c r="F8">
-        <v>1.8485427604320753E-5</v>
+        <v>6.9283985931128088E-5</v>
       </c>
       <c r="G8">
-        <v>-1.0322553460433709E-6</v>
+        <v>-1.0661675351007915E-6</v>
       </c>
       <c r="H8">
-        <v>-9.6762335643933934E-7</v>
+        <v>-1.9904157947006211E-6</v>
       </c>
       <c r="I8">
-        <v>6.1796875936086801E-4</v>
+        <v>1.1554501388860996E-3</v>
       </c>
       <c r="J8">
-        <v>-3.7497478690561557E-4</v>
+        <v>-6.7284931370970903E-4</v>
       </c>
       <c r="K8">
-        <v>4.4761269406464125E-5</v>
+        <v>1.049971861618407E-5</v>
       </c>
       <c r="L8">
-        <v>5.9902405359073981E-5</v>
+        <v>3.8217915019731519E-6</v>
       </c>
       <c r="M8">
-        <v>4.6305666069040131E-5</v>
+        <v>-5.0602482790209274E-6</v>
       </c>
       <c r="N8">
-        <v>5.1068782388609506E-5</v>
+        <v>4.3523940448230287E-5</v>
       </c>
       <c r="O8">
-        <v>-5.4892206806808937E-6</v>
+        <v>2.4534641687168204E-5</v>
       </c>
       <c r="P8">
-        <v>-1.6539226477007367E-5</v>
+        <v>4.325161289895353E-5</v>
       </c>
       <c r="Q8">
-        <v>2.7328509818100592E-6</v>
+        <v>2.9769772419562816E-5</v>
       </c>
       <c r="R8">
-        <v>1.4405351413018885E-5</v>
+        <v>4.7778292883395375E-5</v>
       </c>
       <c r="S8">
-        <v>3.3786718897630341E-5</v>
-      </c>
-      <c r="T8">
-        <v>3.54521696126912E-5</v>
-      </c>
-      <c r="U8">
-        <v>-6.9602413068016615E-5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+        <v>1.3947093333270183E-5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>19</v>
       </c>
       <c r="B9">
-        <v>0.1509164931780729</v>
+        <v>0.15729799650635709</v>
       </c>
       <c r="C9">
-        <v>-5.9997672812430052E-5</v>
+        <v>-9.989576313608215E-5</v>
       </c>
       <c r="D9">
-        <v>7.2766952902568039E-7</v>
+        <v>1.2381891837900468E-6</v>
       </c>
       <c r="E9">
-        <v>-1.5548585841976872E-4</v>
+        <v>-2.7849206698020402E-4</v>
       </c>
       <c r="F9">
-        <v>-2.3418352221129033E-4</v>
+        <v>-4.6360055926254425E-4</v>
       </c>
       <c r="G9">
-        <v>3.4227643185557299E-6</v>
+        <v>6.050977551665317E-6</v>
       </c>
       <c r="H9">
-        <v>5.1560093311154052E-6</v>
+        <v>1.0133633440555271E-5</v>
       </c>
       <c r="I9">
-        <v>-3.7497478690561557E-4</v>
+        <v>-6.7284931370970903E-4</v>
       </c>
       <c r="J9">
-        <v>7.3795263833672392E-4</v>
+        <v>1.174431753492085E-3</v>
       </c>
       <c r="K9">
-        <v>-7.475434199807245E-6</v>
+        <v>-9.4401013266262254E-5</v>
       </c>
       <c r="L9">
-        <v>-1.7140032492401472E-5</v>
+        <v>-8.14422760242469E-5</v>
       </c>
       <c r="M9">
-        <v>-1.7190971304137533E-5</v>
+        <v>-8.4247186908254575E-5</v>
       </c>
       <c r="N9">
-        <v>-1.0793137523339494E-5</v>
+        <v>-1.0803323628960821E-4</v>
       </c>
       <c r="O9">
-        <v>-1.9970769546636098E-5</v>
+        <v>-1.5729002233802734E-5</v>
       </c>
       <c r="P9">
-        <v>-1.3503340704290248E-5</v>
+        <v>-1.7023824768450618E-5</v>
       </c>
       <c r="Q9">
-        <v>-9.7038111611169713E-6</v>
+        <v>-1.601460813675806E-5</v>
       </c>
       <c r="R9">
-        <v>-3.1011652843156467E-6</v>
+        <v>-2.7772084131539434E-5</v>
       </c>
       <c r="S9">
-        <v>-6.8016713171535625E-6</v>
-      </c>
-      <c r="T9">
-        <v>-1.1669827593387049E-5</v>
-      </c>
-      <c r="U9">
-        <v>1.1597034318128123E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+        <v>1.9940792767828984E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>20</v>
       </c>
       <c r="B10">
-        <v>5.03013188529495E-2</v>
+        <v>-7.6048042973068275E-2</v>
       </c>
       <c r="C10">
-        <v>-1.5563009798783055E-5</v>
+        <v>4.0011559855158063E-5</v>
       </c>
       <c r="D10">
-        <v>1.2231691700982213E-7</v>
+        <v>-4.8791034271895273E-7</v>
       </c>
       <c r="E10">
-        <v>-2.71262895294611E-4</v>
+        <v>1.4476827231387976E-4</v>
       </c>
       <c r="F10">
-        <v>-2.1929174340031563E-4</v>
+        <v>1.248552377121335E-4</v>
       </c>
       <c r="G10">
-        <v>6.7223929073088689E-6</v>
+        <v>-3.9526744459397761E-6</v>
       </c>
       <c r="H10">
-        <v>4.7458459044915637E-6</v>
+        <v>-3.2952144281677418E-6</v>
       </c>
       <c r="I10">
-        <v>4.4761269406464125E-5</v>
+        <v>1.049971861618407E-5</v>
       </c>
       <c r="J10">
-        <v>-7.475434199807245E-6</v>
+        <v>-9.4401013266262254E-5</v>
       </c>
       <c r="K10">
-        <v>2.1224719408154177E-2</v>
+        <v>4.0510995450321677E-2</v>
       </c>
       <c r="L10">
-        <v>1.8649383744936118E-2</v>
+        <v>3.278696271438724E-2</v>
       </c>
       <c r="M10">
-        <v>1.865858514752541E-2</v>
+        <v>3.2758219707248057E-2</v>
       </c>
       <c r="N10">
-        <v>1.8662280700243783E-2</v>
+        <v>3.2711200621266978E-2</v>
       </c>
       <c r="O10">
-        <v>8.3479761221535856E-6</v>
+        <v>-8.9941121421260048E-6</v>
       </c>
       <c r="P10">
-        <v>3.818614437122723E-5</v>
+        <v>-2.8942685802240851E-5</v>
       </c>
       <c r="Q10">
-        <v>1.9637980948991769E-6</v>
+        <v>4.0955476855725618E-5</v>
       </c>
       <c r="R10">
-        <v>-6.8603135056956728E-6</v>
+        <v>1.6884896246418141E-4</v>
       </c>
       <c r="S10">
-        <v>6.9827762657253696E-5</v>
-      </c>
-      <c r="T10">
-        <v>-1.9480778303288568E-5</v>
-      </c>
-      <c r="U10">
-        <v>-1.8265334684390032E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-3.3429701872089948E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>21</v>
       </c>
       <c r="B11">
-        <v>0.35359106127345563</v>
+        <v>0.18995160933757613</v>
       </c>
       <c r="C11">
-        <v>-1.9766302118130697E-5</v>
+        <v>4.0881789881167517E-5</v>
       </c>
       <c r="D11">
-        <v>1.8276580332176824E-7</v>
+        <v>-4.7617692409602678E-7</v>
       </c>
       <c r="E11">
-        <v>-2.3446099711258838E-4</v>
+        <v>2.297317151055767E-4</v>
       </c>
       <c r="F11">
-        <v>-1.9364681770705008E-4</v>
+        <v>2.0560523316586485E-4</v>
       </c>
       <c r="G11">
-        <v>5.9345672049429814E-6</v>
+        <v>-6.4408209160362245E-6</v>
       </c>
       <c r="H11">
-        <v>4.4280871576168228E-6</v>
+        <v>-4.6515957169408171E-6</v>
       </c>
       <c r="I11">
-        <v>5.9902405359073981E-5</v>
+        <v>3.8217915019731519E-6</v>
       </c>
       <c r="J11">
-        <v>-1.7140032492401472E-5</v>
+        <v>-8.14422760242469E-5</v>
       </c>
       <c r="K11">
-        <v>1.8649383744936118E-2</v>
+        <v>3.278696271438724E-2</v>
       </c>
       <c r="L11">
-        <v>1.9223417457068001E-2</v>
+        <v>3.4680770460432664E-2</v>
       </c>
       <c r="M11">
-        <v>1.8676936072989689E-2</v>
+        <v>3.2766248890333971E-2</v>
       </c>
       <c r="N11">
-        <v>1.8685113862595255E-2</v>
+        <v>3.2725031116369221E-2</v>
       </c>
       <c r="O11">
-        <v>4.0868290489433888E-6</v>
+        <v>5.3777182604724199E-5</v>
       </c>
       <c r="P11">
-        <v>4.8096405166353127E-5</v>
+        <v>-3.0381477934219008E-5</v>
       </c>
       <c r="Q11">
-        <v>4.9685513221011692E-6</v>
+        <v>2.8809987422450745E-6</v>
       </c>
       <c r="R11">
-        <v>-2.9767458511327526E-5</v>
+        <v>1.983695665447156E-5</v>
       </c>
       <c r="S11">
-        <v>9.602603037848085E-5</v>
-      </c>
-      <c r="T11">
-        <v>-2.6767836730126195E-5</v>
-      </c>
-      <c r="U11">
-        <v>-1.8232071887149381E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-3.3499347329985371E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>22</v>
       </c>
       <c r="B12">
-        <v>0.45134617462578541</v>
+        <v>0.32384679153534224</v>
       </c>
       <c r="C12">
-        <v>-2.2210318004473766E-5</v>
+        <v>1.9459011589502894E-5</v>
       </c>
       <c r="D12">
-        <v>2.4623230069167793E-7</v>
+        <v>-2.1020494501931718E-7</v>
       </c>
       <c r="E12">
-        <v>-2.5014098609346452E-4</v>
+        <v>1.5130623853884355E-4</v>
       </c>
       <c r="F12">
-        <v>-2.2223399644873349E-4</v>
+        <v>8.7440728328730052E-5</v>
       </c>
       <c r="G12">
-        <v>6.6443942348316283E-6</v>
+        <v>-4.1182160470683684E-6</v>
       </c>
       <c r="H12">
-        <v>6.0157985670712097E-6</v>
+        <v>-6.1243228836349876E-7</v>
       </c>
       <c r="I12">
-        <v>4.6305666069040131E-5</v>
+        <v>-5.0602482790209274E-6</v>
       </c>
       <c r="J12">
-        <v>-1.7190971304137533E-5</v>
+        <v>-8.4247186908254575E-5</v>
       </c>
       <c r="K12">
-        <v>1.865858514752541E-2</v>
+        <v>3.2758219707248057E-2</v>
       </c>
       <c r="L12">
-        <v>1.8676936072989689E-2</v>
+        <v>3.2766248890333971E-2</v>
       </c>
       <c r="M12">
-        <v>1.8857246223978427E-2</v>
+        <v>3.3208734510537852E-2</v>
       </c>
       <c r="N12">
-        <v>1.8760710251238818E-2</v>
+        <v>3.2769599077386954E-2</v>
       </c>
       <c r="O12">
-        <v>8.2772616030091684E-6</v>
+        <v>2.7345159215593607E-5</v>
       </c>
       <c r="P12">
-        <v>4.1302534985789236E-5</v>
+        <v>-5.7430355159880696E-5</v>
       </c>
       <c r="Q12">
-        <v>-1.3975399154520852E-5</v>
+        <v>-1.524186383173871E-5</v>
       </c>
       <c r="R12">
-        <v>-2.9562792813617707E-5</v>
+        <v>6.176432650481403E-5</v>
       </c>
       <c r="S12">
-        <v>1.7272832640820456E-4</v>
-      </c>
-      <c r="T12">
-        <v>-3.2382936481249172E-5</v>
-      </c>
-      <c r="U12">
-        <v>-1.8328144779612615E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-3.3137589384682087E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>23</v>
       </c>
       <c r="B13">
-        <v>0.48873657067541398</v>
+        <v>0.39518715914229102</v>
       </c>
       <c r="C13">
-        <v>-1.3480307993270603E-5</v>
+        <v>2.7580221923044317E-5</v>
       </c>
       <c r="D13">
-        <v>1.92721574307935E-7</v>
+        <v>-1.9273104139859351E-7</v>
       </c>
       <c r="E13">
-        <v>-2.2324790646733456E-4</v>
+        <v>1.737627423225984E-4</v>
       </c>
       <c r="F13">
-        <v>-1.4496498569025818E-4</v>
+        <v>1.1715322306155712E-4</v>
       </c>
       <c r="G13">
-        <v>6.2436974521190222E-6</v>
+        <v>-3.8710776677730553E-6</v>
       </c>
       <c r="H13">
-        <v>4.7929011884338587E-6</v>
+        <v>1.5409947899575917E-7</v>
       </c>
       <c r="I13">
-        <v>5.1068782388609506E-5</v>
+        <v>4.3523940448230287E-5</v>
       </c>
       <c r="J13">
-        <v>-1.0793137523339494E-5</v>
+        <v>-1.0803323628960821E-4</v>
       </c>
       <c r="K13">
-        <v>1.8662280700243783E-2</v>
+        <v>3.2711200621266978E-2</v>
       </c>
       <c r="L13">
-        <v>1.8685113862595255E-2</v>
+        <v>3.2725031116369221E-2</v>
       </c>
       <c r="M13">
-        <v>1.8760710251238818E-2</v>
+        <v>3.2769599077386954E-2</v>
       </c>
       <c r="N13">
-        <v>1.9340131670336193E-2</v>
+        <v>3.3105277943617825E-2</v>
       </c>
       <c r="O13">
-        <v>6.550155202539673E-6</v>
+        <v>-2.923085273124124E-5</v>
       </c>
       <c r="P13">
-        <v>3.4590680505645519E-5</v>
+        <v>-1.3691875555393892E-4</v>
       </c>
       <c r="Q13">
-        <v>7.3475129002230485E-6</v>
+        <v>-3.9095956266818461E-5</v>
       </c>
       <c r="R13">
-        <v>-9.6822832539177506E-6</v>
+        <v>2.7503885289132486E-5</v>
       </c>
       <c r="S13">
-        <v>1.9130658856181401E-4</v>
-      </c>
-      <c r="T13">
-        <v>-7.4289154693602132E-5</v>
-      </c>
-      <c r="U13">
-        <v>-1.8658961389699226E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-3.3595617969659146E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B14">
-        <v>-0.17388542857539849</v>
+        <v>0.21452389894231177</v>
       </c>
       <c r="C14">
-        <v>-1.722445078440298E-7</v>
+        <v>9.4556542375068059E-6</v>
       </c>
       <c r="D14">
-        <v>-7.3415494540964995E-9</v>
+        <v>-1.157310678534181E-7</v>
       </c>
       <c r="E14">
-        <v>-4.3558166736141961E-5</v>
+        <v>-1.6564954706462288E-4</v>
       </c>
       <c r="F14">
-        <v>-6.0302569911059256E-5</v>
+        <v>-2.0571094759482385E-4</v>
       </c>
       <c r="G14">
-        <v>9.9669961823471284E-7</v>
+        <v>1.1913499768653453E-6</v>
       </c>
       <c r="H14">
-        <v>6.6355851705747697E-7</v>
+        <v>-4.1581866265821325E-7</v>
       </c>
       <c r="I14">
-        <v>-5.4892206806808937E-6</v>
+        <v>2.4534641687168204E-5</v>
       </c>
       <c r="J14">
-        <v>-1.9970769546636098E-5</v>
+        <v>-1.5729002233802734E-5</v>
       </c>
       <c r="K14">
-        <v>8.3479761221535856E-6</v>
+        <v>-8.9941121421260048E-6</v>
       </c>
       <c r="L14">
-        <v>4.0868290489433888E-6</v>
+        <v>5.3777182604724199E-5</v>
       </c>
       <c r="M14">
-        <v>8.2772616030091684E-6</v>
+        <v>2.7345159215593607E-5</v>
       </c>
       <c r="N14">
-        <v>6.550155202539673E-6</v>
+        <v>-2.923085273124124E-5</v>
       </c>
       <c r="O14">
-        <v>7.8413476824234953E-4</v>
+        <v>1.4551184824678493E-3</v>
       </c>
       <c r="P14">
-        <v>3.7037031322499755E-4</v>
+        <v>5.9508925901910112E-4</v>
       </c>
       <c r="Q14">
-        <v>3.6415447632432801E-4</v>
+        <v>-6.2068087059668071E-5</v>
       </c>
       <c r="R14">
-        <v>3.650370310593585E-4</v>
+        <v>4.5984356418568073E-5</v>
       </c>
       <c r="S14">
-        <v>1.3075309473251689E-6</v>
-      </c>
-      <c r="T14">
-        <v>-9.1663994682348562E-6</v>
-      </c>
-      <c r="U14">
-        <v>-3.3089833030840703E-4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-6.4435638581217497E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B15">
-        <v>-0.21949401773440641</v>
+        <v>8.1807109859653782E-2</v>
       </c>
       <c r="C15">
-        <v>2.2621790227096362E-6</v>
+        <v>3.0829652103056914E-6</v>
       </c>
       <c r="D15">
-        <v>-4.1405463618942173E-8</v>
+        <v>-6.2995994491638683E-8</v>
       </c>
       <c r="E15">
-        <v>-5.4170447110038817E-5</v>
+        <v>-1.2150213826119868E-4</v>
       </c>
       <c r="F15">
-        <v>-6.838577944489543E-5</v>
+        <v>-1.2975359834338469E-4</v>
       </c>
       <c r="G15">
-        <v>1.2934976085714162E-6</v>
+        <v>3.1570715686370967E-7</v>
       </c>
       <c r="H15">
-        <v>6.5448357706602333E-7</v>
+        <v>-2.093768492365384E-6</v>
       </c>
       <c r="I15">
-        <v>-1.6539226477007367E-5</v>
+        <v>4.325161289895353E-5</v>
       </c>
       <c r="J15">
-        <v>-1.3503340704290248E-5</v>
+        <v>-1.7023824768450618E-5</v>
       </c>
       <c r="K15">
-        <v>3.818614437122723E-5</v>
+        <v>-2.8942685802240851E-5</v>
       </c>
       <c r="L15">
-        <v>4.8096405166353127E-5</v>
+        <v>-3.0381477934219008E-5</v>
       </c>
       <c r="M15">
-        <v>4.1302534985789236E-5</v>
+        <v>-5.7430355159880696E-5</v>
       </c>
       <c r="N15">
-        <v>3.4590680505645519E-5</v>
+        <v>-1.3691875555393892E-4</v>
       </c>
       <c r="O15">
-        <v>3.7037031322499755E-4</v>
+        <v>5.9508925901910112E-4</v>
       </c>
       <c r="P15">
-        <v>1.3646239367116841E-3</v>
+        <v>8.2866118625574733E-4</v>
       </c>
       <c r="Q15">
-        <v>3.6420172411396853E-4</v>
+        <v>-2.3681580572168187E-5</v>
       </c>
       <c r="R15">
-        <v>3.6502631301578198E-4</v>
+        <v>3.6272036016440062E-5</v>
       </c>
       <c r="S15">
-        <v>-4.7970792346286467E-6</v>
-      </c>
-      <c r="T15">
-        <v>-1.3680342947719369E-5</v>
-      </c>
-      <c r="U15">
-        <v>-3.9387172454949349E-4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-3.9417444782652799E-4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B16">
-        <v>5.7814928672014425E-2</v>
+        <v>-0.13184738394069029</v>
       </c>
       <c r="C16">
-        <v>2.3991446953912111E-6</v>
+        <v>7.3110629487688374E-6</v>
       </c>
       <c r="D16">
-        <v>-2.7963942818845067E-8</v>
+        <v>-1.0985379778191721E-7</v>
       </c>
       <c r="E16">
-        <v>-1.5659281569126556E-5</v>
+        <v>1.9240455357888676E-5</v>
       </c>
       <c r="F16">
-        <v>2.4455767231052672E-5</v>
+        <v>5.7537973327299321E-5</v>
       </c>
       <c r="G16">
-        <v>1.962202378184701E-7</v>
+        <v>-8.4086490503052985E-7</v>
       </c>
       <c r="H16">
-        <v>-4.5905722994325752E-7</v>
+        <v>-8.0973506603725822E-7</v>
       </c>
       <c r="I16">
-        <v>2.7328509818100592E-6</v>
+        <v>2.9769772419562816E-5</v>
       </c>
       <c r="J16">
-        <v>-9.7038111611169713E-6</v>
+        <v>-1.601460813675806E-5</v>
       </c>
       <c r="K16">
-        <v>1.9637980948991769E-6</v>
+        <v>4.0955476855725618E-5</v>
       </c>
       <c r="L16">
-        <v>4.9685513221011692E-6</v>
+        <v>2.8809987422450745E-6</v>
       </c>
       <c r="M16">
-        <v>-1.3975399154520852E-5</v>
+        <v>-1.524186383173871E-5</v>
       </c>
       <c r="N16">
-        <v>7.3475129002230485E-6</v>
+        <v>-3.9095956266818461E-5</v>
       </c>
       <c r="O16">
-        <v>3.6415447632432801E-4</v>
+        <v>-6.2068087059668071E-5</v>
       </c>
       <c r="P16">
-        <v>3.6420172411396853E-4</v>
+        <v>-2.3681580572168187E-5</v>
       </c>
       <c r="Q16">
-        <v>7.1554020928869778E-4</v>
+        <v>1.4094582908010895E-3</v>
       </c>
       <c r="R16">
-        <v>3.6551066523228439E-4</v>
+        <v>1.6482390717076316E-4</v>
       </c>
       <c r="S16">
-        <v>-9.8610578505999353E-6</v>
-      </c>
-      <c r="T16">
-        <v>-2.2995204200527797E-5</v>
-      </c>
-      <c r="U16">
-        <v>-3.9968679920780769E-4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-2.093084983721721E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="B17">
-        <v>-2.1913673614024333E-2</v>
+        <v>6.1021982515530267E-2</v>
       </c>
       <c r="C17">
-        <v>-3.3191668018174263E-6</v>
+        <v>1.3631580733524158E-5</v>
       </c>
       <c r="D17">
-        <v>2.3311869542606505E-8</v>
+        <v>-2.0467457236225154E-7</v>
       </c>
       <c r="E17">
-        <v>-3.6652921427093446E-5</v>
+        <v>-6.6312637477876813E-5</v>
       </c>
       <c r="F17">
-        <v>-3.1949093644481304E-5</v>
+        <v>-8.8148846299568074E-5</v>
       </c>
       <c r="G17">
-        <v>9.6077506648547138E-7</v>
+        <v>3.4796851448337864E-7</v>
       </c>
       <c r="H17">
-        <v>7.51976611483882E-7</v>
+        <v>2.1088534207859283E-6</v>
       </c>
       <c r="I17">
-        <v>1.4405351413018885E-5</v>
+        <v>4.7778292883395375E-5</v>
       </c>
       <c r="J17">
-        <v>-3.1011652843156467E-6</v>
+        <v>-2.7772084131539434E-5</v>
       </c>
       <c r="K17">
-        <v>-6.8603135056956728E-6</v>
+        <v>1.6884896246418141E-4</v>
       </c>
       <c r="L17">
-        <v>-2.9767458511327526E-5</v>
+        <v>1.983695665447156E-5</v>
       </c>
       <c r="M17">
-        <v>-2.9562792813617707E-5</v>
+        <v>6.176432650481403E-5</v>
       </c>
       <c r="N17">
-        <v>-9.6822832539177506E-6</v>
+        <v>2.7503885289132486E-5</v>
       </c>
       <c r="O17">
-        <v>3.650370310593585E-4</v>
+        <v>4.5984356418568073E-5</v>
       </c>
       <c r="P17">
-        <v>3.6502631301578198E-4</v>
+        <v>3.6272036016440062E-5</v>
       </c>
       <c r="Q17">
-        <v>3.6551066523228439E-4</v>
+        <v>1.6482390717076316E-4</v>
       </c>
       <c r="R17">
-        <v>7.0548371493185452E-4</v>
+        <v>4.8531943851173875E-3</v>
       </c>
       <c r="S17">
-        <v>-2.0037083366513791E-5</v>
-      </c>
-      <c r="T17">
-        <v>-2.6145515327277031E-5</v>
-      </c>
-      <c r="U17">
-        <v>-2.4854654835416664E-4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+        <v>-3.9996189495915849E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B18">
-        <v>2.6293346108347087E-2</v>
+        <v>-2.1109549089821558</v>
       </c>
       <c r="C18">
-        <v>5.542133523911114E-7</v>
+        <v>-2.0132406675531685E-3</v>
       </c>
       <c r="D18">
-        <v>-1.1647933314582327E-8</v>
+        <v>2.0421382490313473E-5</v>
       </c>
       <c r="E18">
-        <v>3.5847934905068052E-5</v>
+        <v>-1.2815575569462336E-2</v>
       </c>
       <c r="F18">
-        <v>4.3159309391400518E-5</v>
+        <v>-6.0950607968087E-3</v>
       </c>
       <c r="G18">
-        <v>-5.1301654658652414E-7</v>
+        <v>2.7475551255166318E-4</v>
       </c>
       <c r="H18">
-        <v>-3.844878576548745E-7</v>
+        <v>1.2996263204848529E-4</v>
       </c>
       <c r="I18">
-        <v>3.3786718897630341E-5</v>
+        <v>1.3947093333270183E-5</v>
       </c>
       <c r="J18">
-        <v>-6.8016713171535625E-6</v>
+        <v>1.9940792767828984E-3</v>
       </c>
       <c r="K18">
-        <v>6.9827762657253696E-5</v>
+        <v>-3.3429701872089948E-2</v>
       </c>
       <c r="L18">
-        <v>9.602603037848085E-5</v>
+        <v>-3.3499347329985371E-2</v>
       </c>
       <c r="M18">
-        <v>1.7272832640820456E-4</v>
+        <v>-3.3137589384682087E-2</v>
       </c>
       <c r="N18">
-        <v>1.9130658856181401E-4</v>
+        <v>-3.3595617969659146E-2</v>
       </c>
       <c r="O18">
-        <v>1.3075309473251689E-6</v>
+        <v>-6.4435638581217497E-4</v>
       </c>
       <c r="P18">
-        <v>-4.7970792346286467E-6</v>
+        <v>-3.9417444782652799E-4</v>
       </c>
       <c r="Q18">
-        <v>-9.8610578505999353E-6</v>
+        <v>-2.093084983721721E-4</v>
       </c>
       <c r="R18">
-        <v>-2.0037083366513791E-5</v>
+        <v>-3.9996189495915849E-4</v>
       </c>
       <c r="S18">
-        <v>9.4869603445216092E-4</v>
-      </c>
-      <c r="T18">
-        <v>1.0055023555592694E-4</v>
-      </c>
-      <c r="U18">
-        <v>-2.8476340521160862E-4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19">
-        <v>4.5535795803608003E-2</v>
-      </c>
-      <c r="C19">
-        <v>5.2746190028111183E-6</v>
-      </c>
-      <c r="D19">
-        <v>-6.8873212652933109E-8</v>
-      </c>
-      <c r="E19">
-        <v>6.2512585385281915E-5</v>
-      </c>
-      <c r="F19">
-        <v>7.6604072547063409E-5</v>
-      </c>
-      <c r="G19">
-        <v>-9.4346988155687637E-7</v>
-      </c>
-      <c r="H19">
-        <v>-1.1530492061730575E-6</v>
-      </c>
-      <c r="I19">
-        <v>3.54521696126912E-5</v>
-      </c>
-      <c r="J19">
-        <v>-1.1669827593387049E-5</v>
-      </c>
-      <c r="K19">
-        <v>-1.9480778303288568E-5</v>
-      </c>
-      <c r="L19">
-        <v>-2.6767836730126195E-5</v>
-      </c>
-      <c r="M19">
-        <v>-3.2382936481249172E-5</v>
-      </c>
-      <c r="N19">
-        <v>-7.4289154693602132E-5</v>
-      </c>
-      <c r="O19">
-        <v>-9.1663994682348562E-6</v>
-      </c>
-      <c r="P19">
-        <v>-1.3680342947719369E-5</v>
-      </c>
-      <c r="Q19">
-        <v>-2.2995204200527797E-5</v>
-      </c>
-      <c r="R19">
-        <v>-2.6145515327277031E-5</v>
-      </c>
-      <c r="S19">
-        <v>1.0055023555592694E-4</v>
-      </c>
-      <c r="T19">
-        <v>1.7169054178136076E-3</v>
-      </c>
-      <c r="U19">
-        <v>-1.6900310894604875E-4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>26</v>
-      </c>
-      <c r="B20">
-        <v>-2.8488763167161055</v>
-      </c>
-      <c r="C20">
-        <v>-1.1135601312801011E-3</v>
-      </c>
-      <c r="D20">
-        <v>1.0553055313925292E-5</v>
-      </c>
-      <c r="E20">
-        <v>-9.6714204456533823E-3</v>
-      </c>
-      <c r="F20">
-        <v>-8.1509002182341833E-3</v>
-      </c>
-      <c r="G20">
-        <v>2.0260508682320348E-4</v>
-      </c>
-      <c r="H20">
-        <v>1.7272721890891285E-4</v>
-      </c>
-      <c r="I20">
-        <v>-6.9602413068016615E-5</v>
-      </c>
-      <c r="J20">
-        <v>1.1597034318128123E-3</v>
-      </c>
-      <c r="K20">
-        <v>-1.8265334684390032E-2</v>
-      </c>
-      <c r="L20">
-        <v>-1.8232071887149381E-2</v>
-      </c>
-      <c r="M20">
-        <v>-1.8328144779612615E-2</v>
-      </c>
-      <c r="N20">
-        <v>-1.8658961389699226E-2</v>
-      </c>
-      <c r="O20">
-        <v>-3.3089833030840703E-4</v>
-      </c>
-      <c r="P20">
-        <v>-3.9387172454949349E-4</v>
-      </c>
-      <c r="Q20">
-        <v>-3.9968679920780769E-4</v>
-      </c>
-      <c r="R20">
-        <v>-2.4854654835416664E-4</v>
-      </c>
-      <c r="S20">
-        <v>-2.8476340521160862E-4</v>
-      </c>
-      <c r="T20">
-        <v>-1.6900310894604875E-4</v>
-      </c>
-      <c r="U20">
-        <v>4.6045282318807251E-2</v>
+        <v>8.0132395338931461E-2</v>
       </c>
     </row>
   </sheetData>
